--- a/datasets.xlsx
+++ b/datasets.xlsx
@@ -4318,20 +4318,86 @@
       <c r="AB42" s="2" t="n"/>
     </row>
     <row r="43" ht="14.25" customHeight="1">
-      <c r="A43" s="1" t="n"/>
-      <c r="B43" s="1" t="n"/>
-      <c r="C43" s="1" t="n"/>
-      <c r="D43" s="3" t="n"/>
-      <c r="E43" s="1" t="n"/>
-      <c r="F43" s="1" t="n"/>
-      <c r="G43" s="1" t="n"/>
+      <c r="A43" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="1" t="inlineStr">
+        <is>
+          <t>EPA Enterprise Data Catalog</t>
+        </is>
+      </c>
+      <c r="C43" s="1" t="inlineStr">
+        <is>
+          <t>EPA's Enterprise Data Catalog indexes thousands of agency air, water, land, and chemical datasets for open discovery.</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>https://www.epa.gov/data/enterprise-data-catalog</t>
+        </is>
+      </c>
+      <c r="E43" s="1" t="inlineStr">
+        <is>
+          <t>People; Ecosystems</t>
+        </is>
+      </c>
+      <c r="F43" s="1" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="G43" s="1" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
       <c r="H43" s="1" t="n"/>
-      <c r="I43" s="1" t="n"/>
-      <c r="J43" s="1" t="n"/>
-      <c r="K43" s="3" t="n"/>
-      <c r="L43" s="1" t="n"/>
-      <c r="M43" s="3" t="n"/>
-      <c r="N43" s="1" t="n"/>
+      <c r="I43" s="1" t="n">
+        <v>1901</v>
+      </c>
+      <c r="J43" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>Ecosystem Data; Public Health; Air Quality; Water Quality; Land Management; Energy</t>
+        </is>
+      </c>
+      <c r="L43" s="1" t="inlineStr">
+        <is>
+          <t>EPA; U.S. EPA; US EPA; USEPA; United States Environmental Protection Agency; Environmental Protection Agency; Enterprise Data Catalog; EDC; Environmental Dataset Gateway; EDG; Data.gov; General Services Administration; GSA; Office of Mission Support; Office of Information Collection; open data; open government; metadata catalog; data inventory; federal data; government data; air quality; water quality; drinking water; watersheds; impaired waters; surface water; groundwater; greenhouse gas emissions; GHG inventory; emission factors; criteria pollutants; toxic chemical releases; Toxics Release Inventory; TRI; PCBs; pesticides; chemicals; chemical safety; hazardous waste; solid waste; Superfund; brownfields; contaminated sites; environmental justice; climate change; climate change indicators; ecosystem services; land cover; land use; facility compliance; enforcement data; ecotoxicology; ECOTOX; Envirofacts; EnviroAtlas; ECHO; Enforcement and Compliance History Online; AirNow; AirData; Air Quality System; AQS; ATTAINS; WATERS; Clean Air Markets; Facility Registry Service; FRS; System of Registries; Central Data Exchange; CDX; How's My Waterway; Clip and Ship; EPA GeoPlatform; GIS; geospatial data; geospatial analysis; shapefile; CSV; JSON; GeoJSON; XML; XLSX; ZIP; KML; REST API; web services; API; api.data.gov; API key; DCAT; FGDC; ISO 19115; metadata; CKAN; ArcGIS; ArcGIS Hub; Esri; environmental monitoring; exposure assessment; risk assessment; ecological risk assessment; environmental epidemiology; environmental toxicology; environmental compliance; environmental health; One Health; pollution; emissions; regulatory data; United States; nationwide; state-level; county-level; facility-level; EPA Regions; watershed data; Ecosystem Data; Public Health; Air Quality; Water Quality; Land Management; Energy; Historic; Current; Present; 1901-2026; continuously updated</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>The Enterprise Data Catalog is the U.S. Environmental Protection Agency's master inventory of open data; the former Environmental Dataset Gateway (EDG) now redirects here. Metadata records contributed by EPA program offices, regional offices, and research laboratories cover air, water, land, waste, chemicals, climate, and environmental-health topics, with the searchable catalog hosted on Data.gov (about 6,600 EPA datasets as of September 2026). Researchers can download data in common formats, extract custom geospatial subsets, browse bulk files by office and region, or query the agency's public APIs and web services.
+#### Host Organization
+- United States Environmental Protection Agency (U.S. EPA)
+#### Data Format
+- Formats vary by dataset; commonly:
+	- **Tabular/structured**: CSV, JSON, XLSX, XML, ZIP archives
+	- **Geospatial**: GeoJSON, KML, plus on-demand extraction via the Clip and Ship ArcGIS Hub
+- Nine public APIs and web services (e.g., AirData AQS, ECHO, WATERS, Facility Registry Service); some require a free api.data.gov key
+#### How to access data of interest
+- Orient at the [EPA Enterprise Data Catalog](https://www.epa.gov/data/enterprise-data-catalog), which links every access route
+- Search and filter EPA's inventory on [Data.gov](https://catalog.data.gov/organization/epa-gov) by keyword, tag, and format, then download from the dataset record - no login needed
+- Browse bulk files by EPA office and region at the [EPA Data Download Site](https://edg.epa.gov/data/public/) or pick an API from [EPA Data APIs](https://www.epa.gov/data/application-programming-interface-api)
+#### Database Time Range
+- 1901-2026
+	- Coverage varies by dataset; some historical series reach back to the early 1900s
+#### Access Type
+- Public
+#### Citation Information
+- EPA data is public domain by default under the [EPA Data License](https://edg.epa.gov/EPA_Data_License.html); cite individual datasets per their own metadata
+- U.S. Environmental Protection Agency. "Enterprise Data Catalog." *US EPA*, May 2026, &lt;https://www.epa.gov/data/enterprise-data-catalog&gt;. 2026-09-01
+- See specific source citation details on the database website.</t>
+        </is>
+      </c>
+      <c r="N43" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
       <c r="O43" s="1" t="n"/>
       <c r="P43" s="1" t="n"/>
       <c r="Q43" s="1" t="n"/>
@@ -4348,20 +4414,85 @@
       <c r="AB43" s="2" t="n"/>
     </row>
     <row r="44" ht="14.25" customHeight="1">
-      <c r="A44" s="1" t="n"/>
-      <c r="B44" s="1" t="n"/>
-      <c r="C44" s="1" t="n"/>
-      <c r="D44" s="3" t="n"/>
-      <c r="E44" s="1" t="n"/>
-      <c r="F44" s="1" t="n"/>
-      <c r="G44" s="1" t="n"/>
+      <c r="A44" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="1" t="inlineStr">
+        <is>
+          <t>EPA AirData</t>
+        </is>
+      </c>
+      <c r="C44" s="1" t="inlineStr">
+        <is>
+          <t>AirData provides outdoor air quality data from thousands of monitors across the U.S. since 1980.</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>https://www.epa.gov/outdoor-air-quality-data</t>
+        </is>
+      </c>
+      <c r="E44" s="1" t="inlineStr">
+        <is>
+          <t>People; Ecosystems</t>
+        </is>
+      </c>
+      <c r="F44" s="1" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="G44" s="1" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
       <c r="H44" s="1" t="n"/>
-      <c r="I44" s="1" t="n"/>
-      <c r="J44" s="1" t="n"/>
-      <c r="K44" s="3" t="n"/>
-      <c r="L44" s="1" t="n"/>
-      <c r="M44" s="3" t="n"/>
-      <c r="N44" s="1" t="n"/>
+      <c r="I44" s="1" t="n">
+        <v>1980</v>
+      </c>
+      <c r="J44" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>Air Quality; Public Health; Population Health; Ecosystem Data; Weather</t>
+        </is>
+      </c>
+      <c r="L44" s="1" t="inlineStr">
+        <is>
+          <t>AirData; EPA AirData; Outdoor Air Quality Data; EPA; U.S. EPA; US EPA; USEPA; United States Environmental Protection Agency; Environmental Protection Agency; Office of Air and Radiation; OAR; OAQPS; state local and tribal air agencies; Air Quality System; AQS; AQS Data Mart; AQS API; AirNow; Fire and Smoke Map; Pre-generated Data Files; Download Daily Data; Daily Air Quality Tracker; Tile Plot; AQI Plot; Concentration Plot; Concentration Map; Air Quality Index Report; Monitor Values Report; air quality; air pollution; outdoor air; ambient air; air monitoring; PM2.5; PM10; particulate matter; fine particles; coarse particles; ozone; O3; ground-level ozone; carbon monoxide; CO; nitrogen dioxide; NO2; sulfur dioxide; SO2; lead; Pb; criteria pollutants; criteria gases; hazardous air pollutants; HAPs; air toxics; VOCs; volatile organic compounds; ozone precursors; PM speciation; AQI; Air Quality Index; NAAQS; National Ambient Air Quality Standards; design values; total suspended particulate; TSP; meteorological data; wind; temperature; humidity; barometric pressure; smoke; wildfire smoke; emissions; smog; haze; visibility; CSV; ZIP; JSON; REST API; API key; OpenAPI; interactive maps; charts; reports; air quality monitoring; air pollution epidemiology; exposure assessment; environmental epidemiology; atmospheric science; environmental monitoring; respiratory health; asthma; cardiovascular health; environmental justice; trend analysis; regulatory data; United States; USA; nationwide; Puerto Rico; U.S. Virgin Islands; state; county; city; CBSA; monitoring site; outdoor monitors; Air Quality; Public Health; Population Health; Ecosystem Data; Weather; Historic; Current; Present; 1980-2026; 1957; hourly data; daily summaries; annual summaries; ozone season; updated semiannually</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>AirData is EPA's public gateway to the Air Quality System (AQS), the agency's repository of ambient air measurements reported by EPA, state, local, and tribal agencies at thousands of outdoor monitors across the United States, Puerto Rico, and the U.S. Virgin Islands. It offers pre-generated annual, daily, and hourly files for criteria pollutants, air toxics, and meteorological parameters from 1980 to the present, plus interactive query tools, AQI reports, visualizations, and an API for row-level data. These are the quality-assured measurements behind federal air standards; for real-time conditions, EPA points users to AirNow.
+#### Host Organization
+- United States Environmental Protection Agency (U.S. EPA)
+#### Data Format
+- **Pre-generated bulk files**: CSV in ZIP archives by pollutant and year (annual, daily, hourly)
+- **AQS API**: JSON REST web service for row-level sample data (free email registration for a key)
+- **Interactive tools**: filtered CSV extracts, AQI reports, and visualizations on the AirData site
+#### How to access data of interest
+- Start at [EPA AirData](https://www.epa.gov/outdoor-air-quality-data) and choose downloads, visualizations, or reports
+- For bulk data, open [Pre-generated Data Files](https://aqs.epa.gov/aqsweb/airdata/download_files.html), pick pollutant, aggregation level, and year - no login needed
+- For a filtered slice, use [Download Daily Data](https://www.epa.gov/outdoor-air-quality-data/download-daily-data); for programmatic access, register for the [AQS API](https://aqs.epa.gov/aqsweb/documents/data_api.html)
+#### Database Time Range
+- 1980-2026
+	- Scattered AQS records reach back to 1957 for a few Los Angeles County monitors; 1980 marks the start of nationally consistent monitoring procedures
+#### Access Type
+- Public
+#### Citation Information
+- Follow the instructions on [How do I cite AirData?](https://www.epa.gov/outdoor-air-quality-data/how-do-i-cite-data-and-graphics-obtained-airdata-website)
+- US Environmental Protection Agency. *Air Quality System Data Mart* [internet database], available via &lt;https://www.epa.gov/outdoor-air-quality-data&gt;. Accessed September 1, 2026.
+- See specific source citation details on the database website.</t>
+        </is>
+      </c>
+      <c r="N44" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
       <c r="O44" s="1" t="n"/>
       <c r="P44" s="1" t="n"/>
       <c r="Q44" s="1" t="n"/>
@@ -4378,20 +4509,84 @@
       <c r="AB44" s="2" t="n"/>
     </row>
     <row r="45" ht="14.25" customHeight="1">
-      <c r="A45" s="1" t="n"/>
-      <c r="B45" s="1" t="n"/>
-      <c r="C45" s="1" t="n"/>
-      <c r="D45" s="3" t="n"/>
-      <c r="E45" s="1" t="n"/>
-      <c r="F45" s="1" t="n"/>
-      <c r="G45" s="1" t="n"/>
+      <c r="A45" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="1" t="inlineStr">
+        <is>
+          <t>Water Quality Portal</t>
+        </is>
+      </c>
+      <c r="C45" s="1" t="inlineStr">
+        <is>
+          <t>Water Quality Portal serves 400+ million water-quality records from USGS, EPA, and 1,000+ partners for research.</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>https://www.waterqualitydata.us/</t>
+        </is>
+      </c>
+      <c r="E45" s="1" t="inlineStr">
+        <is>
+          <t>Ecosystems; Animals; People</t>
+        </is>
+      </c>
+      <c r="F45" s="1" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="G45" s="1" t="inlineStr">
+        <is>
+          <t>United States; Global</t>
+        </is>
+      </c>
       <c r="H45" s="1" t="n"/>
-      <c r="I45" s="1" t="n"/>
-      <c r="J45" s="1" t="n"/>
-      <c r="K45" s="3" t="n"/>
-      <c r="L45" s="1" t="n"/>
-      <c r="M45" s="3" t="n"/>
-      <c r="N45" s="1" t="n"/>
+      <c r="I45" s="1" t="n">
+        <v>1900</v>
+      </c>
+      <c r="J45" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>Water Quality; Ecosystem Data; Public Health; Conservation; Agriculture; Wildlife</t>
+        </is>
+      </c>
+      <c r="L45" s="1" t="inlineStr">
+        <is>
+          <t>Water Quality Portal; WQP; waterqualitydata.us; USGS; U.S. Geological Survey; United States Geological Survey; EPA; U.S. Environmental Protection Agency; Environmental Protection Agency; NWQMC; National Water Quality Monitoring Council; USDA; Agricultural Research Service; ARS; STEWARDS; NWIS; National Water Information System; WQX; Water Quality Exchange; WQX 3.0; STORET; BIODATA; BioData; water quality; water data; freshwater; surface water; groundwater; drinking water; source water; streams; rivers; lakes; reservoirs; estuaries; coastal waters; wetlands; wells; springs; aquifers; watershed; nutrients; nitrogen; phosphorus; nitrate; phosphate; pH; dissolved oxygen; water temperature; specific conductance; conductivity; turbidity; salinity; metals; heavy metals; mercury; pesticides; contaminants; pollutants; sediment; chlorophyll; E. coli; fecal coliform; fecal indicator bacteria; pathogens; microbiology; biological indicators; macroinvertebrates; benthic; fish community; habitat assessment; taxonomy; aquatic life; aquatic ecology; limnology; hydrology; watershed science; water resources; water monitoring; water sampling; discrete sampling; monitoring stations; monitoring network; water-quality assessment; biogeochemistry; CSV; TSV; Excel; XLSX; KML; KMZ; GeoJSON; XML; WQX XML; REST API; web services; WMS; WFS; OGC; dataRetrieval; R package; R; Python; United States; all 50 states; District of Columbia; Puerto Rico; Guam; American Samoa; Canada; Mexico; Great Lakes; HUC; hydrologic unit code; bounding box; county-level; state-level; Water Quality; Ecosystem Data; Public Health; Conservation; Agriculture; Wildlife; Historic; Current; Present; 1900-2026; twice-weekly updates; century-scale records</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>The Water Quality Portal (WQP) is the largest standardized source of discrete water-quality monitoring data for the United States, integrating the USGS National Water Information System (NWIS), the EPA Water Quality Exchange (WQX), the USDA ARS STEWARDS database, and USGS BioData into a single query point. It delivers physical, chemical, microbiological, and biological results - nutrients, contaminants, pH, temperature, bacteria, and aquatic-community metrics - from millions of monitoring locations in streams, lakes, groundwater, and coastal waters, with some records extending back more than a century. USGS NWIS data is refreshed daily and EPA WQX data weekly (Thursday evenings), and the portal is midway through a multi-year modernization to the richer WQX 3.0 data profile.
+#### Host Organization
+- United States Geological Survey (USGS), U.S. Environmental Protection Agency (EPA), and the National Water Quality Monitoring Council (NWQMC)
+#### Data Format
+- Query downloads: **CSV**, **TSV**, **MS Excel**, **KML/KMZ**, **GeoJSON**, and **WQX XML**, optionally zipped
+- REST-like web services (Station, Result, Project, Activity, and biological endpoints) plus OGC WMS/WFS map services; the USGS *dataRetrieval* R package wraps them
+#### How to access data of interest
+- Open the [Water Quality Portal](https://www.waterqualitydata.us/) and build a query by location, site type, sample media, characteristic, and date range
+- Choose a data profile and file format, then download; guidance in the [WQP User Guide](https://www.waterqualitydata.us/portal_userguide/)
+- For scripted retrieval, see the [Web Services Guide](https://www.waterqualitydata.us/webservices_documentation/); USGS data added after March 11, 2024 currently requires the [WQX 3.0 beta profiles](https://www.waterqualitydata.us/beta/)
+#### Database Time Range
+- 1900-2026
+	- Holdings date back more than a century; no exact earliest year is published
+#### Access Type
+- Public
+#### Citation Information
+- Follow the instructions in the [WQP User Guide](https://www.waterqualitydata.us/portal_userguide/) under "Cite the Water Quality Portal"
+- National Water Quality Monitoring Council, United States Geological Survey (USGS), and Environmental Protection Agency (EPA). "Water Quality Portal." *Water Quality Portal*, 2021, &lt;https://doi.org/10.5066/P9QRKUVJ&gt;. 2026-09-01
+- See specific source citation details on the database website.</t>
+        </is>
+      </c>
+      <c r="N45" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
       <c r="O45" s="1" t="n"/>
       <c r="P45" s="1" t="n"/>
       <c r="Q45" s="1" t="n"/>

--- a/datasets.xlsx
+++ b/datasets.xlsx
@@ -3130,12 +3130,12 @@
       </c>
       <c r="K29" s="23" t="inlineStr">
         <is>
-          <t>Animal Health; Biological Variability; Disease Surveillance; Infectious Disease Monitoring; Public Health</t>
+          <t>Animal Health; Biological Variability; Disease Surveillance; Infectious Disease Monitoring; Public Health; Genomics</t>
         </is>
       </c>
       <c r="L29" s="24" t="inlineStr">
         <is>
-          <t>BV-BRC; PATRIC; IRD; ViPR; bacterial genomes; viral genomes; annotated genomes; genome assembly; antimicrobial resistance; AMR; antibiotic resistance; virulence factors; genome metadata; host metadata; phylogenetics; phylogenomic analysis; pan-genome; core genome; genome browser; genome annotation; comparative genomics; protein families; protein-protein interactions; metabolic pathways; protein structures; viral proteins; pathogen-host interactions; serology; surveillance data; high-throughput sequencing; whole genome sequencing; transcriptomics; gene expression; metagenomics; metatranscriptomics; epitope prediction; immune epitopes; vaccine targets; CRISPR-Cas systems; biosurveillance; zoonotic diseases; emerging pathogens; NIAID; reference genomes; representative genomes; RefSeq; GenBank; SRA; host-pathogen interactions; functional annotation; SNP analysis; protein domains; alignment tools; BLAST; multiple sequence alignment; Clustal Omega; MUSCLE; phylogenetic trees; tree viewer; heatmap; genome statistics; metadata visualization; sample metadata; taxonomic classification; microbial taxonomy; pathogen genomics; infectious diseases; comparative analysis; data mining; infectious disease informatics; bacterial pathogens; viral pathogens; virome; bacteriophage; eukaryotic pathogens; zoonoses; host data; sample metadata; disease outbreak data; annotation services; genome annotation pipeline; custom genomes; private workspace; command-line tools; REST API; data integration; NCBI data; biosample metadata; curated data; experimental data; computational predictions; public health; clinical isolates; biothreat agents; NIAID priority pathogens; biodefense; antibiotic targets; resistance genes; virulence genes; microbial surveillance; public data repository; big data; systems biology; bioinformatics tools; omics data; sequence data; comparative tools; data visualization; integrated workflows; curated genomes; taxonomic lineage; literature mining; PubMed integration; protein annotations; functional roles; subsystem annotation; comparative pathway analysis; AMR metadata; epidemiological metadata; genome feature comparison; fastq files; GFF files; genome FASTA; protein FASTA; genome reports; metadata filtering; viral surveillance; global health; research resource; scientific reproducibility; data provenance; microbial ecology; host specificity; host range; sequence typing; MLST; genome epidemiology; genome metrics; read mapping; feature overview; experimental conditions; virology; bacteriology; pathogen discovery; infectious disease surveillance; virus taxonomy; genome graph; PATRIC tools; IRD tools; ViPR tools; clinical metadata; virome analysis; SARS-CoV-2; influenza virus; HIV; norovirus; coronavirus; enteric pathogens; foodborne pathogens; environmental sampling; biosample tracking; data submission; public genomics resource; genome curation; bacterial phylogeny; viral evolution; genetic markers; mobile genetic elements; insertion sequences; plasmid profiling; genomic islands; integrons; pathogenicity islands; horizontal gene transfer; molecular epidemiology; genome diversity; host adaptation; comparative virology; functional genomics; post-genomic analysis; genome-scale analysis; resistance profiling; virulence profiling; phylogenetic inference; maximum likelihood trees; genome-wide association studies; GWAS pathogens; proteome analysis; systems vaccinology; immunoinformatics; antibody response; antigen discovery; host response data; omics integration; transcriptome browser; single-cell sequencing; long-read sequencing; third-generation sequencing; genome completeness; assembly quality; contig analysis; scaffolding; automated annotation; protein modeling; genome visualization; genetic context analysis; viral genomics pipelines; outbreak tracking; pathogen transmission; epidemic modeling; time-resolved phylogenetics; metadata harmonization; FAIR data; public health bioinformatics; microbial forensics; host genotype; reservoir species; environmental metagenomics; microbial consortia; gene ontology; resistance ontology; virulence ontology; biological pathways; curated ontologies; strain typing; phenotypic profiling; laboratory data integration; sequence curation; in silico typing; pathogen surveillance networks; real-time genomics; data standardization; cross-species analysis; species-specific databases; experimental pipelines; web-based bioinformatics; predictive modeling; bioinformatics workflows; annotation accuracy; sequence QC; genome submission tools; research reproducibility; sample tracking; sequence repositories; outbreak databases; pathogen biogeography; genomics-informed response; integrative genomics; predictive epidemiology; comparative AMR analytics; pan-virome analysis; clinical pathogenomics; translational bioinformatics; genomic epidemiology platforms; emerging zoonoses monitoring; computational virology; sequence aligner tools; open-access bioinformatics; public sequencing efforts; genomic public health response; national bioinformatics networks; CSV; Text; DNA FASTA; Historic; Current; Present; 2025</t>
+          <t>BV-BRC; PATRIC; IRD; ViPR; bacterial genomes; viral genomes; annotated genomes; genome assembly; antimicrobial resistance; AMR; antibiotic resistance; virulence factors; genome metadata; host metadata; phylogenetics; phylogenomic analysis; pan-genome; core genome; genome browser; genome annotation; comparative genomics; protein families; protein-protein interactions; metabolic pathways; protein structures; viral proteins; pathogen-host interactions; serology; surveillance data; high-throughput sequencing; whole genome sequencing; transcriptomics; gene expression; metagenomics; metatranscriptomics; epitope prediction; immune epitopes; vaccine targets; CRISPR-Cas systems; biosurveillance; zoonotic diseases; emerging pathogens; NIAID; reference genomes; representative genomes; RefSeq; GenBank; SRA; host-pathogen interactions; functional annotation; SNP analysis; protein domains; alignment tools; BLAST; multiple sequence alignment; Clustal Omega; MUSCLE; phylogenetic trees; tree viewer; heatmap; genome statistics; metadata visualization; sample metadata; taxonomic classification; microbial taxonomy; pathogen genomics; infectious diseases; comparative analysis; data mining; infectious disease informatics; bacterial pathogens; viral pathogens; virome; bacteriophage; eukaryotic pathogens; zoonoses; host data; sample metadata; disease outbreak data; annotation services; genome annotation pipeline; custom genomes; private workspace; command-line tools; REST API; data integration; NCBI data; biosample metadata; curated data; experimental data; computational predictions; public health; clinical isolates; biothreat agents; NIAID priority pathogens; biodefense; antibiotic targets; resistance genes; virulence genes; microbial surveillance; public data repository; big data; systems biology; bioinformatics tools; omics data; sequence data; comparative tools; data visualization; integrated workflows; curated genomes; taxonomic lineage; literature mining; PubMed integration; protein annotations; functional roles; subsystem annotation; comparative pathway analysis; AMR metadata; epidemiological metadata; genome feature comparison; fastq files; GFF files; genome FASTA; protein FASTA; genome reports; metadata filtering; viral surveillance; global health; research resource; scientific reproducibility; data provenance; microbial ecology; host specificity; host range; sequence typing; MLST; genome epidemiology; genome metrics; read mapping; feature overview; experimental conditions; virology; bacteriology; pathogen discovery; infectious disease surveillance; virus taxonomy; genome graph; PATRIC tools; IRD tools; ViPR tools; clinical metadata; virome analysis; SARS-CoV-2; influenza virus; HIV; norovirus; coronavirus; enteric pathogens; foodborne pathogens; environmental sampling; biosample tracking; data submission; public genomics resource; genome curation; bacterial phylogeny; viral evolution; genetic markers; mobile genetic elements; insertion sequences; plasmid profiling; genomic islands; integrons; pathogenicity islands; horizontal gene transfer; molecular epidemiology; genome diversity; host adaptation; comparative virology; functional genomics; post-genomic analysis; genome-scale analysis; resistance profiling; virulence profiling; phylogenetic inference; maximum likelihood trees; genome-wide association studies; GWAS pathogens; proteome analysis; systems vaccinology; immunoinformatics; antibody response; antigen discovery; host response data; omics integration; transcriptome browser; single-cell sequencing; long-read sequencing; third-generation sequencing; genome completeness; assembly quality; contig analysis; scaffolding; automated annotation; protein modeling; genome visualization; genetic context analysis; viral genomics pipelines; outbreak tracking; pathogen transmission; epidemic modeling; time-resolved phylogenetics; metadata harmonization; FAIR data; public health bioinformatics; microbial forensics; host genotype; reservoir species; environmental metagenomics; microbial consortia; gene ontology; resistance ontology; virulence ontology; biological pathways; curated ontologies; strain typing; phenotypic profiling; laboratory data integration; sequence curation; in silico typing; pathogen surveillance networks; real-time genomics; data standardization; cross-species analysis; species-specific databases; experimental pipelines; web-based bioinformatics; predictive modeling; bioinformatics workflows; annotation accuracy; sequence QC; genome submission tools; research reproducibility; sample tracking; sequence repositories; outbreak databases; pathogen biogeography; genomics-informed response; integrative genomics; predictive epidemiology; comparative AMR analytics; pan-virome analysis; clinical pathogenomics; translational bioinformatics; genomic epidemiology platforms; emerging zoonoses monitoring; computational virology; sequence aligner tools; open-access bioinformatics; public sequencing efforts; genomic public health response; national bioinformatics networks; CSV; Text; DNA FASTA; Historic; Current; Present; 2025; Genomics</t>
         </is>
       </c>
       <c r="M29" s="25" t="inlineStr">
@@ -4603,20 +4603,84 @@
       <c r="AB45" s="2" t="n"/>
     </row>
     <row r="46" ht="14.25" customHeight="1">
-      <c r="A46" s="1" t="n"/>
-      <c r="B46" s="1" t="n"/>
-      <c r="C46" s="1" t="n"/>
-      <c r="D46" s="3" t="n"/>
-      <c r="E46" s="1" t="n"/>
-      <c r="F46" s="1" t="n"/>
-      <c r="G46" s="1" t="n"/>
+      <c r="A46" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="1" t="inlineStr">
+        <is>
+          <t>NASA Earthdata</t>
+        </is>
+      </c>
+      <c r="C46" s="1" t="inlineStr">
+        <is>
+          <t>NASA Earthdata provides free access to 178+ petabytes of satellite Earth observation data for research.</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>https://www.earthdata.nasa.gov/</t>
+        </is>
+      </c>
+      <c r="E46" s="1" t="inlineStr">
+        <is>
+          <t>Ecosystems; People</t>
+        </is>
+      </c>
+      <c r="F46" s="1" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="G46" s="1" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
       <c r="H46" s="1" t="n"/>
-      <c r="I46" s="1" t="n"/>
-      <c r="J46" s="1" t="n"/>
-      <c r="K46" s="3" t="n"/>
-      <c r="L46" s="1" t="n"/>
-      <c r="M46" s="3" t="n"/>
-      <c r="N46" s="1" t="n"/>
+      <c r="I46" s="1" t="n">
+        <v>1950</v>
+      </c>
+      <c r="J46" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>Ecosystem Data; Air Quality; Ocean; Long Term Weather Trends; Public Health</t>
+        </is>
+      </c>
+      <c r="L46" s="1" t="inlineStr">
+        <is>
+          <t>NASA; Earthdata; NASA Earthdata; EarthData; EOSDIS; Earth Observing System Data and Information System; ESDIS; ESDS; Earth Science Data Systems; DAAC; Distributed Active Archive Center; GES DISC; LP DAAC; NSIDC DAAC; OB.DAAC; Ocean Biology DAAC; ORNL DAAC; PO.DAAC; Physical Oceanography DAAC; SEDAC; Socioeconomic Data and Applications Center; ASF DAAC; Alaska Satellite Facility; GHRC; LAADS DAAC; Goddard Space Flight Center; Earth observation; satellite imagery; satellite data; remote sensing; aerosols; air temperature; precipitation; global precipitation; solar irradiance; radiation budget; sea surface temperature; ocean color; chlorophyll; sea level; sea ice; snow cover; cryosphere; glaciers; soil moisture; land cover; land use; vegetation index; NDVI; evapotranspiration; wildfire detection; thermal anomalies; aerosol optical depth; nitrogen dioxide; greenhouse gases; carbon dioxide; methane; hydrology; biodiversity; ecological dynamics; population density; socioeconomic indicators; environmental health; vector-borne disease environments; Earthdata Search; Worldview; GIBS; Giovanni; LANCE; FIRMS; AppEEARS; Earthdata Login; Common Metadata Repository; CMR; Harmony; earthaccess; Earthdata Cloud; Data Pathfinders; Health and Air Quality Data Pathfinder; Diseases Data Pathfinder; HDF; HDF5; HDF-EOS; netCDF; GeoTIFF; Cloud Optimized GeoTIFF; OPeNDAP; CSV; shapefile; REST API; WMTS; Python; R; geospatial analysis; GIS; Earth system science; climate science; climate modeling; time-series analysis; environmental epidemiology; near real-time; open data; global; polar regions; Arctic; Antarctica; oceans; Ecosystem Data; Air Quality; Ocean; Long Term Weather Trends; Public Health; Historic; Current; Present; 1950-2026; Nimbus; satellite era; multi-decadal; daily; ongoing</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>NASA Earthdata is the public gateway to NASA's Earth Observing System Data and Information System (EOSDIS), which archives more than 178 petabytes of satellite and field observations across 12 discipline-specific Distributed Active Archive Centers (DAACs). Anyone can search its 11,600+ EOSDIS collections (54,000+ including partner catalogs) or browse daily global imagery in Worldview without an account; downloading data requires a free Earthdata Login. For One Health work, its environmental records - air quality, temperature, precipitation, vegetation, water, and land use - pair with SEDAC's population and public-health datasets to connect ecosystem conditions with human and animal health outcomes. The NSIDC DAAC is operated by the National Snow and Ice Data Center, cataloged separately here.
+#### Host Organization
+- National Aeronautics and Space Administration (NASA), Earth Science Data Systems (ESDS) Program
+#### Data Format
+- NASA standard formats: **HDF5 / HDF-EOS5**, **netCDF**, and **GeoTIFF**, varying by collection
+- Programmatic access via the **CMR search API**, **OPeNDAP** subsetting, and the **earthaccess** Python library; visual browse via Worldview and Giovanni
+#### How to access data of interest
+- Explore topics, pathfinders, and tools at [NASA Earthdata](https://www.earthdata.nasa.gov/)
+- Search collections by keyword, map area, and date in [Earthdata Search](https://search.earthdata.nasa.gov/search) - no account needed to search
+- Create a free [Earthdata Login](https://urs.earthdata.nasa.gov/) (required for downloads), then download via Earthdata Search, individual DAAC portals, or programmatically
+#### Database Time Range
+- 1950-2026
+	- Selected archived field collections begin in the 1950s; the satellite record begins 1964 (Nimbus-1) and densifies from 1978
+#### Access Type
+- Free Registration
+#### Citation Information
+- Follow the [Data Use and Citation Guidance](https://www.earthdata.nasa.gov/about/esdis/esco/standards-practices/data-use-citation-guidance); individual datasets should be cited by their DOI
+- National Aeronautics and Space Administration. "NASA Earthdata." *NASA Earthdata*, September 2026, &lt;https://www.earthdata.nasa.gov/&gt;. 2026-09-01
+- See specific source citation details on the database website.</t>
+        </is>
+      </c>
+      <c r="N46" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
       <c r="O46" s="1" t="n"/>
       <c r="P46" s="1" t="n"/>
       <c r="Q46" s="1" t="n"/>
@@ -4633,20 +4697,84 @@
       <c r="AB46" s="2" t="n"/>
     </row>
     <row r="47" ht="14.25" customHeight="1">
-      <c r="A47" s="1" t="n"/>
-      <c r="B47" s="1" t="n"/>
-      <c r="C47" s="1" t="n"/>
-      <c r="D47" s="3" t="n"/>
-      <c r="E47" s="1" t="n"/>
-      <c r="F47" s="1" t="n"/>
-      <c r="G47" s="1" t="n"/>
+      <c r="A47" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="1" t="inlineStr">
+        <is>
+          <t>Ocean Biodiversity Information System</t>
+        </is>
+      </c>
+      <c r="C47" s="1" t="inlineStr">
+        <is>
+          <t>OBIS aggregates 220M+ marine species observations worldwide to support ocean science, conservation, and management.</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>https://obis.org/</t>
+        </is>
+      </c>
+      <c r="E47" s="1" t="inlineStr">
+        <is>
+          <t>Animals; Ecosystems</t>
+        </is>
+      </c>
+      <c r="F47" s="1" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="G47" s="1" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
       <c r="H47" s="1" t="n"/>
-      <c r="I47" s="1" t="n"/>
-      <c r="J47" s="1" t="n"/>
-      <c r="K47" s="3" t="n"/>
-      <c r="L47" s="1" t="n"/>
-      <c r="M47" s="3" t="n"/>
-      <c r="N47" s="1" t="n"/>
+      <c r="I47" s="1" t="n">
+        <v>1750</v>
+      </c>
+      <c r="J47" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>Ocean; Species Distribution; Ecosystem Data; Biological Variability; Conservation</t>
+        </is>
+      </c>
+      <c r="L47" s="1" t="inlineStr">
+        <is>
+          <t>OBIS; Ocean Biodiversity Information System; Ocean Biogeographic Information System; IOC; IOC-UNESCO; Intergovernmental Oceanographic Commission; UNESCO; IODE; International Oceanographic Data and Information Exchange; Census of Marine Life; CoML; iOBIS; marine species; marine biodiversity; species occurrence records; occurrence data; fish; marine mammals; whales; seabirds; sea turtles; plankton; zooplankton; phytoplankton; algae; corals; coral reefs; mollusks; crustaceans; benthos; invertebrates; abundance; biomass; presence absence; temperature; salinity; depth; DNA sequences; eDNA; environmental DNA; measurements and facts; OBIS nodes; OBIS-USA; EurOBIS; OBIS-SEAMAP; Ocean Tracking Network; GOOS; Global Ocean Observing System; MBON; Marine Biodiversity Observation Network; GEO BON; WoRMS; World Register of Marine Species; GBIF; LifeWatch; UN Ocean Decade; Darwin Core; DwC-A; Darwin Core Archive; extendedMeasurementOrFact; eMoF; OBIS-ENV-DATA; EML; CSV; TSV; JSON; GeoParquet; REST API; robis; pyobis; R; Python; OBIS Mapper; IPT; Integrated Publishing Toolkit; AWS Open Data; marine ecology; biogeography; biodiversity informatics; oceanography; species distribution modeling; taxonomy; marine spatial planning; conservation biology; essential ocean variables; global ocean; high seas; deep sea; coastal waters; EEZ; Arctic; Southern Ocean; Atlantic; Pacific; Indian Ocean; Ocean; Species Distribution; Ecosystem Data; Biological Variability; Conservation; Historic; Current; Present; 1750-2026; founded 2000; weekly updates; time series</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>The Ocean Biodiversity Information System (OBIS) is the global open-access clearing-house for marine biodiversity data, operated as a programme component of the International Oceanographic Data and Information Exchange (IODE) of UNESCO's Intergovernmental Oceanographic Commission. Founded in 2000 under the Census of Marine Life, OBIS today integrates over 220 million observations of some 200,000 marine taxa from roughly 7,000 datasets contributed by a worldwide network of 38 nodes. Unlike general biodiversity aggregators such as GBIF (also in this catalog), OBIS attaches environmental and sampling measurements and DNA-derived data to occurrence records and applies marine-specific quality control against the World Register of Marine Species.
+#### Host Organization
+- Intergovernmental Oceanographic Commission of UNESCO (IOC-UNESCO), IODE programme
+#### Data Format
+- **Darwin Core / Darwin Core Archive** source datasets with environmental extensions (OBIS-ENV-DATA, extendedMeasurementOrFact)
+- Subset downloads (CSV/TSV) via the OBIS Mapper; **JSON REST API**; **robis** (R) and **pyobis** (Python) clients; bulk **GeoParquet** exports on AWS Open Data
+#### How to access data of interest
+- Explore datasets and taxa in the [OBIS search portal](https://obis.org/search), or map, filter, and download subsets (no login) in the [OBIS Mapper](https://mapper.obis.org)
+- Query programmatically via the [OBIS API](https://api.obis.org) or the robis/pyobis clients
+- For large-scale analysis, pull full exports from [OBIS on AWS Open Data](https://registry.opendata.aws/obis/)
+#### Database Time Range
+- 1750-2026
+	- Continuous annual coverage begins in 1751; scattered earlier records reach back to the 1600s
+#### Access Type
+- Public
+#### Citation Information
+- Follow the instructions in the [OBIS Manual](https://manual.obis.org/citing.html); subset downloads should also cite individual datasets
+- Intergovernmental Oceanographic Commission of UNESCO. "Ocean Biodiversity Information System." *OBIS*, September 2026, &lt;https://obis.org/&gt;. 2026-09-01
+- See specific source citation details on the database website.</t>
+        </is>
+      </c>
+      <c r="N47" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
       <c r="O47" s="1" t="n"/>
       <c r="P47" s="1" t="n"/>
       <c r="Q47" s="1" t="n"/>
@@ -4663,20 +4791,84 @@
       <c r="AB47" s="2" t="n"/>
     </row>
     <row r="48" ht="14.25" customHeight="1">
-      <c r="A48" s="1" t="n"/>
-      <c r="B48" s="1" t="n"/>
-      <c r="C48" s="1" t="n"/>
-      <c r="D48" s="3" t="n"/>
-      <c r="E48" s="1" t="n"/>
-      <c r="F48" s="1" t="n"/>
-      <c r="G48" s="1" t="n"/>
+      <c r="A48" s="1" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="1" t="inlineStr">
+        <is>
+          <t>GenBank</t>
+        </is>
+      </c>
+      <c r="C48" s="1" t="inlineStr">
+        <is>
+          <t>GenBank archives billions of annotated DNA sequences spanning all organisms for free public research use.</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/genbank/</t>
+        </is>
+      </c>
+      <c r="E48" s="1" t="inlineStr">
+        <is>
+          <t>People; Animals; Ecosystems</t>
+        </is>
+      </c>
+      <c r="F48" s="1" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="G48" s="1" t="inlineStr">
+        <is>
+          <t>Global; United States</t>
+        </is>
+      </c>
       <c r="H48" s="1" t="n"/>
-      <c r="I48" s="1" t="n"/>
-      <c r="J48" s="1" t="n"/>
-      <c r="K48" s="3" t="n"/>
-      <c r="L48" s="1" t="n"/>
-      <c r="M48" s="3" t="n"/>
-      <c r="N48" s="1" t="n"/>
+      <c r="I48" s="1" t="n">
+        <v>1982</v>
+      </c>
+      <c r="J48" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>Genomics; Infectious Disease Monitoring; Disease Surveillance; Animal Health; Public Health; Biological Variability</t>
+        </is>
+      </c>
+      <c r="L48" s="1" t="inlineStr">
+        <is>
+          <t>GenBank; NCBI; National Center for Biotechnology Information; NLM; National Library of Medicine; NIH; National Institutes of Health; INSDC; International Nucleotide Sequence Database Collaboration; DDBJ; DNA Data Bank of Japan; ENA; European Nucleotide Archive; EMBL; EMBL-EBI; nucleotide sequences; DNA sequences; RNA; mRNA; cDNA; genomic DNA; genes; genomes; whole genome shotgun; WGS; transcriptome shotgun assembly; TSA; targeted locus study; TLS; EST; ribosomal RNA; 16S; DNA barcoding; metagenomes; environmental sequences; viruses; bacteria; archaea; fungi; plants; vertebrates; invertebrates; SARS-CoV-2; influenza; mitochondrial DNA; chloroplast genomes; plasmids; pathogen sequences; zoonotic pathogens; Entrez; Entrez Nucleotide; BLAST; E-utilities; efetch; esearch; NCBI Datasets; RefSeq; SRA; Sequence Read Archive; Taxonomy; BioProject; BioSample; PubMed; Submission Portal; BankIt; accession number; GenBank flatfile; ASN.1; FASTA; INSDSeq XML; feature table; FTP download; API key; REST API; genomics; bioinformatics; molecular biology; sequence annotation; phylogenetics; comparative genomics; next-generation sequencing; Sanger sequencing; open data; data sharing; Bethesda Maryland; United States; global; worldwide submissions; Genomics; Infectious Disease Monitoring; Disease Surveillance; Animal Health; Public Health; Biological Variability; Historic; Current; Present; 1982-2026; bimonthly releases; daily updates; 40+ years</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>GenBank is the NIH genetic sequence database - an annotated, openly available collection of all public DNA sequences, maintained since 1982 by the National Center for Biotechnology Information at the National Library of Medicine. It holds tens of trillions of base pairs from billions of records representing more than half a million described species, from humans and livestock to viruses, plants, and environmental microbes. As a founding member of the International Nucleotide Sequence Database Collaboration, GenBank exchanges data daily with its European (ENA) and Japanese (DDBJ) counterparts, making it the global deposit-of-record for sequence data cited in published research.
+#### Host Organization
+- National Center for Biotechnology Information (NCBI), National Library of Medicine, National Institutes of Health
+#### Data Format
+- **GenBank flatfile** and **ASN.1** release distributions; per-record retrieval as **FASTA** or XML
+- Web search via **Entrez Nucleotide** and **BLAST**; programmatic access via the **E-utilities REST API** (free; optional key raises rate limits); bulk **FTP** downloads
+#### How to access data of interest
+- Search records by organism, gene, or accession at [Entrez Nucleotide](https://www.ncbi.nlm.nih.gov/nucleotide/) - no account needed
+- Find sequences similar to your own with [BLAST](https://blast.ncbi.nlm.nih.gov/Blast.cgi)
+- For programmatic or bulk work, use the [E-utilities API](https://www.ncbi.nlm.nih.gov/books/NBK25501/) or the [GenBank FTP site](https://ftp.ncbi.nlm.nih.gov/genbank/)
+#### Database Time Range
+- 1982-2026
+	- Some records derive from sequences published before 1982; the database has grown continuously since its founding
+#### Access Type
+- Public
+#### Citation Information
+- Cite the current GenBank paper in *Nucleic Acids Research* (see the [GenBank Overview](https://www.ncbi.nlm.nih.gov/genbank/) for the recommended reference)
+- National Center for Biotechnology Information. "GenBank." *National Library of Medicine*, 2026, &lt;https://www.ncbi.nlm.nih.gov/genbank/&gt;. 2026-09-01
+- See specific source citation details on the database website.</t>
+        </is>
+      </c>
+      <c r="N48" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
       <c r="O48" s="1" t="n"/>
       <c r="P48" s="1" t="n"/>
       <c r="Q48" s="1" t="n"/>
@@ -4693,20 +4885,84 @@
       <c r="AB48" s="2" t="n"/>
     </row>
     <row r="49" ht="14.25" customHeight="1">
-      <c r="A49" s="1" t="n"/>
-      <c r="B49" s="1" t="n"/>
-      <c r="C49" s="1" t="n"/>
-      <c r="D49" s="3" t="n"/>
-      <c r="E49" s="1" t="n"/>
-      <c r="F49" s="1" t="n"/>
-      <c r="G49" s="1" t="n"/>
+      <c r="A49" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="1" t="inlineStr">
+        <is>
+          <t>NCBI Pathogen Detection</t>
+        </is>
+      </c>
+      <c r="C49" s="1" t="inlineStr">
+        <is>
+          <t>NCBI Pathogen Detection tracks 2.5M+ pathogen genomes for outbreak clusters and antimicrobial resistance.</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pathogens/</t>
+        </is>
+      </c>
+      <c r="E49" s="1" t="inlineStr">
+        <is>
+          <t>People; Animals; Ecosystems</t>
+        </is>
+      </c>
+      <c r="F49" s="1" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="G49" s="1" t="inlineStr">
+        <is>
+          <t>Global; United States</t>
+        </is>
+      </c>
       <c r="H49" s="1" t="n"/>
-      <c r="I49" s="1" t="n"/>
-      <c r="J49" s="1" t="n"/>
-      <c r="K49" s="3" t="n"/>
-      <c r="L49" s="1" t="n"/>
-      <c r="M49" s="3" t="n"/>
-      <c r="N49" s="1" t="n"/>
+      <c r="I49" s="1" t="n">
+        <v>2013</v>
+      </c>
+      <c r="J49" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>Disease Surveillance; Infectious Disease Monitoring; Genomics; Public Health; Animal Health; Agriculture</t>
+        </is>
+      </c>
+      <c r="L49" s="1" t="inlineStr">
+        <is>
+          <t>NCBI Pathogen Detection; Pathogen Detection; NCBI; National Center for Biotechnology Information; NLM; National Library of Medicine; NIH; FDA; CDC; USDA; WHO; PHE; UKHSA; NDARO; National Database of Antibiotic Resistant Organisms; NARMS; GenomeTrakr; PulseNet; state public health laboratories; Salmonella; Escherichia coli; E. coli; Shigella; Listeria; Listeria monocytogenes; Campylobacter; Klebsiella pneumoniae; Staphylococcus aureus; Streptococcus pneumoniae; Enterobacterales; carbapenem-resistant bacteria; CP-CRE; foodborne pathogens; foodborne illness; hospital-acquired infections; bacterial pathogens; fungal pathogens; zoonotic bacteria; antimicrobial resistance; AMR; antibiotic resistance; antibiotic resistance genes; resistance genes; virulence genes; stress response genes; antibiograms; Isolates Browser; MicroBIGG-E; MicroBIGG-E Map; AST Browser; Antibiotic Susceptibility Test; AMRFinderPlus; AMRFinder; Reference Gene Catalog; SNP clusters; PDS accession; PDT accession; PDG accession; Newick; ASN.1; TSV; FASTA; FTP download; Google Cloud; BigQuery; SQL; BLAST; HMM; whole genome sequencing; WGS; genomic epidemiology; phylogenetics; SNP analysis; outbreak detection; foodborne outbreak; traceback; food safety; source attribution; cluster analysis; molecular surveillance; comparative genomics; One Health; antimicrobial susceptibility testing; environmental isolates; United States; global; international; multistate outbreaks; Disease Surveillance; Infectious Disease Monitoring; Genomics; Public Health; Animal Health; Agriculture; Historic; Current; Present; 2013-2026; daily updates; real-time analysis</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>NCBI Pathogen Detection is a centralized surveillance system from the National Library of Medicine that integrates bacterial and fungal pathogen genomes submitted by public health and regulatory laboratories worldwide, including the CDC, FDA, and USDA. Its automated pipeline clusters newly submitted sequences with the more than 2.5 million isolates already archived - results update approximately daily - revealing potential transmission chains behind foodborne, hospital-acquired, and zoonotic outbreaks. Each isolate is screened for antimicrobial resistance, stress response, and virulence genes with AMRFinderPlus. Because isolates span patients, foods, food animals (via USDA and NARMS surveillance), and environmental sources such as water and production facilities, the system is a working example of One Health surveillance at global scale.
+#### Host Organization
+- National Center for Biotechnology Information (NCBI), National Library of Medicine, National Institutes of Health
+#### Data Format
+- Web query interfaces: **Isolates Browser**, **MicroBIGG-E** (AMR/virulence gene browser), and **AST Browser**
+- Bulk **FTP** results (SNP trees in Newick/ASN.1, metadata tables in TSV); daily-updated tables in **Google Cloud BigQuery**
+#### How to access data of interest
+- Open the [NCBI Pathogen Detection home page](https://www.ncbi.nlm.nih.gov/pathogens/) and pick a tool - no account needed
+- Search isolates and SNP clusters in the [Isolates Browser](https://www.ncbi.nlm.nih.gov/pathogens/isolates/), or resistance genes in [MicroBIGG-E](https://www.ncbi.nlm.nih.gov/pathogens/microbigge/)
+- Download per-organism cluster results from the [FTP results area](https://ftp.ncbi.nlm.nih.gov/pathogen/Results/) or query via [BigQuery](https://www.ncbi.nlm.nih.gov/pathogens/docs/microbigge_gcp/)
+#### Database Time Range
+- 2013-2026
+	- The analysis pipeline has operated since 2013; archived isolates carry earlier collection dates
+#### Access Type
+- Public
+#### Citation Information
+- Follow NCBI's [how-to-cite guidance (PDF)](https://www.ncbi.nlm.nih.gov/core/assets/pathogens/files/HowTo/how_to_cite_pathogen_detection.pdf), including PDG/PDT/PDS identifiers for data subsets
+- National Center for Biotechnology Information. "Pathogen Detection." *National Library of Medicine*, September 2026, &lt;https://www.ncbi.nlm.nih.gov/pathogens/&gt;. 2026-09-01
+- See specific source citation details on the database website.</t>
+        </is>
+      </c>
+      <c r="N49" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
       <c r="O49" s="1" t="n"/>
       <c r="P49" s="1" t="n"/>
       <c r="Q49" s="1" t="n"/>
@@ -4723,20 +4979,84 @@
       <c r="AB49" s="2" t="n"/>
     </row>
     <row r="50" ht="14.25" customHeight="1">
-      <c r="A50" s="1" t="n"/>
-      <c r="B50" s="1" t="n"/>
-      <c r="C50" s="1" t="n"/>
-      <c r="D50" s="3" t="n"/>
-      <c r="E50" s="1" t="n"/>
-      <c r="F50" s="1" t="n"/>
-      <c r="G50" s="1" t="n"/>
+      <c r="A50" s="1" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="1" t="inlineStr">
+        <is>
+          <t>USGS Water Data for the Nation</t>
+        </is>
+      </c>
+      <c r="C50" s="1" t="inlineStr">
+        <is>
+          <t>USGS Water Data for the Nation delivers real-time and historical water data from 1M+ US monitoring sites.</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>https://waterdata.usgs.gov/</t>
+        </is>
+      </c>
+      <c r="E50" s="1" t="inlineStr">
+        <is>
+          <t>Ecosystems; People</t>
+        </is>
+      </c>
+      <c r="F50" s="1" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="G50" s="1" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
       <c r="H50" s="1" t="n"/>
-      <c r="I50" s="1" t="n"/>
-      <c r="J50" s="1" t="n"/>
-      <c r="K50" s="3" t="n"/>
-      <c r="L50" s="1" t="n"/>
-      <c r="M50" s="3" t="n"/>
-      <c r="N50" s="1" t="n"/>
+      <c r="I50" s="1" t="n">
+        <v>1889</v>
+      </c>
+      <c r="J50" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>Hydrology; Water Quality; Ecosystem Data; Public Health; Agriculture</t>
+        </is>
+      </c>
+      <c r="L50" s="1" t="inlineStr">
+        <is>
+          <t>USGS; U.S. Geological Survey; United States Geological Survey; Department of the Interior; WDFN; Water Data for the Nation; NWIS; National Water Information System; NWISWeb; Water Resources Mission Area; streamflow; discharge; gage height; stage; river level; river flow; groundwater level; water table; precipitation; water temperature; specific conductance; dissolved oxygen; pH; turbidity; nitrate; sediment; lake level; reservoir storage; coastal conditions; peak flow; daily mean streamflow; water use; field measurements; discrete samples; continuous sensor data; derived statistics; streamgage; stream gauge; streamgaging network; monitoring location; Explore USGS Water Data; National Water Dashboard; WaterAlert; WaterWatch; Groundwater Watch; dataRetrieval; OGC API; STAC; SpatioTemporal Asset Catalog; REST API; JSON; GeoJSON; CSV; RDB; tab-delimited; WaterML; WQX; Water Quality Exchange; pygeoapi; API key; hydrology; surface water; groundwater; water resources; hydrologic monitoring; time series; flood forecasting; flood warning; drought monitoring; water availability; watershed; basin; irrigation; environmental sensing; drinking water sources; United States; US states and territories; nationwide; Embudo New Mexico; Rio Grande; HUC; hydrologic unit; Hydrology; Water Quality; Ecosystem Data; Public Health; Agriculture; Historic; Current; Present; 1889-2026; real-time; 15-minute intervals; instantaneous values; daily values; water year; continuous</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>USGS Water Data for the Nation is the U.S. Geological Survey's portal to its National Water Information System, serving over 135 years of water data from more than one million monitoring locations, including 13,500+ real-time stream, lake, reservoir, precipitation, water-quality, and groundwater stations. Its core strength is continuous and real-time time-series data - streamflow, gage height, groundwater levels, and sensor-based water quality - typically recorded at 15-minute intervals, reaching back to the first USGS streamgage at Embudo, New Mexico in 1889. For discrete water-quality samples pooled from many agencies, use the companion Water Quality Portal entry in this catalog; this portal is the source for USGS's own quantity, real-time, and continuous-sensor records.
+#### Host Organization
+- U.S. Geological Survey (USGS), U.S. Department of the Interior
+#### Data Format
+- Modern **Water Data APIs** (OGC API family and STAC) returning **JSON/GeoJSON**; monitoring-location pages with chart and **CSV** downloads
+- Discrete samples delivered in **WQX** format; the USGS **dataRetrieval** R/Python package wraps all services; free API key optionally raises rate limits
+#### How to access data of interest
+- Search or map monitoring locations at [Explore USGS Water Data](https://waterdata.usgs.gov/explore/)
+- Open a monitoring-location page to view real-time and historical charts and download continuous, daily, field-measurement, or sample data
+- For programmatic access, use the [USGS Water Data APIs](https://api.waterdata.usgs.gov/docs/) or the [dataRetrieval package](https://water.code-pages.usgs.gov/dataRetrieval/)
+#### Database Time Range
+- 1889-2026
+	- USGS streamgaging began at Embudo, New Mexico in January 1889; real-time data flow continuously today
+#### Access Type
+- Public
+#### Citation Information
+- Follow the [USGS citation FAQ](https://help.waterdata.usgs.gov/faq/miscellaneous/how-to-cite-usgs-water-data-for-the-nation-waterdata.usgs.gov-in-a-publication); the stable identifier is DOI 10.5066/F7P55KJN
+- U.S. Geological Survey. "USGS Water Data for the Nation." *National Water Information System*, September 2026, &lt;https://waterdata.usgs.gov/&gt;. 2026-09-01
+- See specific source citation details on the database website.</t>
+        </is>
+      </c>
+      <c r="N50" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
       <c r="O50" s="1" t="n"/>
       <c r="P50" s="1" t="n"/>
       <c r="Q50" s="1" t="n"/>
@@ -4753,20 +5073,84 @@
       <c r="AB50" s="2" t="n"/>
     </row>
     <row r="51" ht="14.25" customHeight="1">
-      <c r="A51" s="1" t="n"/>
-      <c r="B51" s="1" t="n"/>
-      <c r="C51" s="1" t="n"/>
-      <c r="D51" s="3" t="n"/>
-      <c r="E51" s="1" t="n"/>
-      <c r="F51" s="1" t="n"/>
-      <c r="G51" s="1" t="n"/>
+      <c r="A51" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="1" t="inlineStr">
+        <is>
+          <t>National Centers for Environmental Information</t>
+        </is>
+      </c>
+      <c r="C51" s="1" t="inlineStr">
+        <is>
+          <t>NOAA's NCEI archives 30+ petabytes of atmospheric, coastal, oceanic, and geophysical data for global research.</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ncei.noaa.gov/</t>
+        </is>
+      </c>
+      <c r="E51" s="1" t="inlineStr">
+        <is>
+          <t>Ecosystems; People</t>
+        </is>
+      </c>
+      <c r="F51" s="1" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="G51" s="1" t="inlineStr">
+        <is>
+          <t>Global; United States</t>
+        </is>
+      </c>
       <c r="H51" s="1" t="n"/>
-      <c r="I51" s="1" t="n"/>
-      <c r="J51" s="1" t="n"/>
-      <c r="K51" s="3" t="n"/>
-      <c r="L51" s="1" t="n"/>
-      <c r="M51" s="3" t="n"/>
-      <c r="N51" s="1" t="n"/>
+      <c r="I51" s="1" t="n">
+        <v>1763</v>
+      </c>
+      <c r="J51" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>Weather; Long Term Weather Trends; Ocean; Ecosystem Data</t>
+        </is>
+      </c>
+      <c r="L51" s="1" t="inlineStr">
+        <is>
+          <t>NCEI; National Centers for Environmental Information; National Center for Environmental Information; NOAA; National Oceanic and Atmospheric Administration; NESDIS; Department of Commerce; NCDC; National Climatic Data Center; NGDC; National Geophysical Data Center; NODC; National Oceanographic Data Center; World Data Service for Paleoclimatology; atmospheric data; oceanic data; coastal data; geophysical data; climatology; meteorology; oceanography; paleoclimatology; space weather; bathymetry; sea surface temperature; precipitation; snowfall; temperature extremes; climate normals; drought; severe weather; storms; tornado records; hurricanes; marine geology; geomagnetism; solar data; Climate Data Online; CDO; GHCN; Global Historical Climatology Network; GHCNd; GHCNm; Storm Events Database; Storm Data; World Ocean Database; WOD; NOAA OneStop; Severe Weather Data Inventory; NEXRAD; Local Climatological Data; Global Summary of the Month; Global Summary of the Year; US Climate Normals; Daily Weather Records; NetCDF; HDF; CSV; TSV; GeoTIFF; KML; GRIB; BUFR; JSON; ISO 19115; THREDDS; REST API; CDO Web Services API; map services; geoportal; bulk download; climate monitoring; climate research; tree rings; ice cores; corals; lake sediments; proxy records; station observations; buoy observations; radar; satellite data records; weather history; historical weather; Asheville North Carolina; Boulder Colorado; 180 countries; global stations; United States; Weather; Long Term Weather Trends; Ocean; Ecosystem Data; Historic; Current; Present; 1763-2026; 18th century; paleoclimate; continuously updated</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>NOAA's National Centers for Environmental Information (NCEI) maintains one of the most significant environmental archives on Earth - more than 30 petabytes of atmospheric, coastal, oceanic, and geophysical data spanning from the depths of the ocean to the surface of the sun. Formed in 2015 from NOAA's three legacy data centers, NCEI hosts flagship resources including Climate Data Online, the Global Historical Climatology Network, the US Storm Events Database, the World Ocean Database (also cataloged separately here), and the World Data Service for Paleoclimatology. Instrumental records reach back to the 1700s, while paleoclimate proxies such as tree rings, ice cores, and sediments extend the record by hundreds to millions of years.
+#### Host Organization
+- National Oceanic and Atmospheric Administration (NOAA), National Environmental Satellite, Data, and Information Service (NESDIS)
+#### Data Format
+- Open archive formats including **NetCDF**, **CSV/TSV**, **GeoTIFF**, **KML**, **GRIB**, and **BUFR**, with ISO 19115 metadata
+- **Climate Data Online** ordering; **CDO Web Services API v2** (JSON; free email-issued token); GIS map services and **THREDDS** for gridded data
+#### How to access data of interest
+- Browse the catalog via [NCEI Access](https://www.ncei.noaa.gov/access) or the [Products index](https://www.ncei.noaa.gov/products)
+- For station weather and climate data, search and order through [Climate Data Online](https://www.ncei.noaa.gov/cdo-web/) (free; downloads delivered by email link)
+- For programmatic access, request a free token and query the [CDO Web Services API](https://www.ncei.noaa.gov/cdo-web/webservices/v2)
+#### Database Time Range
+- 1763-2026
+	- Earliest instrumental series (Global Summary of the Year) begins 1763; paleoclimate holdings extend far earlier and are excluded from this range
+#### Access Type
+- Public
+#### Citation Information
+- Cite individual datasets per their product landing pages (e.g., GHCN's recommended journal reference)
+- National Oceanic and Atmospheric Administration. "National Centers for Environmental Information." *NCEI*, September 2026, &lt;https://www.ncei.noaa.gov/&gt;. 2026-09-01
+- See specific source citation details on the database website.</t>
+        </is>
+      </c>
+      <c r="N51" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
       <c r="O51" s="1" t="n"/>
       <c r="P51" s="1" t="n"/>
       <c r="Q51" s="1" t="n"/>
@@ -4783,20 +5167,84 @@
       <c r="AB51" s="2" t="n"/>
     </row>
     <row r="52" ht="14.25" customHeight="1">
-      <c r="A52" s="1" t="n"/>
-      <c r="B52" s="1" t="n"/>
-      <c r="C52" s="1" t="n"/>
-      <c r="D52" s="3" t="n"/>
-      <c r="E52" s="1" t="n"/>
-      <c r="F52" s="1" t="n"/>
-      <c r="G52" s="1" t="n"/>
+      <c r="A52" s="1" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="1" t="inlineStr">
+        <is>
+          <t>EPA Toxics Release Inventory</t>
+        </is>
+      </c>
+      <c r="C52" s="1" t="inlineStr">
+        <is>
+          <t>EPA's Toxics Release Inventory tracks chemical releases and waste management at 21,000+ US facilities yearly.</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>https://www.epa.gov/toxics-release-inventory-tri-program</t>
+        </is>
+      </c>
+      <c r="E52" s="1" t="inlineStr">
+        <is>
+          <t>People; Ecosystems</t>
+        </is>
+      </c>
+      <c r="F52" s="1" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="G52" s="1" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
       <c r="H52" s="1" t="n"/>
-      <c r="I52" s="1" t="n"/>
-      <c r="J52" s="1" t="n"/>
-      <c r="K52" s="3" t="n"/>
-      <c r="L52" s="1" t="n"/>
-      <c r="M52" s="3" t="n"/>
-      <c r="N52" s="1" t="n"/>
+      <c r="I52" s="1" t="n">
+        <v>1987</v>
+      </c>
+      <c r="J52" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>Air Quality; Water Quality; Public Health; Ecosystem Data</t>
+        </is>
+      </c>
+      <c r="L52" s="1" t="inlineStr">
+        <is>
+          <t>TRI; Toxics Release Inventory; Toxic Release Inventory; TRI Program; EPA; US EPA; U.S. Environmental Protection Agency; United States Environmental Protection Agency; EPCRA; Emergency Planning and Community Right-to-Know Act; Section 313; Pollution Prevention Act; toxic chemicals; toxic releases; chemical releases; PFAS; per- and polyfluoroalkyl substances; dioxins; toxicity equivalents; PBT; persistent bioaccumulative toxic chemicals; lead; mercury; carcinogens; stack emissions; fugitive air emissions; surface water discharges; underground injection; landfill disposal; off-site transfers; chemical waste; releases to air water land; pollution; toxics; contamination; TRI Explorer; TRI Toxics Tracker; TRI Toolbox; Envirofacts; Form R; Form A; TRI National Analysis; RSEI; Risk-Screening Environmental Indicators; EasyRSEI; ECHO; community right-to-know; pollution prevention; source reduction; waste management; recycling; energy recovery; environmental justice; risk screening; exposure assessment; emissions inventory; environmental reporting; industrial facilities; federal facilities; manufacturing; metal mining; electric power generation; hazardous waste treatment; CSV; tab-delimited; ZIP; XLSX; JSON; XML; Parquet; RESTful API; Envirofacts Data Service API; bulk download; Basic Data Files; Basic Plus Data Files; United States; US states; territories; Puerto Rico; tribal lands; county-level; ZIP code; facility-level; geocoded; Air Quality; Water Quality; Public Health; Ecosystem Data; Historic; Current; Present; 1987-2025; annual; calendar year; reporting year; updated annually</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>The Toxics Release Inventory (TRI) was established by the Emergency Planning and Community Right-to-Know Act of 1986, with facility reporting beginning for calendar year 1987. More than 21,000 US industrial and federal facilities annually report their releases of 800+ listed chemicals and chemical categories to air, water, and land, along with recycling, energy recovery, treatment, and pollution-prevention activities. TRI is a cornerstone of community right-to-know and environmental-justice research, linking industrial activity to potential human and ecosystem exposure. This entry covers the TRI program database specifically; it is also discoverable through the EPA Enterprise Data Catalog listed in this catalog.
+#### Host Organization
+- United States Environmental Protection Agency (U.S. EPA)
+#### Data Format
+- **CSV** Basic Data Files (100 most-used fields, per state or nationwide) and **tab-delimited** Basic Plus files (complete forms), 1987-present
+- **Envirofacts Data Service API** (JSON, CSV, Excel, XML, Parquet; no key required) plus web tools: TRI Explorer, TRI Toxics Tracker, EasyRSEI
+#### How to access data of interest
+- Start at the [TRI Program homepage](https://www.epa.gov/toxics-release-inventory-tri-program) and open the [TRI Toolbox](https://www.epa.gov/toxics-release-inventory-tri-program/tri-toolbox) to pick a query tool
+- For bulk analysis, download [TRI Basic Data Files](https://www.epa.gov/toxics-release-inventory-tri-program/tri-basic-data-files-calendar-years-1987-present)
+- For programmatic access, query TRI tables via the [Envirofacts Data Service API](https://www.epa.gov/enviro/envirofacts-data-service-api)
+#### Database Time Range
+- 1987-2025
+	- Complete data through reporting year 2024; preliminary 2025 data arrives July-October 2026
+#### Access Type
+- Public
+#### Citation Information
+- EPA publishes data-use guidance in [Factors to Consider When Using TRI Data](https://www.epa.gov/toxics-release-inventory-tri-program/factors-consider-when-using-toxics-release-inventory-data)
+- U.S. Environmental Protection Agency. "Toxics Release Inventory (TRI) Program." *US EPA*, September 2026, &lt;https://www.epa.gov/toxics-release-inventory-tri-program&gt;. 2026-09-01
+- See specific source citation details on the database website.</t>
+        </is>
+      </c>
+      <c r="N52" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
       <c r="O52" s="1" t="n"/>
       <c r="P52" s="1" t="n"/>
       <c r="Q52" s="1" t="n"/>
@@ -4813,20 +5261,84 @@
       <c r="AB52" s="2" t="n"/>
     </row>
     <row r="53" ht="14.25" customHeight="1">
-      <c r="A53" s="1" t="n"/>
-      <c r="B53" s="1" t="n"/>
-      <c r="C53" s="1" t="n"/>
-      <c r="D53" s="3" t="n"/>
-      <c r="E53" s="1" t="n"/>
-      <c r="F53" s="1" t="n"/>
-      <c r="G53" s="1" t="n"/>
+      <c r="A53" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="1" t="inlineStr">
+        <is>
+          <t>Global Health Data Exchange</t>
+        </is>
+      </c>
+      <c r="C53" s="1" t="inlineStr">
+        <is>
+          <t>IHME's Global Health Data Exchange catalogs worldwide surveys, censuses, vital statistics, and GBD results.</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>https://ghdx.healthdata.org/</t>
+        </is>
+      </c>
+      <c r="E53" s="1" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+      <c r="F53" s="1" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="G53" s="1" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
       <c r="H53" s="1" t="n"/>
-      <c r="I53" s="1" t="n"/>
-      <c r="J53" s="1" t="n"/>
-      <c r="K53" s="3" t="n"/>
-      <c r="L53" s="1" t="n"/>
-      <c r="M53" s="3" t="n"/>
-      <c r="N53" s="1" t="n"/>
+      <c r="I53" s="1" t="n">
+        <v>1749</v>
+      </c>
+      <c r="J53" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>Population Health; Public Health; Demography; Disease Surveillance; Infectious Disease Monitoring</t>
+        </is>
+      </c>
+      <c r="L53" s="1" t="inlineStr">
+        <is>
+          <t>GHDx; Global Health Data Exchange; IHME; Institute for Health Metrics and Evaluation; University of Washington; healthdata.org; GBD; Global Burden of Disease; GBD Collaborators; DALYs; disability-adjusted life years; YLLs; years of life lost; YLDs; years lived with disability; HALE; healthy life expectancy; mortality; morbidity; cause of death; prevalence; incidence; life expectancy; risk factors; disability weights; comparative risk assessment; SDG health indicators; noncommunicable diseases; injuries; maternal and child health; under-5 mortality; child mortality; smoking; air pollution exposure; malnutrition; cancer burden; COVID-19; census; censuses; vital registration; vital statistics; birth records; death records; household survey; DHS; demographic surveillance; disease registry; epi surveillance; epidemiological surveillance; administrative data; environmental monitoring; geospatial data; GBD Results Tool; GBD Compare; GBD Foresight; GBD Sources Tool; US Health Map; country profiles; CSV; ZIP; codebook; health metrics; epidemiology; demography; population health science; burden of disease; health economics; forecasting; modeled estimates; systematic analysis; global health; global; 204 countries and territories; subnational; US counties; low- and middle-income countries; WHO regions; Population Health; Public Health; Demography; Disease Surveillance; Infectious Disease Monitoring; Historic; Current; Present; 1749-2026; 1990 baseline; GBD 2023; annual updates</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>The Global Health Data Exchange (GHDx) is the data catalog of the Institute for Health Metrics and Evaluation (IHME) at the University of Washington, and the access point for results of the Global Burden of Disease (GBD) study. It indexes surveys, censuses, vital statistics, disease registries, surveillance systems, and environmental monitoring data from around the world - with documented holdings reaching back to 1749 - alongside IHME's own downloadable estimates for 204 countries and territories from 1990 through GBD 2023. Catalog searching is open to all; downloading data files requires a free account under IHME's non-commercial user agreement, and many records route to the original data providers.
+#### Host Organization
+- Institute for Health Metrics and Evaluation (IHME), University of Washington
+#### Data Format
+- **CSV** exports from the GBD Results tool, with codebook and values files in **ZIP**
+- Catalog records with standardized metadata; files download from the record's Files tab or via provider links for third-party datasets
+#### How to access data of interest
+- Search the catalog at [ghdx.healthdata.org](https://ghdx.healthdata.org/) by keyword, location, data type, and year
+- For GBD estimates (deaths, DALYs, prevalence, risks), query the [GBD Results tool](https://vizhub.healthdata.org/gbd-results/), register a free account when prompted, and export CSV
+- For third-party datasets (censuses, surveys, vital statistics), follow the record's provider link to the original source
+#### Database Time Range
+- 1749-2026
+	- Earliest verified holding begins 1749 (Human Mortality Database); GBD estimates cover 1990-2023 with forecasts to 2050
+#### Access Type
+- Free Registration
+#### Citation Information
+- Follow the guidance at [About Suggested Citations](https://ghdx.healthdata.org/about-ghdx/suggested-citations), including an access date and the record's permanent identifier
+- Institute for Health Metrics and Evaluation (IHME). "Global Health Data Exchange (GHDx)." *GHDx*, September 2026, &lt;https://ghdx.healthdata.org/&gt;. 2026-09-01
+- See specific source citation details on the database website.</t>
+        </is>
+      </c>
+      <c r="N53" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
       <c r="O53" s="1" t="n"/>
       <c r="P53" s="1" t="n"/>
       <c r="Q53" s="1" t="n"/>

--- a/datasets.xlsx
+++ b/datasets.xlsx
@@ -2349,12 +2349,12 @@
       </c>
       <c r="K20" s="28" t="inlineStr">
         <is>
-          <t>Agriculture; Land Management; Animal Health</t>
+          <t>Agriculture; Land Management; Animal Health; Livestock</t>
         </is>
       </c>
       <c r="L20" s="15" t="inlineStr">
         <is>
-          <t>Agriculture; Food Production; Census of Agriculture; USDA NASS; Agricultural Statistics; 2022 Census; 2017 Census; Historical Census Data; National Data; State Data; County Data; ZIP Code Data; Congressional District Data; Watershed Data; American Indian Reservation Data; Farm Operations; Farm Demographics; Farm Economics; Farm Production Practices; Market Value of Products; Net Farm Income; Government Payments; Total Land in Farms; Land Use; Irrigated Land; Organic Agriculture; Specialty Crops; Aquaculture; Beginning Farmers; Young Farmers; Internet Access on Farms; Farm Labor; Hired Workers; Operator Characteristics; Livestock Inventory; Crop Acreage; Commodities Grown; Value of Sales; Conservation Practices; Energy Generation on Farms; Computer and Internet Use; Ag Census Web Maps; Interactive Data Tools; Quick Stats Database; Quick Stats Lite; Ag Census API; Data Tables; Full Reports; State Reports; County Reports; Congressional Reports; ZIP Code Reports; Watershed Reports; Highlights; Infographics; Methodology; Survey Forms; Response Rates; Data Quality; Confidentiality; Legal Authority; Title 7 Compliance; CIPSEA Compliance; Partner Resources; Ag Census News; Data Visualization; Downloadable Datasets; PDF Reports; CSV Files; Ag Atlas Maps; Historic; 2022; Farm Size; Crop Yields; Agricultural Inputs; Soil Health; Pest Management; Farm Equipment; Agricultural Innovation; Agricultural Policy; Subsidies; Farm Credit; Agricultural Extension Services; Rural Development; Food Security; Agricultural Exports; Crop Insurance; Agricultural Labor Force; Seasonal Workers; Farm Safety; Agricultural Research; Climate Impact on Agriculture; Sustainable Farming; Precision Agriculture; Farm Technology Adoption; Water Use Efficiency; Agricultural Cooperatives; Commodity Prices; Agricultural Trade; Farm Succession; Land Tenure; Agricultural Education; Farm Income Diversification; Organic Certification; Agroforestry; Agricultural Emissions; Carbon Sequestration in Agriculture; Crop Rotation; Soil Erosion; Farm Mechanization; Agricultural Biodiversity; Irrigation Systems; Agricultural Marketing; Farm Profitability; Agricultural Loans; Rural Infrastructure; Agricultural Census Data Access; Farm Mapping Tools; Agricultural Demographics Trends; Agricultural Supply Chain; Farm-to-Table; Agricultural Productivity; Agricultural Workforce Demographics; Agricultural Land Cover; Crop Disease Management; Agricultural Data Integration; Farm Operation Types; Agricultural Workforce Training; Historic; Current; 1840 - 2023</t>
+          <t>Agriculture; Food Production; Census of Agriculture; USDA NASS; Agricultural Statistics; 2022 Census; 2017 Census; Historical Census Data; National Data; State Data; County Data; ZIP Code Data; Congressional District Data; Watershed Data; American Indian Reservation Data; Farm Operations; Farm Demographics; Farm Economics; Farm Production Practices; Market Value of Products; Net Farm Income; Government Payments; Total Land in Farms; Land Use; Irrigated Land; Organic Agriculture; Specialty Crops; Aquaculture; Beginning Farmers; Young Farmers; Internet Access on Farms; Farm Labor; Hired Workers; Operator Characteristics; Livestock Inventory; Crop Acreage; Commodities Grown; Value of Sales; Conservation Practices; Energy Generation on Farms; Computer and Internet Use; Ag Census Web Maps; Interactive Data Tools; Quick Stats Database; Quick Stats Lite; Ag Census API; Data Tables; Full Reports; State Reports; County Reports; Congressional Reports; ZIP Code Reports; Watershed Reports; Highlights; Infographics; Methodology; Survey Forms; Response Rates; Data Quality; Confidentiality; Legal Authority; Title 7 Compliance; CIPSEA Compliance; Partner Resources; Ag Census News; Data Visualization; Downloadable Datasets; PDF Reports; CSV Files; Ag Atlas Maps; Historic; 2022; Farm Size; Crop Yields; Agricultural Inputs; Soil Health; Pest Management; Farm Equipment; Agricultural Innovation; Agricultural Policy; Subsidies; Farm Credit; Agricultural Extension Services; Rural Development; Food Security; Agricultural Exports; Crop Insurance; Agricultural Labor Force; Seasonal Workers; Farm Safety; Agricultural Research; Climate Impact on Agriculture; Sustainable Farming; Precision Agriculture; Farm Technology Adoption; Water Use Efficiency; Agricultural Cooperatives; Commodity Prices; Agricultural Trade; Farm Succession; Land Tenure; Agricultural Education; Farm Income Diversification; Organic Certification; Agroforestry; Agricultural Emissions; Carbon Sequestration in Agriculture; Crop Rotation; Soil Erosion; Farm Mechanization; Agricultural Biodiversity; Irrigation Systems; Agricultural Marketing; Farm Profitability; Agricultural Loans; Rural Infrastructure; Agricultural Census Data Access; Farm Mapping Tools; Agricultural Demographics Trends; Agricultural Supply Chain; Farm-to-Table; Agricultural Productivity; Agricultural Workforce Demographics; Agricultural Land Cover; Crop Disease Management; Agricultural Data Integration; Farm Operation Types; Agricultural Workforce Training; Historic; Current; 1840 - 2023; Livestock</t>
         </is>
       </c>
       <c r="M20" s="16" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="L46" s="1" t="inlineStr">
         <is>
-          <t>NASA; Earthdata; NASA Earthdata; EarthData; EOSDIS; Earth Observing System Data and Information System; ESDIS; ESDS; Earth Science Data Systems; DAAC; Distributed Active Archive Center; GES DISC; LP DAAC; NSIDC DAAC; OB.DAAC; Ocean Biology DAAC; ORNL DAAC; PO.DAAC; Physical Oceanography DAAC; SEDAC; Socioeconomic Data and Applications Center; ASF DAAC; Alaska Satellite Facility; GHRC; LAADS DAAC; Goddard Space Flight Center; Earth observation; satellite imagery; satellite data; remote sensing; aerosols; air temperature; precipitation; global precipitation; solar irradiance; radiation budget; sea surface temperature; ocean color; chlorophyll; sea level; sea ice; snow cover; cryosphere; glaciers; soil moisture; land cover; land use; vegetation index; NDVI; evapotranspiration; wildfire detection; thermal anomalies; aerosol optical depth; nitrogen dioxide; greenhouse gases; carbon dioxide; methane; hydrology; biodiversity; ecological dynamics; population density; socioeconomic indicators; environmental health; vector-borne disease environments; Earthdata Search; Worldview; GIBS; Giovanni; LANCE; FIRMS; AppEEARS; Earthdata Login; Common Metadata Repository; CMR; Harmony; earthaccess; Earthdata Cloud; Data Pathfinders; Health and Air Quality Data Pathfinder; Diseases Data Pathfinder; HDF; HDF5; HDF-EOS; netCDF; GeoTIFF; Cloud Optimized GeoTIFF; OPeNDAP; CSV; shapefile; REST API; WMTS; Python; R; geospatial analysis; GIS; Earth system science; climate science; climate modeling; time-series analysis; environmental epidemiology; near real-time; open data; global; polar regions; Arctic; Antarctica; oceans; Ecosystem Data; Air Quality; Ocean; Long Term Weather Trends; Public Health; Historic; Current; Present; 1950-2026; Nimbus; satellite era; multi-decadal; daily; ongoing</t>
+          <t>NASA; Earthdata; NASA Earthdata; EarthData; EOSDIS; Earth Observing System Data and Information System; ESDIS; ESDS; Earth Science Data Systems; DAAC; Distributed Active Archive Center; GES DISC; LP DAAC; NSIDC DAAC; OB.DAAC; Ocean Biology DAAC; ORNL DAAC; PO.DAAC; Physical Oceanography DAAC; SEDAC; Socioeconomic Data and Applications Center; ASF DAAC; Alaska Satellite Facility; GHRC; LAADS DAAC; Goddard Space Flight Center; Earth observation; satellite imagery; satellite data; remote sensing; aerosols; air temperature; precipitation; global precipitation; solar irradiance; radiation budget; sea surface temperature; ocean color; chlorophyll; sea level; sea ice; snow cover; cryosphere; glaciers; soil moisture; land cover; land use; vegetation index; NDVI; evapotranspiration; wildfire detection; thermal anomalies; aerosol optical depth; nitrogen dioxide; greenhouse gases; carbon dioxide; methane; hydrology; biodiversity; ecological dynamics; population density; socioeconomic indicators; environmental health; vector-borne disease environments; Earthdata Search; Worldview; GIBS; Giovanni; LANCE; FIRMS; AppEEARS; Earthdata Login; Common Metadata Repository; CMR; Harmony; earthaccess; Earthdata Cloud; Data Pathfinders; Health and Air Quality Data Pathfinder; Diseases Data Pathfinder; HDF; HDF5; HDF-EOS; netCDF; GeoTIFF; Cloud Optimized GeoTIFF; OPeNDAP; CSV; shapefile; REST API; WMTS; Python; R; geospatial analysis; GIS; Earth system science; climate science; climate modeling; time-series analysis; environmental epidemiology; near real-time; open data; global; polar regions; Arctic; Antarctica; oceans; Ecosystem Data; Air Quality; Ocean; Long Term Weather Trends; Public Health; Historic; Current; Present; 1950-2026; Nimbus; satellite era; multi-decadal; daily; ongoing; MODIS; Moderate Resolution Imaging Spectroradiometer; Terra; Aqua; VIIRS; EVI; land surface temperature; active fire; burned area</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
@@ -5355,20 +5355,85 @@
       <c r="AB53" s="2" t="n"/>
     </row>
     <row r="54" ht="14.25" customHeight="1">
-      <c r="A54" s="1" t="n"/>
-      <c r="B54" s="1" t="n"/>
-      <c r="C54" s="1" t="n"/>
-      <c r="D54" s="3" t="n"/>
-      <c r="E54" s="1" t="n"/>
-      <c r="F54" s="1" t="n"/>
-      <c r="G54" s="1" t="n"/>
+      <c r="A54" s="1" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="1" t="inlineStr">
+        <is>
+          <t>World Bank Data Catalog</t>
+        </is>
+      </c>
+      <c r="C54" s="1" t="inlineStr">
+        <is>
+          <t>World Bank Data Catalog curates 7,800+ open datasets, from 1,400 WDI indicators to health microdata, since 1960.</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>https://datacatalog.worldbank.org/</t>
+        </is>
+      </c>
+      <c r="E54" s="1" t="inlineStr">
+        <is>
+          <t>People; Ecosystems</t>
+        </is>
+      </c>
+      <c r="F54" s="1" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="G54" s="1" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
       <c r="H54" s="1" t="n"/>
-      <c r="I54" s="1" t="n"/>
-      <c r="J54" s="1" t="n"/>
-      <c r="K54" s="3" t="n"/>
-      <c r="L54" s="1" t="n"/>
-      <c r="M54" s="3" t="n"/>
-      <c r="N54" s="1" t="n"/>
+      <c r="I54" s="1" t="n">
+        <v>1960</v>
+      </c>
+      <c r="J54" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>Demography; Population Health; Public Health; Agriculture; Ecosystem Data; Energy</t>
+        </is>
+      </c>
+      <c r="L54" s="1" t="inlineStr">
+        <is>
+          <t>World Bank; The World Bank Group; WBG; World Bank Data Catalog; World Bank Open Data; IBRD; International Bank for Reconstruction and Development; IDA; International Development Association; Development Data Group; DECDG; poverty; inequality; population dynamics; fertility; life expectancy; health; nutrition; education; labor; gender; agriculture; rural development; climate change; environment; biodiversity; water; sanitation; energy; mining; economy; GDP; trade; external debt; aid; migration; refugees; tourism; urban development; infrastructure; social protection; food security; development data; development indicators; World Development Indicators; WDI; DataBank; Microdata Library; Central Microdata Catalog; Data360; Development Data Hub; DDH; International Debt Statistics; Global Economic Monitor; Human Capital Index; EnergyData.info; Gender Data Portal; Enterprise Surveys; LSMS; Living Standards Measurement Study; household surveys; CSV; Excel; XLSX; ZIP; XML; JSON; JSONP; JSON-stat; REST API; Indicators API; api.worldbank.org; CC BY 4.0; open data; development economics; global health metrics; demography; epidemiology; econometrics; cross-country comparison; national accounts; official statistics; SDG monitoring; SDG indicators; global; 217 economies; country groups; low- and middle-income countries; Sub-Saharan Africa; South Asia; East Asia; Latin America; Middle East; Demography; Population Health; Public Health; Agriculture; Ecosystem Data; Energy; Historic; Current; Present; 1960-2026; annual updates; time series</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>The World Bank Data Catalog is the World Bank Group's one-stop discovery layer for its open development data, indexing roughly 7,900 datasets that range from the flagship World Development Indicators - about 1,400 curated time series for 217 economies reaching back to 1960 - to household survey microdata, debt statistics, and energy and geospatial collections. Nearly all headline datasets carry a CC BY 4.0 license and can be downloaded as CSV/Excel or queried through a free, keyless REST API. For One Health work, it pairs population, health, and nutrition indicators with environment, climate, agriculture, and water data in one internationally comparable frame.
+#### Host Organization
+- The World Bank Group (Development Data Group)
+#### Data Format
+- **CSV** and **Excel** downloads per dataset (bulk ZIP archives for large collections), plus interactive exploration in DataBank
+- **Indicators API** (REST at api.worldbank.org/v2): XML, JSON, JSON-stat; no key required
+#### How to access data of interest
+- Search or filter datasets at the [World Bank Data Catalog](https://datacatalog.worldbank.org/) by topic, license, and format
+- Open a dataset page - e.g., [World Development Indicators](https://datacatalog.worldbank.org/search/dataset/0037712/World-Development-Indicators) - and download CSV/Excel, no account needed
+- Browse indicators visually at [World Bank Open Data](https://data.worldbank.org/) or query the keyless [Indicators API](https://datahelpdesk.worldbank.org/knowledgebase/articles/889392-about-the-indicators-api-documentation)
+- Household/health survey microdata routes through the [Microdata Library](https://microdata.worldbank.org/); public-use files need free registration
+#### Database Time Range
+- 1960-2026
+	- WDI series begin in 1960; individual cataloged datasets vary
+#### Access Type
+- Public
+#### Citation Information
+- Data are CC BY 4.0; attribution format per the [Summary Terms of Use](https://data.worldbank.org/summary-terms-of-use)
+- The World Bank Group. "World Bank Data Catalog." *World Bank Data Catalog*, September 2026, &lt;https://datacatalog.worldbank.org/&gt;. 2026-09-02
+- See specific source citation details on the database website.</t>
+        </is>
+      </c>
+      <c r="N54" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
       <c r="O54" s="1" t="n"/>
       <c r="P54" s="1" t="n"/>
       <c r="Q54" s="1" t="n"/>
@@ -5385,20 +5450,85 @@
       <c r="AB54" s="2" t="n"/>
     </row>
     <row r="55" ht="14.25" customHeight="1">
-      <c r="A55" s="1" t="n"/>
-      <c r="B55" s="1" t="n"/>
-      <c r="C55" s="1" t="n"/>
-      <c r="D55" s="3" t="n"/>
-      <c r="E55" s="1" t="n"/>
-      <c r="F55" s="1" t="n"/>
-      <c r="G55" s="1" t="n"/>
+      <c r="A55" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="1" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas of Infectious Diseases</t>
+        </is>
+      </c>
+      <c r="C55" s="1" t="inlineStr">
+        <is>
+          <t>Surveillance Atlas of Infectious Diseases maps EU/EEA notifiable disease data with interactive views and CSV export.</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx</t>
+        </is>
+      </c>
+      <c r="E55" s="1" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+      <c r="F55" s="1" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="G55" s="1" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
       <c r="H55" s="1" t="n"/>
-      <c r="I55" s="1" t="n"/>
-      <c r="J55" s="1" t="n"/>
-      <c r="K55" s="3" t="n"/>
-      <c r="L55" s="1" t="n"/>
-      <c r="M55" s="3" t="n"/>
-      <c r="N55" s="1" t="n"/>
+      <c r="I55" s="1" t="n">
+        <v>1999</v>
+      </c>
+      <c r="J55" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>Disease Surveillance; Infectious Disease Monitoring; Public Health; Population Health</t>
+        </is>
+      </c>
+      <c r="L55" s="1" t="inlineStr">
+        <is>
+          <t>ECDC; European Centre for Disease Prevention and Control; Surveillance Atlas; Surveillance Atlas of Infectious Diseases; European Union; EU; EEA; European Economic Area; Europe; European surveillance; TESSy; The European Surveillance System; EpiPulse; EARS-Net; antimicrobial resistance; AMR; MRSA; Annual Epidemiological Report; notifiable diseases; measles; rubella; pertussis; whooping cough; diphtheria; tetanus; meningococcal disease; pneumococcal disease; Haemophilus influenzae; tuberculosis; TB; HIV; AIDS; syphilis; gonorrhoea; chlamydia; hepatitis A; hepatitis B; hepatitis C; salmonellosis; Salmonella; campylobacteriosis; Campylobacter; listeriosis; Listeria; shigellosis; STEC; VTEC; E. coli; yersiniosis; cholera; typhoid; botulism; anthrax; brucellosis; echinococcosis; trichinellosis; tularaemia; Q fever; leptospirosis; rabies; hantavirus; West Nile virus; tick-borne encephalitis; Lyme neuroborreliosis; malaria; dengue; chikungunya; Zika; legionellosis; Legionnaires disease; cryptosporidiosis; giardiasis; influenza; RSV; COVID-19; zoonoses; zoonotic disease; vector-borne disease; vaccine-preventable disease; foodborne disease; waterborne disease; case counts; notification rates; incidence; epidemiology; infectious disease epidemiology; case-based surveillance; outbreak monitoring; CSV; CSV export; permalink; embed; InstantAtlas; Austria; Belgium; France; Germany; Italy; Netherlands; Poland; Spain; Sweden; Norway; Iceland; Liechtenstein; Stockholm; Disease Surveillance; Infectious Disease Monitoring; Public Health; Population Health; Historic; Current; Present; 1999-2026; annual; latest validated year</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>The Surveillance Atlas of Infectious Diseases is the European Centre for Disease Prevention and Control's public window onto The European Surveillance System (TESSy), through which all EU Member States plus Iceland, Liechtenstein, and Norway report notifiable-disease data. Users can map and chart reported cases and notification rates for dozens of diseases - from vaccine-preventable and food- and waterborne infections to zoonotic, vector-borne, and antimicrobial-resistance topics - filtered by country, year, age, and sex. It is the European counterpart to this catalog's US-focused human surveillance sources such as the National Notifiable Diseases Surveillance System.
+#### Host Organization
+- European Centre for Disease Prevention and Control (ECDC), an agency of the European Union
+#### Data Format
+- Interactive maps, tables, and charts in-browser; every view exportable as **CSV**, image capture, embed code, or a shareable permalink
+- No public API; data beyond the Atlas aggregates can be requested from ECDC
+#### How to access data of interest
+- Open the [Surveillance Atlas](https://atlas.ecdc.europa.eu/public/index.aspx) - no account needed
+- Choose a health topic (disease), indicator, and time period, then load the map/table/chart and export as CSV
+- Background and per-disease entry points are on [ECDC's Atlas page](https://www.ecdc.europa.eu/en/surveillance-atlas-infectious-diseases); non-public record-level data goes through [ECDC's third-party access procedure](https://www.ecdc.europa.eu/en/publications-data/access-eueea-surveillance-data-third-parties)
+#### Database Time Range
+- 1999-2026
+	- Coverage depth varies by disease; EU-wide reporting is densest from 2007 onward
+#### Access Type
+- Public
+	- Reuse is permitted with attribution to ECDC and the reporting Member States; data not shown in the Atlas can be requested from ECDC
+#### Citation Information
+- Required attribution: "Data provided by ECDC based on data reported by EU/EEA Member States" (per [ECDC's data access page](https://www.ecdc.europa.eu/en/publications-data/access-eueea-surveillance-data-third-parties))
+- European Centre for Disease Prevention and Control. "Surveillance Atlas of Infectious Diseases." *ECDC*, September 2026, &lt;https://atlas.ecdc.europa.eu/public/index.aspx&gt;. 2026-09-02
+- See specific source citation details on the database website.</t>
+        </is>
+      </c>
+      <c r="N55" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
       <c r="O55" s="1" t="n"/>
       <c r="P55" s="1" t="n"/>
       <c r="Q55" s="1" t="n"/>
@@ -5415,20 +5545,84 @@
       <c r="AB55" s="2" t="n"/>
     </row>
     <row r="56" ht="14.25" customHeight="1">
-      <c r="A56" s="1" t="n"/>
-      <c r="B56" s="1" t="n"/>
-      <c r="C56" s="1" t="n"/>
-      <c r="D56" s="3" t="n"/>
-      <c r="E56" s="1" t="n"/>
-      <c r="F56" s="1" t="n"/>
-      <c r="G56" s="1" t="n"/>
+      <c r="A56" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="1" t="inlineStr">
+        <is>
+          <t>FAOSTAT</t>
+        </is>
+      </c>
+      <c r="C56" s="1" t="inlineStr">
+        <is>
+          <t>FAOSTAT provides free global food and agriculture statistics for 245+ countries and territories since 1961.</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/faostat/en/</t>
+        </is>
+      </c>
+      <c r="E56" s="1" t="inlineStr">
+        <is>
+          <t>People; Animals; Ecosystems</t>
+        </is>
+      </c>
+      <c r="F56" s="1" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="G56" s="1" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
       <c r="H56" s="1" t="n"/>
-      <c r="I56" s="1" t="n"/>
-      <c r="J56" s="1" t="n"/>
-      <c r="K56" s="3" t="n"/>
-      <c r="L56" s="1" t="n"/>
-      <c r="M56" s="3" t="n"/>
-      <c r="N56" s="1" t="n"/>
+      <c r="I56" s="1" t="n">
+        <v>1961</v>
+      </c>
+      <c r="J56" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>Agriculture; Livestock; Land Management; Population Health; Ecosystem Data</t>
+        </is>
+      </c>
+      <c r="L56" s="1" t="inlineStr">
+        <is>
+          <t>FAO; FAOSTAT; Food and Agriculture Organization; Food and Agriculture Organization of the United Nations; UN FAO; United Nations; FAO Statistics Division; crops; livestock; cereals; wheat; maize; rice; fruit; vegetables; pulses; oil crops; sugar crops; livestock products; meat production; dairy; milk; eggs; animal slaughtering; herd size; harvested area; production volume; crop yields; agricultural trade; trade matrix; imports; exports; fertilizers; nitrogen; phosphorus; potassium; pesticides; food supply; food balance sheets; food security; food security indicators; nutrition; dietary intake; diet diversity; undernourishment; greenhouse gas emissions; agrifood systems emissions; enteric fermentation; manure management; land use; irrigation; forestry; forest products; agricultural prices; producer prices; investment; capital stock; population; rural population; employment; Suite of Food Security Indicators; Emissions Totals; Detailed trade matrix; Production Indices; Value of Agricultural Production; MDD-W; FAOSTAT Analytical Briefs; bulk download; CSV; ZIP; normalized CSV; JSON; REST API; API developer portal; machine-readable; CC BY 4.0; agricultural statistics; agri-food systems; food policy; agricultural economics; nutrition surveillance; statistical harmonization; time series; global; worldwide; 245 countries; FAO regions; country-level; Agriculture; Livestock; Land Management; Population Health; Ecosystem Data; Historic; Current; Present; 1961-2026; since 1961; annual; rolling updates</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>FAOSTAT is the Food and Agriculture Organization of the United Nations' flagship statistical database - described by FAO as the world's most comprehensive on food, agriculture, fisheries, forestry, natural resources management and nutrition. It offers free, harmonized annual time series for over 245 countries and territories from 1961 onward, spanning dozens of datasets across production, trade, food balances, food security and nutrition, prices, land use and inputs, agrifood-system emissions, forestry, and investment. For One Health work it uniquely links livestock populations and production, human food security and diet, and land-use and emissions pressures in a single citable global source.
+#### Host Organization
+- Food and Agriculture Organization of the United Nations (FAO)
+#### Data Format
+- Custom web downloads (**CSV**) per domain; whole-domain **bulk ZIP/CSV** files (normalized and pivoted layouts)
+- **FAOSTAT API** returning JSON/CSV via the developer portal (registration); all data licensed **CC BY 4.0**
+#### How to access data of interest
+- Open [FAOSTAT](https://www.fao.org/faostat/en/) and choose a domain under Data (e.g., Production - Crops and livestock products)
+- Filter by country, item, element, and year, then download your selection - no account needed
+- For whole domains, use each domain's bulk download links; for programmatic access, see the [FAOSTAT API portal announcement](https://www.fao.org/statistics/highlights-archive/highlights-detail/faostat-launches-a-new-api-developer-portal-to-make-data-access-easier/en)
+#### Database Time Range
+- 1961-2026
+	- Reference years vary by domain (production series currently through 2024); updates roll out on a monthly release calendar
+#### Access Type
+- Public
+#### Citation Information
+- Follow the [FAO Statistical Database Terms of Use](https://www.fao.org/contact-us/terms/db-terms-of-use): FAO. [Year]. [Database: Dataset]. [Accessed date]. Licence: CC-BY-4.0
+- Food and Agriculture Organization of the United Nations. "FAOSTAT." *FAO*, September 2026, &lt;https://www.fao.org/faostat/en/&gt;. 2026-09-02
+- See specific source citation details on the database website.</t>
+        </is>
+      </c>
+      <c r="N56" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
       <c r="O56" s="1" t="n"/>
       <c r="P56" s="1" t="n"/>
       <c r="Q56" s="1" t="n"/>
@@ -5445,20 +5639,85 @@
       <c r="AB56" s="2" t="n"/>
     </row>
     <row r="57" ht="14.25" customHeight="1">
-      <c r="A57" s="1" t="n"/>
-      <c r="B57" s="1" t="n"/>
-      <c r="C57" s="1" t="n"/>
-      <c r="D57" s="3" t="n"/>
-      <c r="E57" s="1" t="n"/>
-      <c r="F57" s="1" t="n"/>
-      <c r="G57" s="1" t="n"/>
+      <c r="A57" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="1" t="inlineStr">
+        <is>
+          <t>USDA NASS Quick Stats</t>
+        </is>
+      </c>
+      <c r="C57" s="1" t="inlineStr">
+        <is>
+          <t>USDA NASS Quick Stats delivers queryable U.S. agricultural statistics from 1866 on, spanning crops to demographics.</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>https://quickstats.nass.usda.gov/</t>
+        </is>
+      </c>
+      <c r="E57" s="1" t="inlineStr">
+        <is>
+          <t>Animals; People; Ecosystems</t>
+        </is>
+      </c>
+      <c r="F57" s="1" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="G57" s="1" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
       <c r="H57" s="1" t="n"/>
-      <c r="I57" s="1" t="n"/>
-      <c r="J57" s="1" t="n"/>
-      <c r="K57" s="3" t="n"/>
-      <c r="L57" s="1" t="n"/>
-      <c r="M57" s="3" t="n"/>
-      <c r="N57" s="1" t="n"/>
+      <c r="I57" s="1" t="n">
+        <v>1866</v>
+      </c>
+      <c r="J57" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>Agriculture; Livestock; Demography; Land Management</t>
+        </is>
+      </c>
+      <c r="L57" s="1" t="inlineStr">
+        <is>
+          <t>USDA; U.S. Department of Agriculture; United States Department of Agriculture; NASS; National Agricultural Statistics Service; National Agriculture Statistics Service; USDA-NASS; Quick Stats; QuickStats; Quick Stats Lite; Agricultural Statistics Board; corn; wheat; soybeans; cotton; hay; potatoes; barley; sorghum; rice; oats; sunflower; sugarbeets; dry beans; cattle; calves; beef; hogs; pigs; swine; sheep; lambs; goats; poultry; chickens; broilers; turkeys; dairy; milk production; milk cows; eggs; honey; honey bees; bees; aquaculture; crop yield; planted acreage; harvested acreage; crop production; crop progress; crop condition; grain stocks; livestock slaughter; cattle on feed; livestock inventory; agricultural prices; prices received; prices paid; farm labor; farm wages; farm income; production expenses; land values; cash rents; land in farms; farm numbers; farm operations; chemical use; fertilizer use; pesticide use; irrigation; farm operator; producer demographics; farm demographics; Census of Agriculture; county estimates; survey estimates; Cropland Data Layer; CroplandCROS; Quick Stats API; REST API; API key; JSON; XML; CSV; txt.gz; gzip; bulk extracts; spreadsheet export; rnassqs; agricultural statistics; official statistics; agricultural economics; sample surveys; federal statistics; food systems; commodity markets; United States; national; state; county; Agricultural Statistics Districts; Colorado agriculture; Agriculture; Livestock; Demography; Land Management; Historic; Current; Present; 1866-2026; 1850; annual; monthly; weekly; census years 1997-2022; updated each weekday</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>Quick Stats is the query front end to USDA's National Agricultural Statistics Service - official estimates from hundreds of annual sample surveys together with results of the five-year Census of Agriculture (cataloged separately here), all searchable in one system. Data span five sectors (crops, animals and products, economics, demographics, environmental) at national, state, and county levels, with some annual series reaching back to 1866 and census tables back to 1997. Full-sector extracts are refreshed on business days.
+#### Host Organization
+- United States Department of Agriculture, National Agricultural Statistics Service (USDA NASS)
+#### Data Format
+- Interactive web queries with spreadsheet/**CSV** export; whole-sector **compressed text extracts** (.txt.gz) updated on business days (file dates can lag a few days)
+- **Quick Stats API** (REST; free key): CSV, JSON, or XML, up to 50,000 records per request; R/Python client packages available
+#### How to access data of interest
+- Open [Quick Stats](https://quickstats.nass.usda.gov/) and build a query by program (Census/Survey), sector, commodity, geography, and year, then export - or use [Quick Stats Lite](https://www.nass.usda.gov/Quick_Stats/Lite/index.php) for a guided version
+- For bulk data, download sector extract files from the [NASS datasets page](https://www.nass.usda.gov/datasets/)
+- For programmatic access, request a free key for the [Quick Stats API](https://quickstats.nass.usda.gov/api/)
+#### Database Time Range
+- 1866-2026
+	- Continuous annual series begin 1866 (scattered values back to 1850); Census of Agriculture tables cover 1997-2022
+#### Access Type
+- Public
+	- Web queries and bulk downloads need no account; only the API requires a free key
+#### Citation Information
+- NASS asks that "USDA-NASS be given appropriate acknowledgment" per its [Citation Request page](https://www.nass.usda.gov/Data_and_Statistics/Citation_Request/index.php)
+- United States Department of Agriculture, National Agricultural Statistics Service. "Quick Stats." *USDA NASS*, September 2026, &lt;https://quickstats.nass.usda.gov/&gt;. 2026-09-02
+- See specific source citation details on the database website.</t>
+        </is>
+      </c>
+      <c r="N57" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
       <c r="O57" s="1" t="n"/>
       <c r="P57" s="1" t="n"/>
       <c r="Q57" s="1" t="n"/>
@@ -5475,20 +5734,84 @@
       <c r="AB57" s="2" t="n"/>
     </row>
     <row r="58" ht="14.25" customHeight="1">
-      <c r="A58" s="1" t="n"/>
-      <c r="B58" s="1" t="n"/>
-      <c r="C58" s="1" t="n"/>
-      <c r="D58" s="3" t="n"/>
-      <c r="E58" s="1" t="n"/>
-      <c r="F58" s="1" t="n"/>
-      <c r="G58" s="1" t="n"/>
+      <c r="A58" s="1" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="1" t="inlineStr">
+        <is>
+          <t>LANDFIRE</t>
+        </is>
+      </c>
+      <c r="C58" s="1" t="inlineStr">
+        <is>
+          <t>LANDFIRE maps vegetation, fuels, fire regimes, and disturbance across all US lands for fire and resource planning.</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>https://www.landfire.gov/</t>
+        </is>
+      </c>
+      <c r="E58" s="1" t="inlineStr">
+        <is>
+          <t>Ecosystems</t>
+        </is>
+      </c>
+      <c r="F58" s="1" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="G58" s="1" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
       <c r="H58" s="1" t="n"/>
-      <c r="I58" s="1" t="n"/>
-      <c r="J58" s="1" t="n"/>
-      <c r="K58" s="3" t="n"/>
-      <c r="L58" s="1" t="n"/>
-      <c r="M58" s="3" t="n"/>
-      <c r="N58" s="1" t="n"/>
+      <c r="I58" s="1" t="n">
+        <v>1999</v>
+      </c>
+      <c r="J58" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>Wildfire; Ecosystem Data; Land Management; Conservation</t>
+        </is>
+      </c>
+      <c r="L58" s="1" t="inlineStr">
+        <is>
+          <t>LANDFIRE; LF; Landscape Fire and Resource Management Planning Tools; USDA Forest Service; USFS; Forest Service; Fire and Aviation Management; U.S. Department of the Interior; DOI; Office of Wildland Fire; USGS; U.S. Geological Survey; EROS; Earth Resources Observation and Science Center; The Nature Conservancy; TNC; Wildland Fire Leadership Council; wildland fire; wildfire; fire; fuels; surface fuels; canopy fuels; fuel models; fire behavior fuel models; FBFM13; FBFM40; Existing Vegetation Type; EVT; Existing Vegetation Cover; EVC; Existing Vegetation Height; EVH; Biophysical Settings; BpS; vegetation type; vegetation cover; vegetation height; canopy cover; canopy height; canopy base height; canopy bulk density; fire regime; fire regime groups; vegetation condition class; vegetation departure; annual disturbance; disturbance; fuels treatment; prescribed fire; fire behavior modeling; fire ecology; landscape ecology; hazard assessment; habitat modeling; state-and-transition models; vegetation modeling; remote sensing; Landsat; lidar; MTBS; topographic layers; slope; aspect; elevation; LF Map Viewer; Full Extent Downloads; LANDFIRE Products Service; LFPS; REST API; image service; WCS; WMS; OGC services; ArcGIS; GeoTIFF; raster; 30-meter resolution; 30m; zip; XML metadata; LF 2016 Remap; LF 2020; LF 2022; LF 2023; LF 2024; LF 2025; CONUS; conterminous United States; Alaska; Hawaii; Puerto Rico; insular areas; US territories; national coverage; map zones; Wildfire; Ecosystem Data; Land Management; Conservation; Historic; Current; Present; 1999-2026; annual updates; chartered 2004</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>LANDFIRE (Landscape Fire and Resource Management Planning Tools) is a shared interagency program of the USDA Forest Service and the U.S. Department of the Interior, produced with the USGS Earth Resources Observation and Science Center and The Nature Conservancy. It delivers more than 25 consistent 30-meter geospatial layers - vegetation type and structure, surface and canopy fuels, historic fire regimes, and annual disturbance since 1999 - covering all lands of the conterminous United States, Alaska, Hawaii, and the insular areas. The data underpin wildfire behavior modeling, fuels treatment planning, and ecosystem assessment nationwide.
+#### Host Organization
+- USDA Forest Service and U.S. Department of the Interior (with USGS EROS and The Nature Conservancy)
+#### Data Format
+- **GeoTIFF** rasters at 30-m resolution; zipped full-extent regional downloads (CONUS, Alaska, Hawaii, Insular Areas)
+- Streaming via ArcGIS image services, OGC **WCS/WMS**, and the **LANDFIRE Products Service (LFPS) REST API**
+#### How to access data of interest
+- Start at the [LANDFIRE data page](https://landfire.gov/data) to pick a product family (vegetation, fuel, fire regime, disturbance, topographic)
+- For a custom area, open the [LF Map Viewer](https://www.landfire.gov/viewer) and download your area of interest by layer
+- For whole regions and versions, use [Full Extent Downloads](https://landfire.gov/data/FullExtentDownloads); to stream instead, use the [WCS/WMS services](https://www.landfire.gov/data/lf_wcs_wms)
+#### Database Time Range
+- 1999-2026
+	- Annual disturbance layers span 1999-present; base vegetation/fuels versions run from LF National (circa 2001) through LF 2025
+#### Access Type
+- Public
+#### Citation Information
+- Follow the [LANDFIRE citation guidance](https://www.landfire.gov/data/citation); individual layers carry their own version citations
+- U.S. Department of Agriculture Forest Service and U.S. Department of the Interior. "LANDFIRE." *LANDFIRE*, September 2026, &lt;https://www.landfire.gov/&gt;. 2026-09-02
+- See specific source citation details on the database website.</t>
+        </is>
+      </c>
+      <c r="N58" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
       <c r="O58" s="1" t="n"/>
       <c r="P58" s="1" t="n"/>
       <c r="Q58" s="1" t="n"/>
@@ -5505,20 +5828,84 @@
       <c r="AB58" s="2" t="n"/>
     </row>
     <row r="59" ht="14.25" customHeight="1">
-      <c r="A59" s="1" t="n"/>
-      <c r="B59" s="1" t="n"/>
-      <c r="C59" s="1" t="n"/>
-      <c r="D59" s="3" t="n"/>
-      <c r="E59" s="1" t="n"/>
-      <c r="F59" s="1" t="n"/>
-      <c r="G59" s="1" t="n"/>
+      <c r="A59" s="1" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="1" t="inlineStr">
+        <is>
+          <t>Global Forest Watch</t>
+        </is>
+      </c>
+      <c r="C59" s="1" t="inlineStr">
+        <is>
+          <t>Global Forest Watch maps tree cover loss, deforestation alerts, and fires worldwide in near real time.</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>https://globalnaturewatch.org/</t>
+        </is>
+      </c>
+      <c r="E59" s="1" t="inlineStr">
+        <is>
+          <t>Ecosystems</t>
+        </is>
+      </c>
+      <c r="F59" s="1" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="G59" s="1" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
       <c r="H59" s="1" t="n"/>
-      <c r="I59" s="1" t="n"/>
-      <c r="J59" s="1" t="n"/>
-      <c r="K59" s="3" t="n"/>
-      <c r="L59" s="1" t="n"/>
-      <c r="M59" s="3" t="n"/>
-      <c r="N59" s="1" t="n"/>
+      <c r="I59" s="1" t="n">
+        <v>2001</v>
+      </c>
+      <c r="J59" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>Ecosystem Data; Conservation; Land Management; Agriculture</t>
+        </is>
+      </c>
+      <c r="L59" s="1" t="inlineStr">
+        <is>
+          <t>Global Forest Watch; GFW; Global Nature Watch; GNW; World Resources Institute; WRI; University of Maryland; UMD; GLAD; Global Land Analysis and Discovery; forests; forest; deforestation; tree cover; tree cover loss; tree cover gain; tree cover density; forest change; forest monitoring; forest disturbance; forest degradation; primary forest; intact forest landscapes; vegetation loss; land cover; land use; forest carbon; carbon flux; greenhouse gas emissions; biodiversity; fires; active fires; fire alerts; forest fires; wildfire; protected areas; mangroves; plantations; commodity-driven deforestation; grasslands; trees outside forests; GLAD alerts; GLAD-L; GLAD-S2; RADD; DIST-ALERT; integrated deforestation alerts; VIIRS; NASA FIRMS; Open Data Portal; GFW Data API; MapBuilder; Forest Watcher; myGFW; myGNW; dashboards; Global Forest Review; interactive map; GeoJSON; Shapefile; ZIP; CSV; KML; ArcGIS; REST API; JSON; remote sensing; satellite monitoring; Earth observation; near-real-time monitoring; change detection; Landsat; Sentinel-1; Sentinel-2; radar; SAR; 30-meter resolution; canopy cover; Hansen; global; pantropical; tropics; Amazon; Congo Basin; Southeast Asia; Brazil; country dashboards; Ecosystem Data; Conservation; Land Management; Agriculture; Historic; Current; Present; 2001-2026; 2000 baseline; annual updates; weekly alerts; daily updates; near real time; rebranded 2026</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>Global Forest Watch - rebranded Global Nature Watch in mid-2026, with globalforestwatch.org now redirecting there - is the World Resources Institute's free online platform for monitoring the world's forests in near real time. It combines annual tree cover loss data (2001-present, against a 2000 tree-cover baseline) produced by the University of Maryland's GLAD laboratory with daily-updated deforestation and disturbance alerts (GLAD, RADD, and DIST-ALERT) and NASA VIIRS fire alerts. Users can analyze change on an interactive map and country dashboards, download 65+ datasets in GIS-ready formats, or query the Data API; most GFW-produced datasets are CC BY 4.0, though partner datasets carry their own licenses.
+#### Host Organization
+- World Resources Institute (WRI), with data partners including the University of Maryland GLAD lab, Google, and Esri
+#### Data Format
+- Interactive map and country dashboards in-browser
+- Downloads via the [Open Data Portal](https://data.globalforestwatch.org/): **Shapefile (ZIP), GeoJSON, CSV, KML**, and ArcGIS GeoServices; programmatic access via the **GFW Data API** (REST/JSON)
+#### How to access data of interest
+- Explore tree cover loss, deforestation alerts, and fires on the [interactive map](https://www.globalforestwatch.org/map/)
+- View country and custom-area statistics in the dashboards from the [homepage](https://globalnaturewatch.org/)
+- Download datasets from the [Open Data Portal](https://data.globalforestwatch.org/) or query the [GFW Data API](https://data-api.globalforestwatch.org/); a free account adds saved areas and alert subscriptions
+#### Database Time Range
+- 2001-2026
+	- Annual tree cover loss from 2001 (2000 baseline); disturbance and fire alerts update daily
+#### Access Type
+- Public
+#### Citation Information
+- Cite the platform and the specific dataset (each carries its own citation in the Data API metadata, e.g., Hansen et al. 2013 for tree cover loss)
+- World Resources Institute. "Global Forest Watch." *Global Forest Watch*, September 2026, &lt;https://www.globalforestwatch.org/&gt;. 2026-09-02
+- See specific source citation details on the database website.</t>
+        </is>
+      </c>
+      <c r="N59" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
       <c r="O59" s="1" t="n"/>
       <c r="P59" s="1" t="n"/>
       <c r="Q59" s="1" t="n"/>
@@ -5535,20 +5922,85 @@
       <c r="AB59" s="2" t="n"/>
     </row>
     <row r="60" ht="14.25" customHeight="1">
-      <c r="A60" s="1" t="n"/>
-      <c r="B60" s="1" t="n"/>
-      <c r="C60" s="1" t="n"/>
-      <c r="D60" s="3" t="n"/>
-      <c r="E60" s="1" t="n"/>
-      <c r="F60" s="1" t="n"/>
-      <c r="G60" s="1" t="n"/>
+      <c r="A60" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="1" t="inlineStr">
+        <is>
+          <t>OpenTopography</t>
+        </is>
+      </c>
+      <c r="C60" s="1" t="inlineStr">
+        <is>
+          <t>OpenTopography delivers high-resolution lidar point clouds, DEMs, and global elevation data for Earth surface science.</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>https://opentopography.org/</t>
+        </is>
+      </c>
+      <c r="E60" s="1" t="inlineStr">
+        <is>
+          <t>Ecosystems</t>
+        </is>
+      </c>
+      <c r="F60" s="1" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="G60" s="1" t="inlineStr">
+        <is>
+          <t>Global; United States</t>
+        </is>
+      </c>
       <c r="H60" s="1" t="n"/>
-      <c r="I60" s="1" t="n"/>
-      <c r="J60" s="1" t="n"/>
-      <c r="K60" s="3" t="n"/>
-      <c r="L60" s="1" t="n"/>
-      <c r="M60" s="3" t="n"/>
-      <c r="N60" s="1" t="n"/>
+      <c r="I60" s="1" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J60" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>Ecosystem Data; Hydrology; Land Management; Conservation</t>
+        </is>
+      </c>
+      <c r="L60" s="1" t="inlineStr">
+        <is>
+          <t>OpenTopography; Open Topography; OpenTopo; myOpenTopo; OpenTopography Facility; San Diego Supercomputer Center; SDSC; UC San Diego; UCSD; EarthScope Consortium; UNAVCO; Arizona State University; ASU; National Science Foundation; NSF; NCALM; USGS; NOAA; lidar; LiDAR; light detection and ranging; point cloud; point clouds; digital elevation model; DEM; digital terrain model; DTM; digital surface model; DSM; bare earth; canopy height model; hillshade; topography; elevation; terrain; high-resolution topography; bathymetry; topobathymetric; SRTM; Shuttle Radar Topography Mission; NASADEM; Copernicus DEM; ALOS World 3D; AW3D30; GEBCO; GEDI; ICESat-2; 3DEP; 3D Elevation Program; NOAA coastal lidar; ArcticDEM; REMA; photogrammetry; Find Topography Data; on-demand DEM generation; point cloud processing; bulk download; Global Datasets API; Point Elevation API; Data Catalog API; STAC; API key; LAS; LAZ; ASCII; GeoTIFF; Arc ASCII Grid; IMG; KMZ; tar.gz; REST API; JSON; DOI; geomorphology; active tectonics; fault mapping; earthquake science; landslide mapping; flood modeling; watershed analysis; flow direction; coastal erosion; wildfire response; post-fire assessment; forestry; vegetation structure; change detection; topographic differencing; natural hazards; Earth surface processes; hydrology; global coverage; United States; Colorado; Boulder; New Zealand; Switzerland; Norway; Finland; Arctic; Antarctica; Ecosystem Data; Hydrology; Land Management; Conservation; Historic; Current; Present; 2000-2026; SRTM February 2000; monthly data releases; ongoing</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>OpenTopography is an NSF-funded facility operated by the San Diego Supercomputer Center at UC San Diego with the EarthScope Consortium and Arizona State University, providing free access to high-resolution topographic data and web-based processing tools. Holdings span hundreds of research-grade airborne lidar point-cloud collections, high-resolution DEMs, and global rasters such as SRTM, NASADEM, ALOS World 3D, and the Copernicus DEM, plus federated access to USGS 3DEP and NOAA coastal lidar. Its terrain, hydrology, and vegetation-structure products underpin watershed, habitat, hazard, and land-change analyses.
+#### Host Organization
+- San Diego Supercomputer Center (UC San Diego), with the EarthScope Consortium and Arizona State University; NSF-funded
+#### Data Format
+- Point clouds as **LAS/LAZ** (or ASCII); DEMs and derivatives as **GeoTIFF** (delivered in .tar.gz), Arc ASCII Grid, or IMG; KMZ visualizations
+- **REST APIs** (Global Datasets, USGS 3DEP raster, point elevation, catalog search; free API key) and a STAC catalog
+#### How to access data of interest
+- Open [Find Topography Data](https://portal.opentopography.org/datasets) and search by place, or filter by data source (hosted lidar, global DEMs, USGS 3DEP, NOAA)
+- Select a dataset, draw an area of interest, and submit a job to download point clouds or generate on-demand DEMs - no account needed for most hosted data
+- A free [myOpenTopo account](https://portal.opentopography.org/newUser) adds saved jobs and larger limits; US academics with a .edu email can enable restricted federal collections (see [restricted-data instructions](https://opentopography.org/content/how-access-restricted-data-opentopography))
+#### Database Time Range
+- 2000-2026
+	- Global SRTM data date to February 2000; hosted lidar collections begin in the early 2000s and grow monthly
+#### Access Type
+- Public
+	- Core archive and global DEMs are open; some federated collections (USGS 3DEP point clouds, NOAA coastal lidar, ArcticDEM/REMA) are restricted (US academic .edu accounts get automatic access; others by application or a paid tier); APIs use a free key
+#### Citation Information
+- Follow [Citing OpenTopography and Hosted Data](https://opentopography.org/citations); each dataset page carries its exact citation and DOI
+- San Diego Supercomputer Center, EarthScope Consortium, and Arizona State University. "OpenTopography." *OpenTopography*, September 2026, &lt;https://opentopography.org/&gt;. 2026-09-02
+- See specific source citation details on the database website.</t>
+        </is>
+      </c>
+      <c r="N60" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
       <c r="O60" s="1" t="n"/>
       <c r="P60" s="1" t="n"/>
       <c r="Q60" s="1" t="n"/>

--- a/datasets.xlsx
+++ b/datasets.xlsx
@@ -5209,12 +5209,12 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>Air Quality; Water Quality; Public Health; Ecosystem Data</t>
+          <t>Air Quality; Water Quality; Public Health; Ecosystem Data; Toxicology</t>
         </is>
       </c>
       <c r="L52" s="1" t="inlineStr">
         <is>
-          <t>TRI; Toxics Release Inventory; Toxic Release Inventory; TRI Program; EPA; US EPA; U.S. Environmental Protection Agency; United States Environmental Protection Agency; EPCRA; Emergency Planning and Community Right-to-Know Act; Section 313; Pollution Prevention Act; toxic chemicals; toxic releases; chemical releases; PFAS; per- and polyfluoroalkyl substances; dioxins; toxicity equivalents; PBT; persistent bioaccumulative toxic chemicals; lead; mercury; carcinogens; stack emissions; fugitive air emissions; surface water discharges; underground injection; landfill disposal; off-site transfers; chemical waste; releases to air water land; pollution; toxics; contamination; TRI Explorer; TRI Toxics Tracker; TRI Toolbox; Envirofacts; Form R; Form A; TRI National Analysis; RSEI; Risk-Screening Environmental Indicators; EasyRSEI; ECHO; community right-to-know; pollution prevention; source reduction; waste management; recycling; energy recovery; environmental justice; risk screening; exposure assessment; emissions inventory; environmental reporting; industrial facilities; federal facilities; manufacturing; metal mining; electric power generation; hazardous waste treatment; CSV; tab-delimited; ZIP; XLSX; JSON; XML; Parquet; RESTful API; Envirofacts Data Service API; bulk download; Basic Data Files; Basic Plus Data Files; United States; US states; territories; Puerto Rico; tribal lands; county-level; ZIP code; facility-level; geocoded; Air Quality; Water Quality; Public Health; Ecosystem Data; Historic; Current; Present; 1987-2025; annual; calendar year; reporting year; updated annually</t>
+          <t>TRI; Toxics Release Inventory; Toxic Release Inventory; TRI Program; EPA; US EPA; U.S. Environmental Protection Agency; United States Environmental Protection Agency; EPCRA; Emergency Planning and Community Right-to-Know Act; Section 313; Pollution Prevention Act; toxic chemicals; toxic releases; chemical releases; PFAS; per- and polyfluoroalkyl substances; dioxins; toxicity equivalents; PBT; persistent bioaccumulative toxic chemicals; lead; mercury; carcinogens; stack emissions; fugitive air emissions; surface water discharges; underground injection; landfill disposal; off-site transfers; chemical waste; releases to air water land; pollution; toxics; contamination; TRI Explorer; TRI Toxics Tracker; TRI Toolbox; Envirofacts; Form R; Form A; TRI National Analysis; RSEI; Risk-Screening Environmental Indicators; EasyRSEI; ECHO; community right-to-know; pollution prevention; source reduction; waste management; recycling; energy recovery; environmental justice; risk screening; exposure assessment; emissions inventory; environmental reporting; industrial facilities; federal facilities; manufacturing; metal mining; electric power generation; hazardous waste treatment; CSV; tab-delimited; ZIP; XLSX; JSON; XML; Parquet; RESTful API; Envirofacts Data Service API; bulk download; Basic Data Files; Basic Plus Data Files; United States; US states; territories; Puerto Rico; tribal lands; county-level; ZIP code; facility-level; geocoded; Air Quality; Water Quality; Public Health; Ecosystem Data; Historic; Current; Present; 1987-2025; annual; calendar year; reporting year; updated annually; Toxicology</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>Global Forest Watch - rebranded Global Nature Watch in mid-2026, with globalforestwatch.org now redirecting there - is the World Resources Institute's free online platform for monitoring the world's forests in near real time. It combines annual tree cover loss data (2001-present, against a 2000 tree-cover baseline) produced by the University of Maryland's GLAD laboratory with daily-updated deforestation and disturbance alerts (GLAD, RADD, and DIST-ALERT) and NASA VIIRS fire alerts. Users can analyze change on an interactive map and country dashboards, download 65+ datasets in GIS-ready formats, or query the Data API; most GFW-produced datasets are CC BY 4.0, though partner datasets carry their own licenses.
+          <t>Global Forest Watch - rebranded Global Nature Watch in mid-2026, with globalforestwatch.org now redirecting there - is the World Resources Institute's free online platform for monitoring the world's forests in near real time. It combines annual tree cover loss data (2001-present, against a 2000 tree-cover baseline) produced by the University of Maryland's GLAD laboratory (cataloged separately here) with daily-updated deforestation and disturbance alerts (GLAD, RADD, and DIST-ALERT) and NASA VIIRS fire alerts. Users can analyze change on an interactive map and country dashboards, download 65+ datasets in GIS-ready formats, or query the Data API; most GFW-produced datasets are CC BY 4.0, though partner datasets carry their own licenses.
 #### Host Organization
 - World Resources Institute (WRI), with data partners including the University of Maryland GLAD lab, Google, and Esri
 #### Data Format
@@ -6017,20 +6017,84 @@
       <c r="AB60" s="2" t="n"/>
     </row>
     <row r="61" ht="14.25" customHeight="1">
-      <c r="A61" s="1" t="n"/>
-      <c r="B61" s="1" t="n"/>
-      <c r="C61" s="1" t="n"/>
-      <c r="D61" s="3" t="n"/>
-      <c r="E61" s="1" t="n"/>
-      <c r="F61" s="1" t="n"/>
-      <c r="G61" s="1" t="n"/>
+      <c r="A61" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="1" t="inlineStr">
+        <is>
+          <t>Global Land Analysis and Discovery</t>
+        </is>
+      </c>
+      <c r="C61" s="1" t="inlineStr">
+        <is>
+          <t>GLAD publishes global Landsat-based maps of forest change, height, cropland, and surface water.</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>https://glad.umd.edu/</t>
+        </is>
+      </c>
+      <c r="E61" s="1" t="inlineStr">
+        <is>
+          <t>Ecosystems</t>
+        </is>
+      </c>
+      <c r="F61" s="1" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="G61" s="1" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
       <c r="H61" s="1" t="n"/>
-      <c r="I61" s="1" t="n"/>
-      <c r="J61" s="1" t="n"/>
-      <c r="K61" s="3" t="n"/>
-      <c r="L61" s="1" t="n"/>
-      <c r="M61" s="3" t="n"/>
-      <c r="N61" s="1" t="n"/>
+      <c r="I61" s="1" t="n">
+        <v>1982</v>
+      </c>
+      <c r="J61" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>Ecosystem Data; Land Management; Agriculture; Conservation; Hydrology; Wildfire</t>
+        </is>
+      </c>
+      <c r="L61" s="1" t="inlineStr">
+        <is>
+          <t>GLAD; Global Land Analysis and Discovery; Global Land Analysis &amp; Discovery; UMD; University of Maryland; Department of Geographical Sciences; Hansen lab; Matthew Hansen; Potapov; gladxfer; Global Forest Change; Hansen tree cover loss; tree cover loss; forest cover; forest change; forest loss; forest gain; GLAD alerts; GLAD-L; GLAD-S2; DIST-ALERT; OPERA; deforestation alerts; GLCLUC; land cover and land use change; global forest canopy height; forest height; GEDI; intact forest landscapes; primary forest; global cropland; cropland expansion; annual cropland dynamics; soybean expansion; surface water dynamics; inland water; bare ground; tree canopy cover; forest loss due to fire; stand-replacement disturbance; forests; deforestation; land change; Landsat; Landsat ARD; analysis ready data; Sentinel-2; MODIS; AVHRR; spaceborne lidar; 30-m resolution; 16-day composite; surface reflectance; time series; change detection; near-real-time alerts; deforestation monitoring; phenology; remote sensing; Earth observation; satellite data; GeoTIFF; raster; tiles; Google Earth Engine; Earth Engine apps; AWS S3; Google Cloud Storage; API download; curl; wget; GLAD Tools; QGIS; LP DAAC; CC BY; open data; global; pan-tropical; Amazon; Congo Basin; Brazil; Indonesia; Russia; boreal forest; United States croplands; Global Forest Watch; World Resources Institute; land change science; food security mapping; wetlands; Ecosystem Data; Land Management; Agriculture; Conservation; Hydrology; Wildfire; Historic; Current; Present; 1982-2026; 1997; 2000-2024; operationally updated</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>The Global Land Analysis and Discovery (GLAD) laboratory at the University of Maryland produces the satellite-derived land change science behind much of modern deforestation monitoring, publishing roughly 40 open datasets including global tree cover loss, forest canopy height, land cover and land use change, cropland expansion, and surface water dynamics. While GLAD's flagship loss and alert layers are served interactively through Global Forest Watch (also in this catalog), the lab's own site provides direct access to the full product line as ~30 m GeoTIFF downloads, Google Earth Engine assets and apps, and the 16-day GLAD Landsat Analysis Ready Data archive (1997-present). All data are free under Creative Commons Attribution licensing, making GLAD the primary source for researchers who need the underlying rasters rather than a web dashboard.
+#### Host Organization
+- Global Land Analysis and Discovery (GLAD) laboratory, Department of Geographical Sciences, University of Maryland
+#### Data Format
+- **GeoTIFF** rasters (~30 m; 10x10-degree tiles or continental mosaics) via product download pages and tile selectors
+- **GLAD Landsat ARD** via HTTPS API and a public **AWS S3** bucket; **Google Earth Engine** assets and public apps for interactive analysis
+#### How to access data of interest
+- Browse the [GLAD dataset catalog](https://glad.umd.edu/dataset) and open the product page you need (forest height, land cover change, cropland, surface water, alerts)
+- Download GeoTIFF tiles or mosaics from the product's download links - no account needed (e.g., the [GLCLU 2000-2020 tile selector](https://storage.googleapis.com/earthenginepartners-hansen/GLCLU2000-2020/v2/download.html))
+- For the 16-day Landsat ARD archive, follow the [GLAD ARD instructions](https://glad.umd.edu/ard/home); explore interactively in the [GLAD Earth Engine apps](https://glad.earthengine.app/view/global-forest-change)
+#### Database Time Range
+- 1982-2026
+	- Long-term AVHRR-based land change spans 1982-2016; the operational Landsat ARD runs 1997-present; tree cover loss covers 2001 onward
+#### Access Type
+- Public
+#### Citation Information
+- Each dataset page specifies its required paper (e.g., Hansen et al. 2013, *Science*, for Global Forest Change; Potapov et al. 2020 for the ARD)
+- Global Land Analysis and Discovery Laboratory, University of Maryland. "GLAD Datasets." *GLAD*, September 2026, &lt;https://glad.umd.edu/dataset&gt;. 2026-09-02
+- See specific source citation details on the database website.</t>
+        </is>
+      </c>
+      <c r="N61" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
       <c r="O61" s="1" t="n"/>
       <c r="P61" s="1" t="n"/>
       <c r="Q61" s="1" t="n"/>
@@ -6047,20 +6111,84 @@
       <c r="AB61" s="2" t="n"/>
     </row>
     <row r="62" ht="14.25" customHeight="1">
-      <c r="A62" s="1" t="n"/>
-      <c r="B62" s="1" t="n"/>
-      <c r="C62" s="1" t="n"/>
-      <c r="D62" s="3" t="n"/>
-      <c r="E62" s="1" t="n"/>
-      <c r="F62" s="1" t="n"/>
-      <c r="G62" s="1" t="n"/>
+      <c r="A62" s="1" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="1" t="inlineStr">
+        <is>
+          <t>Gene Expression Omnibus</t>
+        </is>
+      </c>
+      <c r="C62" s="1" t="inlineStr">
+        <is>
+          <t>NCBI's public archive of functional genomics data: microarray and sequencing studies spanning all organisms.</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/geo/</t>
+        </is>
+      </c>
+      <c r="E62" s="1" t="inlineStr">
+        <is>
+          <t>People; Animals; Ecosystems</t>
+        </is>
+      </c>
+      <c r="F62" s="1" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="G62" s="1" t="inlineStr">
+        <is>
+          <t>Global; United States</t>
+        </is>
+      </c>
       <c r="H62" s="1" t="n"/>
-      <c r="I62" s="1" t="n"/>
-      <c r="J62" s="1" t="n"/>
-      <c r="K62" s="3" t="n"/>
-      <c r="L62" s="1" t="n"/>
-      <c r="M62" s="3" t="n"/>
-      <c r="N62" s="1" t="n"/>
+      <c r="I62" s="1" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J62" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>Genomics; Biological Variability; Public Health; Animal Health</t>
+        </is>
+      </c>
+      <c r="L62" s="1" t="inlineStr">
+        <is>
+          <t>GEO; Gene Expression Omnibus; NCBI GEO; GEO database; NCBI; National Center for Biotechnology Information; NLM; National Library of Medicine; NIH; National Institutes of Health; GSE; GSM; GPL; GDS; Series; Sample; Platform; DataSet; GEO Profiles; GEO DataSets; accession number; gene expression; expression profiling; transcriptomics; functional genomics; epigenomics; differential expression; RNA-seq; single-cell RNA-seq; scRNA-seq; microarray; ChIP-seq; ATAC-seq; Hi-C; DNA methylation; chromatin accessibility; genome binding; non-coding RNA; miRNA; next-generation sequencing; NGS; high-throughput sequencing; hybridization array; MIAME; MINSEQE; SOFT; Simple Omnibus Format in Text; MINiML; Series Matrix; XML; TXT; supplementary files; CEL files; raw data; GEO2R; GEOquery; limma; DESeq2; Bioconductor; E-utilities; Entrez; eSearch; eFetch; FTP download; bulk download; programmatic access; open access; public repository; human; Homo sapiens; mouse; Mus musculus; rat; zebrafish; Arabidopsis; model organisms; livestock; plants; bacteria; fungi; viruses; multi-species; 6000 organisms; GenBank; SRA; Sequence Read Archive; BioProject; BioSample; ArrayExpress; Expression Atlas; biomarker discovery; disease transcriptomics; cancer gene expression; host-pathogen response; toxicogenomics; comparative transcriptomics; meta-analysis; data reuse; Bethesda Maryland; Genomics; Biological Variability; Public Health; Animal Health; Historic; Current; Present; 2000-2026; established 2000; ongoing submissions</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>The Gene Expression Omnibus (GEO) is NCBI's international public repository for high-throughput functional genomics data, archiving microarray and next-generation sequencing studies of gene expression and epigenomics since 2000. It holds more than 6.5 million samples from over 200,000 studies spanning 6,000+ organisms - from humans and livestock to plants and microbes - all freely downloadable with no login. Records are organized as Platforms, Samples, and Series, retrievable through Entrez search, bulk FTP, and E-utilities, and analyzable in the browser with the GEO2R differential-expression tool. GEO is independent of EMBL-EBI's ArrayExpress (also in this catalog); the two archives hold distinct submissions.
+#### Host Organization
+- National Center for Biotechnology Information (NCBI), National Library of Medicine, National Institutes of Health
+#### Data Format
+- **SOFT** and **MINiML (XML)** record formats, **Series Matrix** TXT files, and raw supplementary files (e.g., tar/gzip archives)
+- Bulk **FTP** download; programmatic access via **E-utilities** (db=gds and db=geoprofiles); in-browser analysis with **GEO2R**
+#### How to access data of interest
+- Search studies by keyword, organism, or accession in [GEO DataSets](https://www.ncbi.nlm.nih.gov/gds) or from the [GEO home page](https://www.ncbi.nlm.nih.gov/geo/)
+- Open any record directly by accession (GSE/GSM/GPL) and download its files; analyze a Series in the browser with [GEO2R](https://www.ncbi.nlm.nih.gov/geo/info/geo2r.html)
+- Bulk-download from the [GEO FTP site](https://www.ncbi.nlm.nih.gov/geo/info/download.html) or script retrieval via [E-utilities](https://www.ncbi.nlm.nih.gov/geo/info/geo_paccess.html)
+#### Database Time Range
+- 2000-2026
+	- Established in 2000; submissions and curation are ongoing
+#### Access Type
+- Public
+#### Citation Information
+- Follow [Citing and linking to GEO](https://www.ncbi.nlm.nih.gov/geo/info/linking.html): cite the accession number and the GEO reference papers
+- National Center for Biotechnology Information. "Gene Expression Omnibus (GEO)." *National Library of Medicine*, September 2026, &lt;https://www.ncbi.nlm.nih.gov/geo/&gt;. 2026-09-02
+- See specific source citation details on the database website.</t>
+        </is>
+      </c>
+      <c r="N62" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
       <c r="O62" s="1" t="n"/>
       <c r="P62" s="1" t="n"/>
       <c r="Q62" s="1" t="n"/>
@@ -6077,20 +6205,84 @@
       <c r="AB62" s="2" t="n"/>
     </row>
     <row r="63" ht="14.25" customHeight="1">
-      <c r="A63" s="1" t="n"/>
-      <c r="B63" s="1" t="n"/>
-      <c r="C63" s="1" t="n"/>
-      <c r="D63" s="3" t="n"/>
-      <c r="E63" s="1" t="n"/>
-      <c r="F63" s="1" t="n"/>
-      <c r="G63" s="1" t="n"/>
+      <c r="A63" s="1" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="1" t="inlineStr">
+        <is>
+          <t>ArrayExpress</t>
+        </is>
+      </c>
+      <c r="C63" s="1" t="inlineStr">
+        <is>
+          <t>ArrayExpress archives functional genomics studies worldwide, now a collection in EMBL-EBI's BioStudies.</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ebi.ac.uk/biostudies/arrayexpress</t>
+        </is>
+      </c>
+      <c r="E63" s="1" t="inlineStr">
+        <is>
+          <t>People; Animals</t>
+        </is>
+      </c>
+      <c r="F63" s="1" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="G63" s="1" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
       <c r="H63" s="1" t="n"/>
-      <c r="I63" s="1" t="n"/>
-      <c r="J63" s="1" t="n"/>
-      <c r="K63" s="3" t="n"/>
-      <c r="L63" s="1" t="n"/>
-      <c r="M63" s="3" t="n"/>
-      <c r="N63" s="1" t="n"/>
+      <c r="I63" s="1" t="n">
+        <v>2002</v>
+      </c>
+      <c r="J63" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>Genomics; Biological Variability; Animal Health; Agriculture</t>
+        </is>
+      </c>
+      <c r="L63" s="1" t="inlineStr">
+        <is>
+          <t>ArrayExpress; Array Express; AE; BioStudies; BioStudies ArrayExpress collection; ArrayExpress collection; ArrayExpress Archive; Functional Genomics Data; E-MTAB; E-GEOD; S-BSST; EMBL-EBI; EBI; European Bioinformatics Institute; EMBL; European Molecular Biology Laboratory; Hinxton; Wellcome Genome Campus; Gene Expression team; functional genomics; transcriptomics; gene expression; expression profiling; microarray; DNA microarray; RNA-seq; single-cell RNA-seq; scRNA-seq; ChIP-seq; ATAC-seq; bisulfite-seq; DNA methylation; epigenomics; high-throughput sequencing; NGS; comparative transcriptomics; MAGE-TAB; IDF; SDRF; ADF; MIAME; MINSEQE; FASTQ; CEL file; raw data; processed data; array design; BioStudies API; REST API; JSON; FTP download; bulk download; programmatic access; accession number; EBI Search; Annotare; GEO; Gene Expression Omnibus; NCBI GEO; Expression Atlas; Single Cell Expression Atlas; European Nucleotide Archive; ENA; BioSamples; human; mouse; model organisms; zebrafish; Drosophila; Arabidopsis; livestock genomics; veterinary transcriptomics; host-pathogen interaction; infection gene expression; cancer transcriptomics; microbial gene expression; open access; public archive; Genomics; Biological Variability; Animal Health; Agriculture; Historic; Current; Present; 2002-2026; migrated to BioStudies 2022; ongoing submissions</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>ArrayExpress is EMBL-EBI's public archive for transcriptomics and other functional genomics data, collecting microarray and high-throughput sequencing studies (RNA-seq, ChIP-seq, ATAC-seq, and more) from research groups worldwide since 2002. In late 2022 the standalone ArrayExpress website was retired and every dataset became the ArrayExpress collection within EMBL-EBI's BioStudies database; old links and accession numbers (E-MTAB-n, E-GEOD-n) remain valid and point to the equivalent BioStudies pages. ArrayExpress is independent of NCBI's GEO (also in this catalog) - regular GEO imports were discontinued (announced in the 2019 update), so each archive holds unique submissions, with legacy GEO imports searchable in ArrayExpress under E-GEOD accessions.
+#### Host Organization
+- EMBL's European Bioinformatics Institute (EMBL-EBI)
+#### Data Format
+- **MAGE-TAB** standardized study metadata (IDF + SDRF) following MIAME/MINSEQE community guidelines, with raw and processed data files per study
+- BioStudies web search plus **REST API** (JSON) and **FTP** bulk access
+#### How to access data of interest
+- Open the [ArrayExpress collection in BioStudies](https://www.ebi.ac.uk/biostudies/arrayexpress) and search, or [browse all studies](https://www.ebi.ac.uk/biostudies/arrayexpress/studies)
+- Filter by organism or technology and open a study record (accessions like E-MTAB-12345), then download its MAGE-TAB metadata and data files
+- For bulk or scripted use, see the [ArrayExpress help](https://www.ebi.ac.uk/biostudies/arrayexpress/help) for the BioStudies API and FTP
+#### Database Time Range
+- 2002-2026
+	- Founded 2002; part of BioStudies since October 2022; submissions ongoing via Annotare
+#### Access Type
+- Public
+#### Citation Information
+- Cite the study accession number and the BioStudies home page per [What is BioStudies?](https://www.ebi.ac.uk/biostudies/about)
+- European Bioinformatics Institute (EMBL-EBI). "ArrayExpress." *BioStudies*, September 2026, &lt;https://www.ebi.ac.uk/biostudies/arrayexpress&gt;. 2026-09-02
+- See specific source citation details on the database website.</t>
+        </is>
+      </c>
+      <c r="N63" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
       <c r="O63" s="1" t="n"/>
       <c r="P63" s="1" t="n"/>
       <c r="Q63" s="1" t="n"/>
@@ -6107,20 +6299,84 @@
       <c r="AB63" s="2" t="n"/>
     </row>
     <row r="64" ht="14.25" customHeight="1">
-      <c r="A64" s="1" t="n"/>
-      <c r="B64" s="1" t="n"/>
-      <c r="C64" s="1" t="n"/>
-      <c r="D64" s="3" t="n"/>
-      <c r="E64" s="1" t="n"/>
-      <c r="F64" s="1" t="n"/>
-      <c r="G64" s="1" t="n"/>
+      <c r="A64" s="1" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="1" t="inlineStr">
+        <is>
+          <t>The Human Protein Atlas</t>
+        </is>
+      </c>
+      <c r="C64" s="1" t="inlineStr">
+        <is>
+          <t>The Human Protein Atlas maps protein expression across human tissues, cells, blood, brain, and cancer.</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>https://www.proteinatlas.org/</t>
+        </is>
+      </c>
+      <c r="E64" s="1" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+      <c r="F64" s="1" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="G64" s="1" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
       <c r="H64" s="1" t="n"/>
-      <c r="I64" s="1" t="n"/>
-      <c r="J64" s="1" t="n"/>
-      <c r="K64" s="3" t="n"/>
-      <c r="L64" s="1" t="n"/>
-      <c r="M64" s="3" t="n"/>
-      <c r="N64" s="1" t="n"/>
+      <c r="I64" s="1" t="n">
+        <v>2003</v>
+      </c>
+      <c r="J64" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>Genomics; Biological Variability; Public Health</t>
+        </is>
+      </c>
+      <c r="L64" s="1" t="inlineStr">
+        <is>
+          <t>Human Protein Atlas; The Human Protein Atlas; HPA; proteinatlas; proteinatlas.org; Protein Atlas; Tissue Atlas; Brain Atlas; Single Cell resource; Subcellular Atlas; Cancer Atlas; Pathology Atlas; Blood Atlas; Cell Line resource; Structure resource; Interaction resource; proteomics; proteome; human proteome; protein expression; protein evidence; protein localization; subcellular localization; secretome; plasma proteome; blood proteins; membrane proteome; transcription factors; druggable proteome; housekeeping genes; tissue specificity; cell type specificity; expression clusters; protein-coding genes; immunohistochemistry; IHC; immunofluorescence; confocal microscopy; antibody-based profiling; antibody validation; antibodies; RNA-seq; transcriptomics; spatial transcriptomics; single-cell RNA sequencing; mass spectrometry; Deep Visual Proteomics; tissue microarray; cancer prognostics; survival analysis; tumor biomarkers; precision medicine; pathology; oncology; disease biomarkers; Ensembl; ENSG; UniProt; gene symbols; Homo sapiens; human; mouse brain; pig brain; mammalian brain; comparative neuroanatomy; KTH Royal Institute of Technology; Uppsala University; Karolinska Institutet; SciLifeLab; Knut and Alice Wallenberg Foundation; Mathias Uhlen; Sweden; Swedish research program; open access; CC BY 4.0; TSV; XML; JSON; RDF; REST API; bulk download; versioned releases; Genomics; Biological Variability; Public Health; Historic; Current; Present; 2003-2026; version 25; updated regularly</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>The Human Protein Atlas is a Swedish open-access program, initiated in 2003 with funding from the Knut and Alice Wallenberg Foundation, that aims to map all human proteins in cells, tissues, and organs. Using antibody-based imaging (millions of annotated images), transcriptomics, mass-spectrometry proteomics, and systems biology, it profiles roughly 20,000 protein-coding genes across resources spanning tissue, brain, single-cell, subcellular, cancer, blood, cell-line, structure, and interaction data. Comparative mouse and pig brain data complement the human focus, and the Pathology Atlas ties expression to cancer patient survival.
+#### Host Organization
+- Human Protein Atlas consortium, led from KTH Royal Institute of Technology at SciLifeLab, Sweden (with Uppsala University, Karolinska Institutet, and Linkoping University)
+#### Data Format
+- Searchable per-gene web pages; whole-atlas bulk downloads as **TSV**, **JSON**, and **XML**
+- Per-gene programmatic URLs (append .tsv/.json/.xml to an Ensembl ID) and a search API; every release archived at versioned URLs (v##.proteinatlas.org)
+#### How to access data of interest
+- Search any gene, protein, tissue, or cell type from the [Human Protein Atlas homepage](https://www.proteinatlas.org/) - no account needed
+- On a gene page, browse the Tissue, Brain, Single Cell, Subcellular, Cancer, Blood, and other tabs for images and expression data
+- Grab whole-atlas files from [Downloadable data](https://www.proteinatlas.org/about/download) or script access per [Programmatic data access](https://www.proteinatlas.org/about/help/dataaccess)
+#### Database Time Range
+- 2003-2026
+	- Program initiated 2003; first public release 2005; current major version 25, updated regularly
+#### Access Type
+- Public
+#### Citation Information
+- Follow the [licence and citation rules](https://www.proteinatlas.org/about/licence) (CC BY 4.0): cite the relevant primary publication and "Human Protein Atlas proteinatlas.org", linking versioned URLs for specific data
+- Human Protein Atlas Consortium. "The Human Protein Atlas." *The Human Protein Atlas*, September 2026, &lt;https://www.proteinatlas.org/&gt;. 2026-09-02
+- See specific source citation details on the database website.</t>
+        </is>
+      </c>
+      <c r="N64" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
       <c r="O64" s="1" t="n"/>
       <c r="P64" s="1" t="n"/>
       <c r="Q64" s="1" t="n"/>
@@ -6137,20 +6393,85 @@
       <c r="AB64" s="2" t="n"/>
     </row>
     <row r="65" ht="14.25" customHeight="1">
-      <c r="A65" s="1" t="n"/>
-      <c r="B65" s="1" t="n"/>
-      <c r="C65" s="1" t="n"/>
-      <c r="D65" s="3" t="n"/>
-      <c r="E65" s="1" t="n"/>
-      <c r="F65" s="1" t="n"/>
-      <c r="G65" s="1" t="n"/>
+      <c r="A65" s="1" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="1" t="inlineStr">
+        <is>
+          <t>Comparative Toxicogenomics Database</t>
+        </is>
+      </c>
+      <c r="C65" s="1" t="inlineStr">
+        <is>
+          <t>CTD curates chemical-gene-disease interactions that link environmental exposures to health outcomes.</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>https://ctdbase.org/</t>
+        </is>
+      </c>
+      <c r="E65" s="1" t="inlineStr">
+        <is>
+          <t>People; Animals; Ecosystems</t>
+        </is>
+      </c>
+      <c r="F65" s="1" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="G65" s="1" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
       <c r="H65" s="1" t="n"/>
-      <c r="I65" s="1" t="n"/>
-      <c r="J65" s="1" t="n"/>
-      <c r="K65" s="3" t="n"/>
-      <c r="L65" s="1" t="n"/>
-      <c r="M65" s="3" t="n"/>
-      <c r="N65" s="1" t="n"/>
+      <c r="I65" s="1" t="n">
+        <v>2004</v>
+      </c>
+      <c r="J65" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>Toxicology; Public Health; Genomics; Animal Health; Population Health</t>
+        </is>
+      </c>
+      <c r="L65" s="1" t="inlineStr">
+        <is>
+          <t>CTD; ctdbase; Comparative Toxicogenomics Database; ctdbase.org; toxicogenomics; toxicology; chemical-gene interactions; chemical-disease associations; gene-disease associations; chemical-phenotype interactions; curated interactions; inferred relationships; literature curation; biocuration; manual curation; CGPD tetramers; mechanistic pathways; exposure module; exposure statements; exposure science; exposome; anatomy module; phenotype module; Batch Query; VennViewer; Set Analyzer; Pathway View; MEDIC; environmental chemicals; chemical stressors; xenobiotics; pollutants; pesticides; heavy metals; drugs; environmental exposure; receptor demographics; biomarkers; environmental health; human disease; disease etiology; adverse outcomes; adverse outcome pathways; phenotypes; cancer; developmental toxicity; neurotoxicity; genes; proteins; gene expression; molecular mechanisms; pathways; Gene Ontology; GO; KEGG; transcriptomics; comparative biology; animal models; vertebrates; invertebrates; Eumetazoa; model organisms; zebrafish; rodent models; cross-species extrapolation; MeSH; NCBI Gene; OMIM; DrugBank; OBO; controlled vocabularies; ontologies; North Carolina State University; NC State; Center for Human Health and the Environment; MDI Biological Laboratory; Mount Desert Island Biological Laboratory; NIEHS; hazard identification; risk assessment; chemical safety; environmental health research; systems toxicology; precision environmental health; CSV; TSV; XML; bulk download; monthly updates; open access; Toxicology; Public Health; Genomics; Animal Health; Population Health; Historic; Current; Present; 2004-2026; founded 2004</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>The Comparative Toxicogenomics Database (CTD) is a literature-curated resource from North Carolina State University that connects environmental chemicals to the genes, phenotypes, diseases, and exposures they affect. Professional biocurators have extracted millions of interactions from over 149,000 publications, covering 17,700+ chemicals, 55,400 genes, and 7,200 diseases across more than 630 species, with integration into pathway and ontology data expanding this to tens of millions of inferred relationships. Because it spans human, laboratory-animal, and wildlife literature while anchoring chemicals to real-world exposure statements, CTD is this catalog's connector between environmental contaminants (such as those in the EPA Toxics Release Inventory, cataloged separately) and human and animal health.
+#### Host Organization
+- North Carolina State University, Department of Biological Sciences (originated at MDI Biological Laboratory, 2004; NIEHS-funded)
+#### Data Format
+- Web query pages plus **Batch Query**, Set Analyzer, VennViewer, and Pathway View analysis tools
+- Bulk data files in **CSV, TSV, XML, and OBO**, refreshed monthly
+#### How to access data of interest
+- Go to [CTD](https://ctdbase.org/) and enter a chemical, gene, disease, phenotype, or exposure term in the keyword search - no account needed
+- For bulk lookups, paste term lists into [Batch Query](https://ctdbase.org/tools/batchQuery.go) and choose the data type and output format
+- Download complete monthly data files from [Data Downloads](https://ctdbase.org/downloads/); review the [Legal Notices](https://ctdbase.org/about/legal.jsp) before redistribution
+#### Database Time Range
+- 2004-2026
+	- Launched November 2004; curated literature reaches back earlier; updated monthly
+#### Access Type
+- Public
+	- Free for non-commercial use; commercial users are asked to arrange a license
+#### Citation Information
+- Follow [Citing CTD](https://ctdbase.org/about/publications/#citing); the current flagship paper is the CTD 20th-anniversary update in *Nucleic Acids Research* (2025)
+- North Carolina State University. "Comparative Toxicogenomics Database (CTD)." *CTD*, September 2026, &lt;https://ctdbase.org/&gt;. 2026-09-02
+- See specific source citation details on the database website.</t>
+        </is>
+      </c>
+      <c r="N65" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
       <c r="O65" s="1" t="n"/>
       <c r="P65" s="1" t="n"/>
       <c r="Q65" s="1" t="n"/>

--- a/datasets.xlsx
+++ b/datasets.xlsx
@@ -1477,12 +1477,12 @@
       </c>
       <c r="L10" s="15" t="inlineStr">
         <is>
-          <t>Aethina tumida; African Horse Sickness; African Swine Fever; Agriculture; Alaskapox virus; American foulbrood of honey bees; Anthrax; Arena virus; Argentine hemorrhagic fever; Aujeszky’s disease; Avian chlamydiosis; Avian infectious bronchitis; Avian infectious laryngotracheitis; Avian Influenza; Avian mycoplasmosis; Blackleg; Bluetongue; Botulism; Bovine Anaplasmosis; Bovine babesiosis; Bovine genital campylobacteriosis; Bovine spongiform encephalopathy; Bovine tuberculosis; Bovine viral diarrhea; Brucellosis; Brucella abortus; Brucella melitensis; Brucella suis; Camelpox; Caprine arthritis; Caprine encephalitis; Chronic respiratory disease; Classical swine fever; Contagious agalactia; Contagious bovine pleuropneumonia; Contagious caprine pleuropneumonia; Contagious equine metritis; COVID-19; Crimean Congo Haemorrhagic fever; Dourine; Duck virus enteritis; Duck virus hepatitis; Ebola virus; Ebola-Reston; Echinococcosis; Enzootic abortion of ewes; Enzootic bovine leukosis; Epizootic haemorrhagic disease; Epizootic ulcerative syndrome; Equine infectious anaemia; Equine influenza; Equine piroplasmosis; Equine rhinopneumonitis; Equine viral arteritis; European foulbrood of honey bees; Foot and Mouth Disease; Fowl cholera; Fowl typhoid; Glanders; Haemorrhagic septicaemia; Hansen’s disease; Heartwater; Hendra virus disease; Infectious bovine rhinotracheitis; Infectious bronchitis; Intoxication; Japanese encephalitis; Junin virus; Kunjin virus; Leishmaniasis; Leprosy; Leptospirosis; Lumpy Skin Disease; Maedi-visna; Malignant catarrhal fever; Marburg Hemorrhagic fever; Marek’s disease; MERS-CoV; Monkey Pox; Myxomatosis; Newcastle disease; New world screwworm (Cochliomyia hominivorax); Nipah virus encephalitis; Old world screwworm (Chrysomya bezziana); Oropouche fever; Other bacterial diseases; Paratuberculosis; Pest control; Peste des Petits Ruminants; Porcine cysticercosis; Porcine epidemic diarrhea; Porcine reproductive and respiratory syndrome; Pullorum disease; Q fever; Rabbit haemorrhagic disease; Rabies; Rift Valley Fever; Rinderpest; Risk assessment; Salmonellosis; Schmallenberg; Scrapie; Sheep pox; Small hive beetle infestation; Starvation; Strangles; Surra; Swine influenza; Swine Novel Enteric Coronavirus Disease; Swine vesicular disease; Teschovirus encephalomyelitis; Theileriosis; Transmissible gastroenteritis; Trichinellosis; Trypanosoma evansi; Trypanosomosis; Tsetse-transmitted diseases; Tuberculosis; Tularemia; Turkey rhinotracheitis; Unknown disease; Varroa mites; Varroosis of honey bees; Venezuelan equine encephalomyelitis; Vesicular stomatitis; West Nile Fever; Wildlife; Wind; Yellow Fever; Yezo virus; Animal density; Animal disease; Animal health; Animal health events; Biosecurity; weather; Atmospheric Shift; Ecological changes; Weather pattern disruption; Crop pests; Data sharing; Disease containment; Disease control measures; Disease data; Disease diagnostics; Disease management; Disease monitoring; Disease notifications; Disease outbreaks; Disease prevention; Disease spread; Disease surveillance; Disease tracking; Early warning system; Emergency response; EMPRES-i; Epidemiology; FAO; Food animals; Food security; Global health; Global surveillance; Infectious diseases; International cooperation; Livestock; Livestock diseases; Pandemic preparedness; Plant health; Plant pest events; Plant pests; Regional health; Transboundary diseases; Veterinary health; Zoonosis; Zoonotic disease; Zoonotic diseases; Acute Respiratory Disease Syndrome; African Trypanosomiasis; Alveolar Echinococcosis; Animal Epidemics; Anthrax Outbreaks; Avian Paramyxovirus; Babesiosis; Bat Rabies; Bovine Respiratory Disease; Brucellosis Control; Canine Distemper; Caprine Arthritis Encephalitis Virus; Cat Scratch Disease; Clostridial Diseases; Coronavirus Infections; Crimean-Congo Hemorrhagic Fever Virus; Cryptosporidiosis; Cysticercosis; Dengue Fever; Diphtheria; Eastern Equine Encephalitis; Encephalomyocarditis Virus; Equine Encephalitis; Equine Herpesvirus; Equine Influenza Virus; Exotic Animal Diseases; Feline Leukemia Virus; Foot-and-Mouth Disease Virus; Fowlpox; Glanders Disease; Hantavirus Pulmonary Syndrome; Hemorrhagic Fever with Renal Syndrome; Hepatitis E Virus; Highly Pathogenic Avian Influenza; Infectious Bursal Disease; Infectious Canine Hepatitis; Infectious Salmon Anemia; Japanese Encephalitis Virus; Lumpy Skin Disease Virus; Lyme Disease; Marek’s Disease Virus; Mycoplasma Infection; Newcastle Disease Virus; Nipah Virus; Parainfluenza Virus; Pasteurellosis; Peste des Petits Ruminants Virus; Plague; Porcine Circovirus; Porcine Respiratory Disease Complex; Rabies Virus; Rift Valley Fever Virus; Rinderpest Virus; Rotavirus Infection; Scrapie Disease; Severe Acute Respiratory Syndrome (SARS); Sheep Scab; Swine Vesicular Disease Virus; Tularemia Bacteria; Viral Hemorrhagic Septicemia; West Nile Virus Disease; Wildlife Disease Surveillance; Wildlife Health Monitoring; Zika Virus; Zoonotic Spillover; Zoonotic Transmission; Animal Biosecurity Measures; Biosafety Protocols; Disease Early Detection; Epidemiological Modeling; Global Animal Health; Herd Immunity in Animals; Infectious Disease Control; Livestock Management; One Health Approach; Pandemic Response; Pathogen Genomics; Plant Disease Management; Plant Pathogens; Veterinary Epidemiology; Vector Control; Wildlife Conservation Health; Zoonotic Risk Assessment; Historic; Current; Present; 2004 - 2025</t>
+          <t>Aethina tumida; African Horse Sickness; African Swine Fever; Agriculture; Alaskapox virus; American foulbrood of honey bees; Anthrax; Arena virus; Argentine hemorrhagic fever; Aujeszky’s disease; Avian chlamydiosis; Avian infectious bronchitis; Avian infectious laryngotracheitis; Avian Influenza; Avian mycoplasmosis; Blackleg; Bluetongue; Botulism; Bovine Anaplasmosis; Bovine babesiosis; Bovine genital campylobacteriosis; Bovine spongiform encephalopathy; Bovine tuberculosis; Bovine viral diarrhea; Brucellosis; Brucella abortus; Brucella melitensis; Brucella suis; Camelpox; Caprine arthritis; Caprine encephalitis; Chronic respiratory disease; Classical swine fever; Contagious agalactia; Contagious bovine pleuropneumonia; Contagious caprine pleuropneumonia; Contagious equine metritis; COVID-19; Crimean Congo Haemorrhagic fever; Dourine; Duck virus enteritis; Duck virus hepatitis; Ebola virus; Ebola-Reston; Echinococcosis; Enzootic abortion of ewes; Enzootic bovine leukosis; Epizootic haemorrhagic disease; Epizootic ulcerative syndrome; Equine infectious anaemia; Equine influenza; Equine piroplasmosis; Equine rhinopneumonitis; Equine viral arteritis; European foulbrood of honey bees; Foot and Mouth Disease; Fowl cholera; Fowl typhoid; Glanders; Haemorrhagic septicaemia; Hansen’s disease; Heartwater; Hendra virus disease; Infectious bovine rhinotracheitis; Infectious bronchitis; Intoxication; Japanese encephalitis; Junin virus; Kunjin virus; Leishmaniasis; Leprosy; Leptospirosis; Lumpy Skin Disease; Maedi-visna; Malignant catarrhal fever; Marburg Hemorrhagic fever; Marek’s disease; MERS-CoV; Monkey Pox; Myxomatosis; Newcastle disease; New world screwworm (Cochliomyia hominivorax); Nipah virus encephalitis; Old world screwworm (Chrysomya bezziana); Oropouche fever; Other bacterial diseases; Paratuberculosis; Pest control; Peste des Petits Ruminants; Porcine cysticercosis; Porcine epidemic diarrhea; Porcine reproductive and respiratory syndrome; Pullorum disease; Q fever; Rabbit haemorrhagic disease; Rabies; Rift Valley Fever; Rinderpest; Risk assessment; Salmonellosis; Schmallenberg; Scrapie; Sheep pox; Small hive beetle infestation; Starvation; Strangles; Surra; Swine influenza; Swine Novel Enteric Coronavirus Disease; Swine vesicular disease; Teschovirus encephalomyelitis; Theileriosis; Transmissible gastroenteritis; Trichinellosis; Trypanosoma evansi; Trypanosomosis; Tsetse-transmitted diseases; Tuberculosis; Tularemia; Turkey rhinotracheitis; Unknown disease; Varroa mites; Varroosis of honey bees; Venezuelan equine encephalomyelitis; Vesicular stomatitis; West Nile Fever; Wildlife; Wind; Yellow Fever; Yezo virus; Animal density; Animal disease; Animal health; Animal health events; Biosecurity; weather; Atmospheric Shift; Ecological changes; Weather pattern disruption; Crop pests; Data sharing; Disease containment; Disease control measures; Disease data; Disease diagnostics; Disease management; Disease monitoring; Disease notifications; Disease outbreaks; Disease prevention; Disease spread; Disease surveillance; Disease tracking; Early warning system; Emergency response; EMPRES-i; Epidemiology; FAO; Food animals; Food security; Global health; Global surveillance; Infectious diseases; International cooperation; Livestock; Livestock diseases; Pandemic preparedness; Plant health; Plant pest events; Plant pests; Regional health; Transboundary diseases; Veterinary health; Zoonosis; Zoonotic disease; Zoonotic diseases; Acute Respiratory Disease Syndrome; African Trypanosomiasis; Alveolar Echinococcosis; Animal Epidemics; Anthrax Outbreaks; Avian Paramyxovirus; Babesiosis; Bat Rabies; Bovine Respiratory Disease; Brucellosis Control; Canine Distemper; Caprine Arthritis Encephalitis Virus; Cat Scratch Disease; Clostridial Diseases; Coronavirus Infections; Crimean-Congo Hemorrhagic Fever Virus; Cryptosporidiosis; Cysticercosis; Dengue Fever; Diphtheria; Eastern Equine Encephalitis; Encephalomyocarditis Virus; Equine Encephalitis; Equine Herpesvirus; Equine Influenza Virus; Exotic Animal Diseases; Feline Leukemia Virus; Foot-and-Mouth Disease Virus; Fowlpox; Glanders Disease; Hantavirus Pulmonary Syndrome; Hemorrhagic Fever with Renal Syndrome; Hepatitis E Virus; Highly Pathogenic Avian Influenza; Infectious Bursal Disease; Infectious Canine Hepatitis; Infectious Salmon Anemia; Japanese Encephalitis Virus; Lumpy Skin Disease Virus; Lyme Disease; Marek’s Disease Virus; Mycoplasma Infection; Newcastle Disease Virus; Nipah Virus; Parainfluenza Virus; Pasteurellosis; Peste des Petits Ruminants Virus; Plague; Porcine Circovirus; Porcine Respiratory Disease Complex; Rabies Virus; Rift Valley Fever Virus; Rinderpest Virus; Rotavirus Infection; Scrapie Disease; Severe Acute Respiratory Syndrome (SARS); Sheep Scab; Swine Vesicular Disease Virus; Tularemia Bacteria; Viral Hemorrhagic Septicemia; West Nile Virus Disease; Wildlife Disease Surveillance; Wildlife Health Monitoring; Zika Virus; Zoonotic Spillover; Zoonotic Transmission; Animal Biosecurity Measures; Biosafety Protocols; Disease Early Detection; Epidemiological Modeling; Global Animal Health; Herd Immunity in Animals; Infectious Disease Control; Livestock Management; One Health Approach; Pandemic Response; Pathogen Genomics; Plant Disease Management; Plant Pathogens; Veterinary Epidemiology; Vector Control; Wildlife Conservation Health; Zoonotic Risk Assessment; Historic; Current; Present; 2004 - 2025; EMA-i; EMA-i+; Event Mobile Application; EMPRES-i+; mobile field reporting; field data collection app</t>
         </is>
       </c>
       <c r="M10" s="16" t="inlineStr">
         <is>
-          <t>EMPRES‑i is FAO’s global animal disease information system that collects, verifies, and maps up-to-date “disease event” data - sourced from national governments, field reports, media and surveillance systems - and is integrated with layers like livestock density and environmental factors to support disease prevention, control strategies, and early warning for disease outbreaks.
+          <t>EMPRES‑i is FAO’s global animal disease information system that collects, verifies, and maps up-to-date “disease event” data - sourced from national governments, field reports, media and surveillance systems - and is integrated with layers like livestock density and environmental factors to support disease prevention, control strategies, and early warning for disease outbreaks. Field reports from veterinary field officers can be submitted through FAO's companion mobile app, EMA-i+ (Event Mobile Application); those national data are shared to the global EMPRES-i+ only at each country's discretion.
 #### Host Organization
 - Food and Agricultural Organization of the United Nations - Global Animal Disease Information System
 #### Data Format
@@ -2494,7 +2494,7 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Move Bank Data Repository</t>
+          <t>Movebank</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="L22" s="15" t="inlineStr">
         <is>
-          <t>animal tracking; animal movement; telemetry data; tracking map; Movebank; GPS locations; Argos tags; VHF telemetry; sensor data; bio-logging; acceleration; magnetometer; barometer; temperature sensor; light-level sensor; satellite tracking; radio transmitter; animal deployments; deployment period; tag deployment; tag model; tag manufacturer; tag attachment; collar tag; harness tag; implant tag; tape tag; event data; timestamped locations; timestamped events; animal ID; tag ID; deployment ID; taxon; species tracking; genus tracking; family tracking; ITIS taxonomy; study metadata; study site; study name; sensor type filter; live data feed; public data access; restricted access data; data download; CSV download; Excel download; shapefile; KML export; REST API; MoveApps; EnvDATA; ECODATA; interactive map; map basemaps; Bing maps; Google maps; OpenStreetMap; density mapping; track visualization; point density; animal density; software tools; R import; telemetry R package; data management tools; attribute dictionary; sensor calibration; duty cycle; outlier filtering; event visibility; deployment comments; data owner; permissions; data sharing; data archiving; study permissions; animal metadata; tag metadata; deployment metadata; behavioral classification; habitat data; animal life stage; tag readout method; satellite uplink; phone network; data processing software; Wildlife movement; migration; animals; animal health; movement ecology; location data; GPS telemetry; tracking collars; tracking devices; biologging sensors; animal behavior monitoring; spatial tracking; remote sensing data; wildlife monitoring; movement patterns; seasonal migration; habitat use; animal migration routes; tracking accuracy; positional data; data filtering; location uncertainty; movement modeling; home range analysis; path analysis; animal speed; animal orientation; tracking frequency; tag battery life; sensor fusion; data interpolation; real-time tracking; animal tracking studies; tracking dataset; tag performance; data visualization tools; migration corridors; movement hotspots; habitat connectivity; spatial ecology; animal tracking software; open tracking data; tracking database; data standardization; movement data analysis; tracking metadata standards; GPS error correction; tag deployment protocols; animal tag retrieval; study design; multi-species tracking; tag sensor data; biologging data formats; animal location services; tag signal strength; telemetry project; movement data archive; wildlife tracking projects; animal path reconstruction; behavioral states; accelerometer data; magnetometer calibration; animal activity patterns; tracking ethics; species migration timing; biodiversity; Historic; Current; Present; 1965 - 2025</t>
+          <t>animal tracking; animal movement; telemetry data; tracking map; Movebank; GPS locations; Argos tags; VHF telemetry; sensor data; bio-logging; acceleration; magnetometer; barometer; temperature sensor; light-level sensor; satellite tracking; radio transmitter; animal deployments; deployment period; tag deployment; tag model; tag manufacturer; tag attachment; collar tag; harness tag; implant tag; tape tag; event data; timestamped locations; timestamped events; animal ID; tag ID; deployment ID; taxon; species tracking; genus tracking; family tracking; ITIS taxonomy; study metadata; study site; study name; sensor type filter; live data feed; public data access; restricted access data; data download; CSV download; Excel download; shapefile; KML export; REST API; MoveApps; EnvDATA; ECODATA; interactive map; map basemaps; Bing maps; Google maps; OpenStreetMap; density mapping; track visualization; point density; animal density; software tools; R import; telemetry R package; data management tools; attribute dictionary; sensor calibration; duty cycle; outlier filtering; event visibility; deployment comments; data owner; permissions; data sharing; data archiving; study permissions; animal metadata; tag metadata; deployment metadata; behavioral classification; habitat data; animal life stage; tag readout method; satellite uplink; phone network; data processing software; Wildlife movement; migration; animals; animal health; movement ecology; location data; GPS telemetry; tracking collars; tracking devices; biologging sensors; animal behavior monitoring; spatial tracking; remote sensing data; wildlife monitoring; movement patterns; seasonal migration; habitat use; animal migration routes; tracking accuracy; positional data; data filtering; location uncertainty; movement modeling; home range analysis; path analysis; animal speed; animal orientation; tracking frequency; tag battery life; sensor fusion; data interpolation; real-time tracking; animal tracking studies; tracking dataset; tag performance; data visualization tools; migration corridors; movement hotspots; habitat connectivity; spatial ecology; animal tracking software; open tracking data; tracking database; data standardization; movement data analysis; tracking metadata standards; GPS error correction; tag deployment protocols; animal tag retrieval; study design; multi-species tracking; tag sensor data; biologging data formats; animal location services; tag signal strength; telemetry project; movement data archive; wildlife tracking projects; animal path reconstruction; behavioral states; accelerometer data; magnetometer calibration; animal activity patterns; tracking ethics; species migration timing; biodiversity; Historic; Current; Present; 1965 - 2025; Move Bank Data Repository; Move Bank; Movebank Data Repository; Move BON; Animal Movement Biodiversity Observation Network; GEO BON; Euromammals; EURODEER; EUROBOAR; EUROLYNX; EUROWILDCAT; EUREDDEER; EUROIBEX; roe deer; wild boar; Eurasian lynx; European mammals; MoveDisease Archive; Move Disease Archive; wildlife disease; pathogen diagnostics; Max Planck Institute of Animal Behavior; Senckenberg</t>
         </is>
       </c>
       <c r="M22" s="16" t="inlineStr">
         <is>
-          <t>The Movebank Tracking Data Map is an interactive platform that allows users to search, visualize, and explore animal movement data from over 9,000 studies worldwide, offering tools to filter by species, sensor type, and study access permissions, and enabling users to view and download available tracking data for scientific research.
+          <t>The Movebank Tracking Data Map is an interactive platform that allows users to search, visualize, and explore animal movement data from over 9,000 studies worldwide, offering tools to filter by species, sensor type, and study access permissions, and enabling users to view and download available tracking data for scientific research. Movebank also connects to related networks: GEO BON's Animal Movement Biodiversity Observation Network (Move BON), the European Euromammals consortium (EURODEER, EUROBOAR, EUROLYNX and others, whose dataset descriptions are searchable from Movebank), and the emerging MoveDisease Archive, a discovery index of movement-plus-pathogen datasets developed with Movebank that hosts no data itself.
 #### Host Organization
 - Movebank for Animal Tracking Data
 #### Data Format
@@ -2552,7 +2552,7 @@
 - Public*
 	- *Must agree to user agreement, but no log in required.
 #### Citation Information
-- Follow the instructions on the [Move Bank Citation Guidelines Page](https://www.movebank.org/cms/movebank-content/citation-guidelines)
+- Follow the instructions on the [Movebank Citation Guidelines Page](https://www.movebank.org/cms/movebank-content/citation-guidelines)
 - See specific source citation details on the database website.</t>
         </is>
       </c>
@@ -6488,20 +6488,87 @@
       <c r="AB65" s="2" t="n"/>
     </row>
     <row r="66" ht="14.25" customHeight="1">
-      <c r="A66" s="1" t="n"/>
-      <c r="B66" s="1" t="n"/>
-      <c r="C66" s="1" t="n"/>
-      <c r="D66" s="3" t="n"/>
-      <c r="E66" s="1" t="n"/>
-      <c r="F66" s="1" t="n"/>
-      <c r="G66" s="1" t="n"/>
+      <c r="A66" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="1" t="inlineStr">
+        <is>
+          <t>WorldClim</t>
+        </is>
+      </c>
+      <c r="C66" s="1" t="inlineStr">
+        <is>
+          <t>WorldClim: free UC Davis global climate rasters for species distribution, disease risk, and ecosystem modeling</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>https://www.worldclim.org/</t>
+        </is>
+      </c>
+      <c r="E66" s="1" t="inlineStr">
+        <is>
+          <t>Ecosystems; Animals</t>
+        </is>
+      </c>
+      <c r="F66" s="1" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="G66" s="1" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
       <c r="H66" s="1" t="n"/>
-      <c r="I66" s="1" t="n"/>
-      <c r="J66" s="1" t="n"/>
-      <c r="K66" s="3" t="n"/>
-      <c r="L66" s="1" t="n"/>
-      <c r="M66" s="3" t="n"/>
-      <c r="N66" s="1" t="n"/>
+      <c r="I66" s="1" t="n">
+        <v>1950</v>
+      </c>
+      <c r="J66" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>Long Term Weather Trends; Weather; Ecosystem Data; Species Distribution; Biological Variability; Conservation</t>
+        </is>
+      </c>
+      <c r="L66" s="1" t="inlineStr">
+        <is>
+          <t>WorldClim; World Climate Data; WorldClim 2; WorldClim 2.1; WorldClim 1.4; worldclim.org; geodata.ucdavis.edu; wc2.1; University of California Davis; UC Davis; Department of Environmental Science and Policy; Robert Hijmans; Stephen Fick; Climatic Research Unit; CRU TS; CRU-TS 4.09; University of East Anglia; CMIP6; Coupled Model Intercomparison Project; PCMDI; climate; climate data; weather; temperature; minimum temperature; maximum temperature; mean temperature; precipitation; rainfall; solar radiation; wind speed; water vapor pressure; vapour pressure; elevation; bioclimatic variables; bioclim; BIO1; BIO12; annual mean temperature; annual precipitation; temperature seasonality; precipitation seasonality; isothermality; diurnal range; climatology; climate normals; climate surfaces; climate projections; future climate; climate scenarios; climate change; SSP; SSP126; SSP245; SSP370; SSP585; shared socioeconomic pathways; global climate models; GCM; downscaling; bias correction; interpolation; thin plate splines; gridded data; raster; GeoTIFF; ESRI grid; GIS; QGIS; ArcGIS; terra; raster package; geodata package; dismo; Google Earth Engine; rasterio; spatial modeling; species distribution modeling; SDM; ecological niche modeling; MaxEnt; habitat suitability; vector-borne disease; mosquito; tick; disease ecology; climate envelope; biodiversity; ecology; agriculture; crop suitability; hydrology; land surface; Long Term Weather Trends; Weather; Ecosystem Data; Species Distribution; Biological Variability; Conservation; Wildlife; Global; worldwide; land areas; 30 arc-seconds; 1 km; 10 arc-minutes; 2.5 arc-minutes; 5 arc-minutes; 1970-2000; 1960-1990; 1950-2024; 2021-2040; 2041-2060; 2061-2080; 2081-2100; historical; monthly; time series; Fick and Hijmans 2017; Hijmans et al. 2005; International Journal of Climatology; CHELSA; PRISM; TerraClimate; NCEI; NASA Earthdata; Historic; Current; Present; 1950 - 2026</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>WorldClim is a database of high-resolution gridded global climate and weather data developed and maintained at the University of California, Davis (Robert J. Hijmans lab). Version 2.1 (January 2020) provides 1970-2000 monthly climatologies for temperature, precipitation, solar radiation, wind speed and water vapor pressure plus 19 bioclimatic variables at four resolutions from 30 arc-seconds (~1 km) to 10 arc-minutes, alongside monthly weather layers for 1950-2024 (downscaled from CRU TS 4.09) and CMIP6 future projections for more than 20 global climate models under four SSP scenarios out to 2100. All products are free GeoTIFF downloads for academic and non-commercial use and can be pulled directly in R with the geodata package. WorldClim's bioclimatic layers are the standard environmental covariates for species-distribution and vector-borne disease models, so they pair naturally with occurrence data from the Global Biodiversity Information Facility, animal tracking in Movebank, ecological observations from NEON, and observed station climate from the National Centers for Environmental Information (all cataloged separately). Note that precipitation surfaces are smoothest where weather stations are sparse, such as mountainous terrain, and should be cross-checked locally where that matters; the documentation site displays third-party ads, while the data files themselves are hosted by UC Davis.
+#### Host Organization
+- University of California, Davis (Department of Environmental Science and Policy; Robert J. Hijmans lab); files served from UC Davis geodata servers
+	- Monthly weather derived from CRU TS 4.09 (Climatic Research Unit, University of East Anglia); future projections from CMIP6
+#### Data Format
+- **GeoTIFF** rasters packaged in ZIP files, one layer per month or per bioclimatic variable
+- Programmatic download in R via the **geodata** package (`worldclim_global()`, `worldclim_country()`, `cmip6_world()`)
+#### How to access data of interest
+- Choose a product on the [WorldClim data page](https://www.worldclim.org/data/index.html): 1970-2000 climatologies and bioclimatic variables, 1950-2024 monthly weather, or CMIP6 future projections
+- Pick a variable and resolution on the product page, for example [Historical climate data (v2.1)](https://www.worldclim.org/data/worldclim21.html) or [Historical monthly weather](https://www.worldclim.org/data/monthlywth.html), and download the ZIP directly from the [UC Davis file server](https://geodata.ucdavis.edu/climate/worldclim/2_1/base/)
+- Or fetch layers in R with the [geodata package](https://rdrr.io/cran/geodata/man/worldclim.html)
+- Review the [licence terms](https://www.worldclim.org/about.html) (non-commercial use) and the [bioclimatic variable definitions](https://www.worldclim.org/data/bioclim.html) before use
+#### Database Time Range
+- 1950-2026
+	- Observed data cover 1950-2024 (monthly weather) and the 1970-2000 climatology; CMIP6 projections extend in 20-year periods to 2081-2100
+#### Access Type
+- Public
+	- No login; freely available for academic and other non-commercial use. Redistribution or commercial use requires prior permission
+#### Citation Information
+- Cite the product-specific paper shown on each [WorldClim data page](https://www.worldclim.org/data/worldclim21.html); the flagship paper is Fick, S.E. and R.J. Hijmans (2017), "WorldClim 2: new 1-km spatial resolution climate surfaces for global land areas," *International Journal of Climatology* 37(12): 4302-4315, &lt;https://doi.org/10.1002/joc.5086&gt;
+- University of California, Davis. "WorldClim." *WorldClim*, September 2026, &lt;https://www.worldclim.org/&gt;. 2026-09-02
+- See specific source citation details on the database website.</t>
+        </is>
+      </c>
+      <c r="N66" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
       <c r="O66" s="1" t="n"/>
       <c r="P66" s="1" t="n"/>
       <c r="Q66" s="1" t="n"/>
@@ -6518,20 +6585,88 @@
       <c r="AB66" s="2" t="n"/>
     </row>
     <row r="67" ht="14.25" customHeight="1">
-      <c r="A67" s="1" t="n"/>
-      <c r="B67" s="1" t="n"/>
-      <c r="C67" s="1" t="n"/>
-      <c r="D67" s="3" t="n"/>
-      <c r="E67" s="1" t="n"/>
-      <c r="F67" s="1" t="n"/>
-      <c r="G67" s="1" t="n"/>
+      <c r="A67" s="1" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="1" t="inlineStr">
+        <is>
+          <t>VectorSurv</t>
+        </is>
+      </c>
+      <c r="C67" s="1" t="inlineStr">
+        <is>
+          <t>VectorSurv: public maps and open-data extracts of mosquito abundance and arbovirus testing across 36 U.S. states</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>https://vectorsurv.org/</t>
+        </is>
+      </c>
+      <c r="E67" s="1" t="inlineStr">
+        <is>
+          <t>People; Animals</t>
+        </is>
+      </c>
+      <c r="F67" s="1" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="G67" s="1" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
       <c r="H67" s="1" t="n"/>
-      <c r="I67" s="1" t="n"/>
-      <c r="J67" s="1" t="n"/>
-      <c r="K67" s="3" t="n"/>
-      <c r="L67" s="1" t="n"/>
-      <c r="M67" s="3" t="n"/>
-      <c r="N67" s="1" t="n"/>
+      <c r="I67" s="1" t="n">
+        <v>2006</v>
+      </c>
+      <c r="J67" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>Vector-Borne Disease; Disease Surveillance; Infectious Disease Monitoring; Public Health; Animal Health; Wildlife</t>
+        </is>
+      </c>
+      <c r="L67" s="1" t="inlineStr">
+        <is>
+          <t>VectorSurv; Vectorborne Disease Surveillance System; CalSurv; California Vectorborne Disease Surveillance System; VectorSurv Maps; VectorSurv Gateway; VectorSurv Public Data Portal; VectorSurv Open Data Portal; vectorsurv.org; maps.vectorsurv.org; opendata.vectorsurv.org; gateway.vectorsurv.org; VectorSurv API; vectorsurvR; UC Davis; University of California Davis; Davis Arbovirus Research and Training; DART; UC Davis School of Veterinary Medicine; Department of Pathology Microbiology and Immunology; Regents of the University of California; CDC; Centers for Disease Control and Prevention; Division of Vector-Borne Diseases; DVBD; California Department of Public Health; CDPH; Mosquito and Vector Control Association of California; MVCAC; NASA Applied Sciences; NOAA; State of California; Mosquito; Mosquitoes; Mosquito Surveillance; Mosquito Abundance; Trap Counts; Mosquito Pools; Pool Testing; Arbovirus; Arboviruses; West Nile Virus; WNV; St. Louis Encephalitis; SLE; Western Equine Encephalitis; WEE; Dengue; Dengue Risk Index; Chikungunya; Zika; Invasive Mosquitoes; Aedes aegypti; Aedes albopictus; Aedes notoscriptus; Culex; Culex tarsalis; Culex pipiens; Sentinel Chickens; Sentinel Flocks; Dead Bird Surveillance; Dead Birds; Ticks; Tick Surveillance; Insecticide Resistance; Bottle Bioassay; Vector Control; Mosquito Control Districts; Vector-Borne Disease; Vectorborne Disease; Infection Rate; Minimum Infection Rate; Vector Index; Abundance Anomaly; Risk Assessment; CSV; Data Extract; Data Dictionary; REST API; JSON; R Package; CRAN; Interactive Map; Data Request Form; Surveillance; Entomological Surveillance; Vector Surveillance; RT-PCR; Trap Collections; Risk Modeling; R0; NLDAS; Land Surface Temperature; United States; California; Colorado; Arizona; New Jersey; North Carolina; Texas; Florida; Washington; Guam; Pacific Islands; Census County Subdivision; 2006; Weekly; Daily Updates; Real-time; ArboNET; CalSurv Gateway; RaHP VEC; Rockies and High Plains Vector-borne Diseases Center; PacVec; Pacific Southwest Center of Excellence in Vector-Borne Diseases; CDC Data; NNDSS; USGS WHISPers; Colorado Department of Public Health Open Data; Disease Surveillance; Infectious Disease Monitoring; Public Health; Animal Health; Species Distribution; Wildlife; Population Health; Historic; Current; Present; 2006 - 2026</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>VectorSurv (the Vectorborne Disease Surveillance System, formerly CalSurv) is a web platform run by the Davis Arbovirus Research and Training group at the University of California, Davis, in collaboration with the CDC Division of Vector-Borne Diseases, that has managed mosquito, tick and sentinel-flock surveillance data, plus arbovirus testing results, for local and state agencies since 2006. It now serves more than 390 agencies and 1,300 users across 36 U.S. states and territories, including Colorado, with public maps of arbovirus-positive samples, invasive *Aedes* detections and a weekly Dengue Risk Index, and a Public Data Portal through which researchers can request abundance and arbovirus-testing extracts; the Gateway, REST API and vectorsurvR package are reserved for participating agencies. For One Health work it links the vector and animal side of arbovirus ecology to human case reporting in CDC Data and the National Notifiable Diseases Surveillance System, and complements wildlife mortality records in USGS WHISPers (all cataloged separately). CSU's Rockies and High Plains Vector-borne Diseases Center (RaHP VEC) highlights VectorSurv on its surveillance resources page as a CDC-funded operational surveillance system.
+#### Host Organization
+- University of California, Davis, Davis Arbovirus Research and Training (DART), School of Veterinary Medicine, in collaboration with the CDC Division of Vector-Borne Diseases
+	- Funded by CDC, the State of California, NASA Applied Sciences, the Mosquito and Vector Control Association of California, and NOAA
+#### Data Format
+- **Interactive web maps** (arbovirus-positive samples, invasive *Aedes* detections, Dengue Risk Index by county subdivision)
+- **Data extracts** with a data dictionary (abundance and arbovirus testing) delivered through the Public Data Portal
+- **REST API** (JSON) and the **vectorsurvR** R package for participating agencies
+#### How to access data of interest
+- Browse current and historical arbovirus positives, invasive *Aedes* detections and the Dengue Risk Index on [VectorSurv Maps](https://maps.vectorsurv.org/) (no login; abundance, insecticide-resistance and WNV-risk layers require an agency login). The [Invasive Map](https://vectorsurv.org/docs/maps/invasive) and [Dengue Risk Map](https://vectorsurv.org/docs/maps/dengue) docs explain each layer
+- Request downloadable abundance or arbovirus-testing extracts through the [VectorSurv Public Data Portal](https://opendata.vectorsurv.org/): fill in the free request form (name, organization, purpose, states, species, trap types, years) and download from the link sent by email
+- Researchers affiliated with a participating vector-control or public-health agency can obtain Gateway and API access via the [Getting Started guide](https://vectorsurv.org/starting/), then use the [VectorSurv API](https://docs.api.vectorsurv.org/) or the [vectorsurvR package](https://vectorsurv.org/docs/vectorsurvr/)
+- Questions: help@vectorsurv.org
+#### Database Time Range
+- 2006-2026
+	- System launched in California in 2006; invasive-mosquito map refreshed daily, dengue risk weekly
+#### Access Type
+- Free Registration
+	- Maps are public with no login. Data extracts require a free request naming the requester and purpose; only data from agencies that have opted into open sharing are included, and use is limited to the stated purpose with no redistribution. California agency data additionally fall under the [CalSurv data policy](https://vectorsurv.org/assets/files/calsurv_data_policy.pdf) (2019), under which requests are reviewed by the CalSurv Steering Committee and intellectual property stays with the originating agencies. Gateway, API and R-package access are limited to participating agencies
+#### Citation Information
+- Cite as directed on the [Getting Started page](https://vectorsurv.org/starting/): VectorSurv Development Team. 2026. VectorSurv - Vectorborne Disease Surveillance System. URL: &lt;https://vectorsurv.org/&gt; [accessed 02 Sep 2026]; also acknowledge the contributing agencies named in your extract, per the [CalSurv data policy](https://vectorsurv.org/assets/files/calsurv_data_policy.pdf)
+- VectorSurv Development Team, University of California, Davis. "VectorSurv - Vectorborne Disease Surveillance System." *VectorSurv*, September 2026, &lt;https://vectorsurv.org/&gt;. 2026-09-02
+- See specific source citation details on the database website.</t>
+        </is>
+      </c>
+      <c r="N67" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
       <c r="O67" s="1" t="n"/>
       <c r="P67" s="1" t="n"/>
       <c r="Q67" s="1" t="n"/>
@@ -6548,20 +6683,88 @@
       <c r="AB67" s="2" t="n"/>
     </row>
     <row r="68" ht="14.25" customHeight="1">
-      <c r="A68" s="1" t="n"/>
-      <c r="B68" s="1" t="n"/>
-      <c r="C68" s="1" t="n"/>
-      <c r="D68" s="3" t="n"/>
-      <c r="E68" s="1" t="n"/>
-      <c r="F68" s="1" t="n"/>
-      <c r="G68" s="1" t="n"/>
+      <c r="A68" s="1" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="1" t="inlineStr">
+        <is>
+          <t>BEACON (Biothreats Emergence, Analysis and Communications Network)</t>
+        </is>
+      </c>
+      <c r="C68" s="1" t="inlineStr">
+        <is>
+          <t>BEACON is Boston University's free One Health outbreak surveillance feed: 3,000+ curated event reports since 2025</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>https://beaconbio.org/</t>
+        </is>
+      </c>
+      <c r="E68" s="1" t="inlineStr">
+        <is>
+          <t>People; Animals; Ecosystems</t>
+        </is>
+      </c>
+      <c r="F68" s="1" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="G68" s="1" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
       <c r="H68" s="1" t="n"/>
-      <c r="I68" s="1" t="n"/>
-      <c r="J68" s="1" t="n"/>
-      <c r="K68" s="3" t="n"/>
-      <c r="L68" s="1" t="n"/>
-      <c r="M68" s="3" t="n"/>
-      <c r="N68" s="1" t="n"/>
+      <c r="I68" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J68" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>Disease Surveillance; Infectious Disease Monitoring; Public Health; Animal Health; Population Health; Wildlife; Vector-Borne Disease</t>
+        </is>
+      </c>
+      <c r="L68" s="1" t="inlineStr">
+        <is>
+          <t>BEACON; Biothreats Emergence, Analysis and Communications Network; Biothreats Emergence Analysis and Communications Network; beaconbio.org; beaconbio; BEACON Outbreaks; Boston University; BU; Boston University Center on Emerging Infectious Diseases; CEID; BU CEID; Hariri Institute; Hariri Institute for Computing and Data Sciences; HealthMap; Boston Children's Hospital; Nahid Bhadelia; Britta Lassmann; John Brownstein; Yannis Paschalidis; Disease Surveillance; Infectious Disease Monitoring; Public Health; Animal Health; Population Health; Wildlife; Livestock; Vector-Borne Disease; Event-Based Surveillance; Epidemic Intelligence; Informal Surveillance; Outbreak Reports; Outbreak Alerts; Disease Reports; Disease Events; Disease Event Digest; Sentinel Cases; Emerging Infectious Diseases; Biothreats; Biosecurity; Health Security; Pandemic Preparedness; Early Warning; Avian Influenza; H5N1; HPAI; Measles; Dengue; Cholera; Ebola; Marburg; Mpox; Lassa Fever; Crimean-Congo Hemorrhagic Fever; CCHF; Rabies; Hantavirus; Tularemia; Norovirus; Salmonella; Foot-and-Mouth Disease; FMD; Marine Toxins; Undiagnosed Disease; Zoonotic Diseases; Vector-Borne Diseases; Foodborne Illness; Plant Diseases; Plant Pathogens; Environmental Health; Humans; Animals; Plants; Environment; PandemIQ Llama; Large Language Model; LLM; Artificial Intelligence; AI; Generative AI; Natural Language Processing; Human-in-the-Loop; Subject Matter Experts; SME; Outbreak Analysts; Editorial Review; Media Monitoring; News Reports; Social Media; Trusted Partners; Web Portal; Advanced Search; Pathogen Filter; Species Filter; Email Subscription; Email Digest; HTML; No Bulk Download; Global; Worldwide; 195 Countries; Africa; Americas; Asia; Europe; Oceania; Colorado; United States; 2025; 2026; Near Real Time; Daily; Weekly; ProMED; EIOS; Epidemic Intelligence from Open Sources; WHO; WOAH; World Organisation for Animal Health; CEPI; CDC; CDC Center for Forecasting and Outbreak Analytics; GeoSentinel; NETEC; Global TravEpiNet; One Health; Journal of Infectious Diseases; Historic; Current; Present; 2025 - 2026</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>The Biothreats Emergence, Analysis and Communications Network (BEACON) is a free, event-based surveillance program that publishes rapid, contextualized reports on emerging infectious disease events affecting humans, animals, plants and the environment worldwide. Launched in April 2025 and based at Boston University's Center on Emerging Infectious Diseases in partnership with the Hariri Institute and HealthMap at Boston Children's Hospital, BEACON pairs a domain-adapted large language model (PandemIQ Llama) with a global team of outbreak analysts and veterinary, medical and epidemiological subject-matter experts who verify every report before publication. As of September 2026 the site holds more than 3,000 reports grouped into hundreds of disease events, covering 195 countries and territories as of late 2025, searchable by pathogen, disease, region, species and date, with daily or weekly regional email digests. For One Health researchers it complements indicator-based systems such as the National Notifiable Diseases Surveillance System, the ECDC Surveillance Atlas, EMPRES-i and the World Organization for Animal Health (all cataloged separately) by surfacing informal, near-real-time signals, from H5N1 in dairy cattle and wild birds to measles clusters in Colorado, that often precede official reporting. Reports are read online only; there is no bulk download.
+#### Host Organization
+- Boston University Center on Emerging Infectious Diseases (CEID), operated in partnership with the Hariri Institute for Computing and Data Sciences (Boston University) and HealthMap (Boston Children's Hospital)
+	- Funded by the National Science Foundation, the Gates Foundation, the Chen Institute, Pax Sapiens, CEPI and Boston University
+#### Data Format
+- **Web reports** (HTML) with structured metadata: pathogen, disease, species, location, region, event date and sources; reports are grouped into Disease Events
+- **Email digests** (daily or weekly, by world region)
+- No CSV/JSON export, bulk download or public API
+#### How to access data of interest
+- Open the [Disease Reports listing](https://beaconbio.org/en/) and use the search box or "Show advanced search options" to filter by pathogen, disease, region, location, species and date range
+- Click a report title to read the full report, or its "Related Disease Event" link to see all reports on that outbreak; review the [Methods and citation guidance](https://beaconbio.org/en/about) before reusing content
+- Subscribe to [daily or weekly regional email digests](https://subscribe.beaconbio.org/beacon-email-subscription) to receive new reports
+- For reuse beyond personal browsing, or to share a signal, see the [Terms of Use](https://beaconcms-prod-media.s3.us-east-1.amazonaws.com/beacon_Terms_Of_Use_5fcf5061c1.pdf) and [contact BEACON](https://beaconbio.org/en/contact)
+#### Database Time Range
+- 2025-2026
+	- Earliest reports dated March 2025; platform launched 24 April 2025; updated daily
+#### Access Type
+- Public
+	- No login. Browse, search and cite only: Boston University's Terms of Use limit content to personal, non-commercial use and prohibit systematic retrieval; contact info@beaconbio.org about research data partnerships
+#### Citation Information
+- Follow the [How to cite BEACON](https://beaconbio.org/en/about) guidance: for a report, "Report Title." Event title (Disease, country). Biothreats Emergence, Analysis and Communications Network (BEACON). Boston University Center on Emerging Infectious Diseases. DD Month YYYY; for the platform, Bhadelia N, Paschalidis IC, Brownstein JS, Lassmann B. "A BEACON for Novel Disease Threats: Leveraging Artificial Intelligence for Informal Event-Based Outbreak Surveillance." *The Journal of Infectious Diseases* 233(2): e287-e289 (2026; published online December 2025), &lt;https://doi.org/10.1093/infdis/jiaf642&gt;
+- Boston University Center on Emerging Infectious Diseases. "Biothreats Emergence, Analysis and Communications Network (BEACON)." *BEACON*, September 2026, &lt;https://beaconbio.org/&gt;. 2026-09-02
+- See specific source citation details on the database website.</t>
+        </is>
+      </c>
+      <c r="N68" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
       <c r="O68" s="1" t="n"/>
       <c r="P68" s="1" t="n"/>
       <c r="Q68" s="1" t="n"/>
@@ -6578,20 +6781,88 @@
       <c r="AB68" s="2" t="n"/>
     </row>
     <row r="69" ht="14.25" customHeight="1">
-      <c r="A69" s="1" t="n"/>
-      <c r="B69" s="1" t="n"/>
-      <c r="C69" s="1" t="n"/>
-      <c r="D69" s="3" t="n"/>
-      <c r="E69" s="1" t="n"/>
-      <c r="F69" s="1" t="n"/>
-      <c r="G69" s="1" t="n"/>
+      <c r="A69" s="1" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="1" t="inlineStr">
+        <is>
+          <t>The GLOBE Program</t>
+        </is>
+      </c>
+      <c r="C69" s="1" t="inlineStr">
+        <is>
+          <t>GLOBE Program: NASA-sponsored global atmosphere, water, soil, land cover and mosquito habitat observations</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>https://www.globe.gov/globe-data</t>
+        </is>
+      </c>
+      <c r="E69" s="1" t="inlineStr">
+        <is>
+          <t>Ecosystems; Animals; People</t>
+        </is>
+      </c>
+      <c r="F69" s="1" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="G69" s="1" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
       <c r="H69" s="1" t="n"/>
-      <c r="I69" s="1" t="n"/>
-      <c r="J69" s="1" t="n"/>
-      <c r="K69" s="3" t="n"/>
-      <c r="L69" s="1" t="n"/>
-      <c r="M69" s="3" t="n"/>
-      <c r="N69" s="1" t="n"/>
+      <c r="I69" s="1" t="n">
+        <v>1995</v>
+      </c>
+      <c r="J69" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>Ecosystem Data; Weather; Air Quality; Water Quality; Hydrology; Vector-Borne Disease; Disease Surveillance</t>
+        </is>
+      </c>
+      <c r="L69" s="1" t="inlineStr">
+        <is>
+          <t>GLOBE; GLOBE Program; The GLOBE Program; Global Learning and Observations to Benefit the Environment; globe.gov; observer.globe.gov; GLOBE Data; GLOBE Data and Information System; GLOBE Observer; GLOBE Observer App; Mosquito Habitat Mapper; MHM; NASA; National Aeronautics and Space Administration; NOAA; National Science Foundation; NSF; U.S. Department of State; GLOBE Implementation Office; GIO; Education Development Center; EDC; City University of New York; CUNY; Mosquito; Mosquitoes; Mosquito Larvae; Larval Habitat; Aedes; Anopheles; Culex; Vector; Vector Surveillance; Vector-Borne Disease; Mosquito-Borne Disease; Dengue; Zika; Malaria; Arbovirus; Entomology; Atmosphere; Air Temperature; Barometric Pressure; Precipitation; Relative Humidity; Clouds; Aerosols; Aerosol Optical Depth; Wind; Dust; Hydrosphere; Water Temperature; pH; Dissolved Oxygen; Conductivity; Salinity; Nitrates; Freshwater Macroinvertebrates; Pedosphere; Soil; Soil Moisture; Soil Temperature; Biosphere; Land Cover; Land Cover Classification; Tree Height; Carbon Cycle; Phenology; Phenological Gardens; Earth as a System; CSV; JSON; GeoJSON; REST API; API; Python; Jupyter Notebook; Advanced Data Access Tool; ADAT; Visualization System; ArcGIS Online; Zenodo; Mobile App; Photos; Georeferenced; Citizen Science; Student Data; K-12; Schools; Teachers; Protocols; Field Observations; Ground Truth; Satellite Validation; Environmental Monitoring; Earth System Science; Quality Assurance; Global; International; 125 Countries; United States; Europe; Latin America; 1995; 2017; Since 1995; Ongoing; Low et al. 2021; GeoHealth; Adopt a Pixel; NASA Earthdata; Air Quality; Disease Surveillance; Ecosystem Data; Hydrology; Infectious Disease Monitoring; Public Health; Water Quality; Weather; Historic; Current; Present; 1995 - 2026</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>The GLOBE Program (Global Learning and Observations to Benefit the Environment) is a NASA-sponsored international science and education program, supported by NSF, NOAA and the U.S. Department of State, whose database holds more than 250 million environmental observations collected since 1995 by trained students and citizen scientists in over 125 countries. Data span more than 40 protocols across the atmosphere (temperature, precipitation, clouds, aerosols), hydrosphere (pH, dissolved oxygen, nitrates, macroinvertebrates), soils and biosphere (land cover, tree height, phenology), and are freely downloadable as CSV, JSON or GeoJSON or through an interactive map. Of particular One Health interest is the Mosquito Habitat Mapper, added to the GLOBE Observer app in 2017, in which volunteers georeference standing-water breeding sites, count larvae and identify *Aedes*, *Anopheles* and *Culex*: more than 24,000 submissions in its first three years, providing ground-level vector habitat data that complement case-based surveillance in CDC Data and the National Notifiable Diseases Surveillance System and satellite products in NASA Earthdata (all cataloged separately). As with all citizen-science data, records pass automated range and logic checks but vary in precision, so users should review the Data User Guide before analysis.
+#### Host Organization
+- The GLOBE Program, sponsored by NASA with support from NSF, NOAA and the U.S. Department of State
+	- Operated by the GLOBE Implementation Office (Education Development Center and the City University of New York, under a NASA cooperative agreement)
+#### Data Format
+- **CSV** via the Advanced Data Access Tool and the Visualization System (which also offers graphs, KML and ArcGIS Online export)
+- **REST API** returning **JSON or GeoJSON** (up to 1,000,000 records per query), with sample Python notebooks
+- Curated snapshots (e.g., Mosquito Habitat Mapper 2017-2020, CC BY 4.0) as CSV on Zenodo; photos as JPG
+#### How to access data of interest
+- Read the [GLOBE Data User Guide](https://www.globe.gov/globe-data/globe-data-user-guide) for protocol variables, metadata fields and known data caveats
+- Explore and download by protocol, place and date in the [GLOBE Visualization System](https://vis.globe.gov/GLOBE/) (map, graphs, CSV export) or use the [Advanced Data Access Tool](https://www.globe.gov/globe-data/retrieve-data) for bulk CSV downloads
+- For programmatic access, query the [GLOBE REST API](https://www.globe.gov/globe-data/globe-api) (JSON/GeoJSON) using the [sample Python notebooks](https://www.globe.gov/globe-data/globe-data-user-guide/-/wiki/Main/Python+Notebook+Samples)
+- For mosquito data specifically, see the [Mosquito Habitat Mapper data page](https://observer.globe.gov/get-data/mosquito-habitat-data) for cleaned CSV releases and the [2017-2020 Zenodo dataset](https://doi.org/10.5281/zenodo.5106571)
+#### Database Time Range
+- 1995-2026
+	- Measurements date back to spring 1995; Mosquito Habitat Mapper data begin in 2017; new observations are typically posted about a month after collection
+#### Access Type
+- Public
+	- No account required; data are open for research, publications and commercial applications under NASA's Earth Science data policy. Downloads are capped at 1,000,000 records per request; narrow the query or contact help@nasaglobe.org for assistance
+#### Citation Information
+- Follow the guidance in the [GLOBE Data User Guide](https://www.globe.gov/globe-data/globe-data-user-guide): cite as "Global Learning and Observations to Benefit the Environment (GLOBE) Program, [date accessed], &lt;https://www.globe.gov/globe-data&gt;" and acknowledge GLOBE's sponsors (NASA, with support from NSF, NOAA and the U.S. Department of State) as described in the guide. The Mosquito Habitat Mapper data paper is Low, R., Boger, R., Nelson, P., and Kimura, M. (2021), "GLOBE Mosquito Habitat Mapper Citizen Science Data 2017-2020," *GeoHealth* 5(10): e2021GH000436, &lt;https://doi.org/10.1029/2021GH000436&gt;
+- The GLOBE Program. "GLOBE Data." *Global Learning and Observations to Benefit the Environment (GLOBE) Program*, September 2026, &lt;https://www.globe.gov/globe-data&gt;. 2026-09-02
+- See specific source citation details on the database website.</t>
+        </is>
+      </c>
+      <c r="N69" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
       <c r="O69" s="1" t="n"/>
       <c r="P69" s="1" t="n"/>
       <c r="Q69" s="1" t="n"/>
@@ -6608,20 +6879,88 @@
       <c r="AB69" s="2" t="n"/>
     </row>
     <row r="70" ht="14.25" customHeight="1">
-      <c r="A70" s="1" t="n"/>
-      <c r="B70" s="1" t="n"/>
-      <c r="C70" s="1" t="n"/>
-      <c r="D70" s="3" t="n"/>
-      <c r="E70" s="1" t="n"/>
-      <c r="F70" s="1" t="n"/>
-      <c r="G70" s="1" t="n"/>
+      <c r="A70" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="1" t="inlineStr">
+        <is>
+          <t>PADI-web (Platform for Automated extraction of Disease Information from the web)</t>
+        </is>
+      </c>
+      <c r="C70" s="1" t="inlineStr">
+        <is>
+          <t>PADI-web mines online news in 28 languages to detect and map animal, plant and human disease outbreaks worldwide</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>https://padi-web.cirad.fr/en/</t>
+        </is>
+      </c>
+      <c r="E70" s="1" t="inlineStr">
+        <is>
+          <t>Animals; People; Ecosystems</t>
+        </is>
+      </c>
+      <c r="F70" s="1" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="G70" s="1" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
       <c r="H70" s="1" t="n"/>
-      <c r="I70" s="1" t="n"/>
-      <c r="J70" s="1" t="n"/>
-      <c r="K70" s="3" t="n"/>
-      <c r="L70" s="1" t="n"/>
-      <c r="M70" s="3" t="n"/>
-      <c r="N70" s="1" t="n"/>
+      <c r="I70" s="1" t="n">
+        <v>2016</v>
+      </c>
+      <c r="J70" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>Disease Surveillance; Infectious Disease Monitoring; Animal Health; Public Health; Livestock; Wildlife; Agriculture</t>
+        </is>
+      </c>
+      <c r="L70" s="1" t="inlineStr">
+        <is>
+          <t>PADI-web; Platform for Automated extraction of Disease Information from the web; Platform for Automated extraction of animal Disease Information from the web; PADI-web 3.0; PADI-web One Health; padi-web.cirad.fr; padi-web-one-health.org; Plant Health PADI-web; Public Health PADI-web; CIRAD; French Agricultural Research Centre for International Development; UMR TETIS; UMR ASTRE; INRAE; ANSES; DGAL; ESA Platform; Plateforme ESA; French Animal Health Epidemiological Surveillance Platform; Veille Sanitaire Internationale; VSI; MOOD; MOOD H2020; MOnitoring Outbreaks for Disease surveillance; Horizon 2020; Montpellier; France; African swine fever; ASF; avian influenza; highly pathogenic avian influenza; HPAI; bird flu; bluetongue; foot-and-mouth disease; FMD; West Nile virus; Zika; Schmallenberg; Rift Valley fever; Crimean-Congo haemorrhagic fever; lumpy skin disease; peste des petits ruminants; Nipah; Usutu; tick-borne encephalitis; tularaemia; leptospirosis; brucella; coronavirus; emerging diseases; zoonotic disease; transboundary animal diseases; Xylella fastidiosa; Fusarium; plant pests; plant pathogens; outbreaks; epidemiological events; symptoms; event-based surveillance; EBS; epidemic intelligence; biosurveillance; web monitoring; news monitoring; online news; Google News; RSS feeds; text mining; natural language processing; NLP; machine learning; BERT; sentiment analysis; topic classification; named entity recognition; information extraction; geocoding; multilingual; machine translation; 28 languages; CSV; XLSX; Excel; JSON; HTML; JSON API; REST API; email notifications; alerts; daily notifications; weekly notifications; Dataverse; annotated corpus; labelled dataset; web interface; Global; worldwide; Europe; Africa; Asia; Americas; 2016; since 2016; 490,000 articles; near real-time; daily updates; One Health; syndromic surveillance; Disease Surveillance; Infectious Disease Monitoring; Animal Health; Public Health; Livestock; Wildlife; Agriculture; Plant Health; Veterinary Epidemiology; EMPRES-i; WOAH; WAHIS; ProMED; HealthMap; EIOS; BEACON; Historic; Current; Present; 2016 - 2026</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>PADI-web (Platform for Automated extraction of Disease Information from the web) is an event-based biosurveillance system developed by CIRAD's TETIS and ASTRE research units in Montpellier, France, and integrated into the French Animal Health Epidemiological Surveillance Platform (ESA). It retrieves news articles from Google News via RSS feeds in 28 languages, translates them, and uses machine learning and text mining to classify their relevance and extract diseases, dates, symptoms, hosts and locations: more than 490,000 articles since 2016, with companion instances for plant health and public health. The public interface lets you filter reports by disease (African swine fever, avian influenza, bluetongue, foot-and-mouth disease, West Nile, Zika and more), continent, topic, sentiment and surveillance theme, while extended historical data, fuller exports and email alerts are available on request. Because it captures unofficial signals often days before formal notification, PADI-web complements the official outbreak records in EMPRES-i and the World Organization for Animal Health, and sits alongside BEACON as this catalog's event-based surveillance sources (all cataloged separately). Note that its content is news text with machine-extracted fields, not verified case data.
+#### Host Organization
+- CIRAD (French Agricultural Research Centre for International Development), UMR TETIS and UMR ASTRE, Montpellier, France, in partnership with the French Animal Health Epidemiological Surveillance Platform (ESA)
+	- Developed with support from CIRAD, INRAE, the French Ministry of Agriculture (DGAL) and the EU Horizon 2020 MOOD project
+#### Data Format
+- **Web interface**: filterable article list with machine-assigned disease, location, relevance, topic and sentiment labels
+- **Data exports** from the article browser, plus configurable **email notifications**; fuller exports and programmatic access come with extended access
+- Annotated training corpora published on CIRAD Dataverse
+#### How to access data of interest
+- Open the [PADI-web article browser](https://padi-web.cirad.fr/en/articles/) and filter by disease, continent, relevance, topic, sentiment or surveillance theme; no login required
+- For plant or human health news, use the sibling instances [Plant Health PADI-web](https://plant.padi-web.cirad.fr/) and [Public Health PADI-web](https://public-health.padi-web.cirad.fr/)
+- For full historical data, fuller exports or email alerts, request extended access from the team at padi-web@cirad.fr (see the [PADI-web homepage](https://padi-web.cirad.fr/en/))
+- Read the methods and publications on the [About Us page](https://padi-web.cirad.fr/en/about/)
+#### Database Time Range
+- 2016-2026
+	- Articles collected daily since 2016; the public view shows recent articles, with the full archive available on request
+#### Access Type
+- Public*
+	- *A limited version is free to browse without login for research or web monitoring; extended data, exports and API access are granted by request to CIRAD via a sign-in account
+#### Citation Information
+- CIRAD asks users to cite the project; the reference paper is Valentin, S., Arsevska, E., Rabatel, J., Falala, S., Mercier, A., Lancelot, R., and Roche, M. (2021), "PADI-web 3.0: A new framework for extracting and disseminating fine-grained information from the news for animal disease surveillance," *One Health* 13: 100357, &lt;https://doi.org/10.1016/j.onehlt.2021.100357&gt; (see the [About Us page](https://padi-web.cirad.fr/en/about/))
+- CIRAD. "PADI-web (Platform for Automated extraction of Disease Information from the web)." *PADI-web*, September 2026, &lt;https://padi-web.cirad.fr/en/&gt;. 2026-09-02
+- See specific source citation details on the database website.</t>
+        </is>
+      </c>
+      <c r="N70" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
       <c r="O70" s="1" t="n"/>
       <c r="P70" s="1" t="n"/>
       <c r="Q70" s="1" t="n"/>

--- a/datasets.xlsx
+++ b/datasets.xlsx
@@ -3912,7 +3912,7 @@
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
-          <t>Global; United States</t>
+          <t>United States; Global</t>
         </is>
       </c>
       <c r="H38" s="12" t="n"/>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="G48" s="1" t="inlineStr">
         <is>
-          <t>Global; United States</t>
+          <t>United States; Global</t>
         </is>
       </c>
       <c r="H48" s="1" t="n"/>
@@ -4915,7 +4915,7 @@
       </c>
       <c r="G49" s="1" t="inlineStr">
         <is>
-          <t>Global; United States</t>
+          <t>United States; Global</t>
         </is>
       </c>
       <c r="H49" s="1" t="n"/>
@@ -5103,7 +5103,7 @@
       </c>
       <c r="G51" s="1" t="inlineStr">
         <is>
-          <t>Global; United States</t>
+          <t>United States; Global</t>
         </is>
       </c>
       <c r="H51" s="1" t="n"/>
@@ -5952,7 +5952,7 @@
       </c>
       <c r="G60" s="1" t="inlineStr">
         <is>
-          <t>Global; United States</t>
+          <t>United States; Global</t>
         </is>
       </c>
       <c r="H60" s="1" t="n"/>
@@ -6141,7 +6141,7 @@
       </c>
       <c r="G62" s="1" t="inlineStr">
         <is>
-          <t>Global; United States</t>
+          <t>United States; Global</t>
         </is>
       </c>
       <c r="H62" s="1" t="n"/>

--- a/datasets.xlsx
+++ b/datasets.xlsx
@@ -798,7 +798,7 @@
 - Public
 #### Citation Information
 - Follow the instructions on the [Citing The IUCN RedList Site](https://www.iucnredlist.org/about/citationinfo)
-- IUCN (International Union for Conservation of Nature). 2025. Spatial Data Download. *The IUCN Red List of Threatened Species*. Version 2025‑2. &lt;https://www.iucnredlist.org/resources/spatial‑data‑download&gt;.
+- IUCN (International Union for Conservation of Nature). 2025. Spatial Data Download. *The IUCN Red List of Threatened Species*. Version 2025-2. &lt;https://www.iucnredlist.org/resources/spatial-data-download&gt;.
 - See specific source citation details on the database website.</t>
         </is>
       </c>
@@ -1230,7 +1230,7 @@
 #### Access Type
 - Public
 #### Citation Information
-- Colorado Department of Public Health &amp; Environment (CDPHE). “Colorado Open Data Portal.” *data‑cdphe.opendata.arcgis.com*, accessed  July 2025, &lt;https://data‑cdphe.opendata.arcgis.com/&gt;.
+- Colorado Department of Public Health &amp; Environment (CDPHE). “Colorado Open Data Portal.” *data-cdphe.opendata.arcgis.com*, accessed  July 2025, &lt;https://data-cdphe.opendata.arcgis.com/&gt;.
 - See specific source citation details on the database website.</t>
         </is>
       </c>
@@ -1322,7 +1322,7 @@
 #### Access Type
 - Public
 #### Citation Information
-- Colorado Department of Public Health &amp; Environment (CDPHE). “Child Health Indicators Dashboard.” *Colorado Health Dashboard*, accessed July 2025, &lt;https://cohealthviz.dphe.state.co.us/t/HSEBPublic/views/CHIDashboard_2024Redesign/CHILandingPage?%3Aembed=y&amp;%3AisGuestRedirectFromVizportal=y&gt;.
+- Colorado Department of Public Health &amp; Environment (CDPHE). “Child Health Indicators Dashboard.” *Colorado Health Dashboard*, accessed July 2025, &lt;https://cohealthviz.dphe.state.co.us/t/HSEBPublic/views/CHIDashboard_2024Redesign/CHILandingPage?%3Aembed=y&amp;%3AisGuestRedirectFromVizportal=y&gt;.
 - See specific source citation details on the database website.</t>
         </is>
       </c>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="M10" s="16" t="inlineStr">
         <is>
-          <t>EMPRES‑i is FAO’s global animal disease information system that collects, verifies, and maps up-to-date “disease event” data - sourced from national governments, field reports, media and surveillance systems - and is integrated with layers like livestock density and environmental factors to support disease prevention, control strategies, and early warning for disease outbreaks. Field reports from veterinary field officers can be submitted through FAO's companion mobile app, EMA-i+ (Event Mobile Application); those national data are shared to the global EMPRES-i+ only at each country's discretion.
+          <t>EMPRES-i is FAO’s global animal disease information system that collects, verifies, and maps up-to-date “disease event” data - sourced from national governments, field reports, media and surveillance systems - and is integrated with layers like livestock density and environmental factors to support disease prevention, control strategies, and early warning for disease outbreaks. Field reports from veterinary field officers can be submitted through FAO's companion mobile app, EMA-i+ (Event Mobile Application); those national data are shared to the global EMPRES-i+ only at each country's discretion.
 #### Host Organization
 - Food and Agricultural Organization of the United Nations - Global Animal Disease Information System
 #### Data Format
@@ -1497,7 +1497,7 @@
 #### Access Type
 - Public
 #### Citation Information
-- Food and Agriculture Organization of the United Nations. (n.d.). *EMPRES‑i: Global Animal Disease Information System*. Retrieved from &lt;https://empres‑i.apps.fao.org/general&gt;
+- Food and Agriculture Organization of the United Nations. (n.d.). *EMPRES-i: Global Animal Disease Information System*. Retrieved from &lt;https://empres-i.apps.fao.org/general&gt;
 - See specific source citation details on the database website.</t>
         </is>
       </c>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="M11" s="25" t="inlineStr">
         <is>
-          <t>NOWDATA provides a range of preliminary local climatological data—such as daily and monthly temperature (max/min/avg), precipitation, degree‑day summaries, record events, and more—via curated reports and links to detailed datasets and archives.
+          <t>NOWDATA provides a range of preliminary local climatological data—such as daily and monthly temperature (max/min/avg), precipitation, degree-day summaries, record events, and more—via curated reports and links to detailed datasets and archives.
 #### Host Organization
 - National Weather Service
 - National Oceanic and Atmospheric Administration
@@ -1745,12 +1745,12 @@
       </c>
       <c r="L13" s="24" t="inlineStr">
         <is>
-          <t>PNNL; Pacific Northwest National Laboratory; Scientific Discovery; Biology; Earth System Science; Human Health; Integrative Omics; Microbiome Science; National Security; Computational Research; Computing &amp; Analytics; Chemical &amp; Biological Signatures; Energy Resiliency; Materials Science; Chemistry; Data Analytics &amp; Machine Learning; Computational Math &amp; Statistics; Atmospheric Science; Renewable Energy; Visual Analytics; Coastal Science; Ecosystem Science; Energy Storage; Plant Science; Solar Energy; Bioenergy Technologies; Cybersecurity; Distribution; Electric Grid Modernization; Energy Efficiency; Grid Cybersecurity; Transportation; Subsurface Science; Terrestrial Aquatics; Wind Energy; Dataset; Publication; Project; Data Source; Person; Institution; Software; Resource; Guide; Method; Virology; Immune Response; Time-sampled Measurement; Differential Expression; Gene Expression; Mass Spectrometry; Multi‑Omics; Virus; MERS‑CoV; Mus musculus; West Nile virus; Influenza A; Ebola; High-throughput Sequencing; Metagenomics; Soil Microbiology; Proteomics; Genomics; Sequencing; Synthetic Data; HDF5; CSV; Globus; Remote Sensing; Large Eddy Simulation; Hydrologic Modeling; Transmissivity Fields; Land Surface Parameters; Tropical Cyclone Tracks; Hydraulic Pressure Fields; PFAS Spectra; Aerosol Modeling; LES; Climate Modeling; Hydrometeorology; Soil Moisture Products; Energy Vulnerability Index; Urban Energy Insecurity; Rooftop Solar; Weatherization; Friction Stir Welding; MCPC Characterization; Chitin Decomposition; Electric Vulnerability; Personal Chemical Exposure; Proteome Profiling; Metabolomics; Lipidomics; Hi-C Metagenomics; Hydraulic Transmissivity; Pressure Field Outputs; Q Exactive Plus; Illumina HiSeq X; Illumina MiSeq; Q Exactive GC Orbitrap; Synchrotron XPS; FTICR Mass Spectrometer; Orbitrap Mass Spec; Epifluorescence Microscopy; X-ray Diffraction; Electricity; Susceptability; Storms; Atmospheric Shift; Ecological changes; Weather pattern disruption; power; United States; policy; scientific data; research data; environmental data; climate data; energy data; experimental data; modeling data; simulation data; data repository; open data; data download; data analysis; geospatial data; atmospheric data; hydrological data; renewable energy data; greenhouse gas data; carbon emissions; water quality; soil data; weather data; sensor data; time series data; laboratory data; field data; data visualization; metadata; scientific research; computational modeling; data sharing; research collaboration; experimental results; project data; scientific computing; environmental monitoring; data standards; data quality; scientific datasets; research datasets; open science; big data; data curation; data management; scientific workflows; technology development; energy systems; PNNL research; grid resilience; electrical infrastructure; climate resilience; extreme weather impacts; energy reliability; electric grid modeling; transmission systems; storm vulnerability; infrastructure risk assessment; smart grid data; grid modernization; energy disruption; blackout analysis; grid hardening; weather-resilient energy systems; data science in energy; high-performance computing; environmental modeling; atmospheric simulations; integrated assessment models; hydrometeorological data; scientific data interoperability; FAIR data principles; scientific data infrastructure; observational data; multivariate data; climate projections; decarbonization data; clean energy transition; climate science; environmental risk assessment; renewable integration; simulation output data; scientific reproducibility; sensor networks; field campaign data; system dynamics modeling; data provenance; collaborative research platforms; cloud-based data systems; DOE data initiatives; research instrumentation; experimental protocols; model validation data; scientific metadata standards; sustainability data; knowledge discovery; interdisciplinary research; research metadata; scientific benchmarking; open access data; DOE National Labs; environmental resilience; climate adaptation; decarbonization strategies; bioinformatics; energy forecasting; grid optimization; power systems; molecular biology; energy transition; hydrogen economy; clean tech; carbon capture; carbon sequestration; electrification; precision agriculture; environmental genomics; environmental chemistry; advanced materials; battery innovation; smart sensors; AI in science; machine learning models; deep learning applications; real-time data; edge computing; high-resolution modeling; predictive modeling; climate impact modeling; earth observation; remote labs; sample metadata; environmental DNA; metatranscriptomics; host-pathogen interaction; zoonotic viruses; air quality; pollutant tracking; chemical forensics; forensic science; biodefense; cyberinfrastructure; quantum computing; supercomputing; exascale computing; digital twin; scientific visualization; temporal datasets; spatial datasets; climate justice; energy equity; environmental equity; equity mapping; urban analytics; green infrastructure; infrastructure monitoring; environmental sensors; sensor fusion; satellite data; UAV data; drone mapping; climate informatics; data pipelines; data integration; bioinformatics pipelines; multi-scale modeling; decision support systems; resilience planning; vulnerability mapping; water-energy nexus; carbon intensity; grid decarbonization; storm modeling; extreme heat modeling; natural hazards; wildfire risk; air-sea interactions; boundary layer dynamics; data governance; research reproducibility; cyber-physical systems; science policy interface; DOE Office of Science; science communication; national lab collaboration; translational research; multidisciplinary research; climate-smart innovation; life cycle assessment; circular economy; low-carbon technologies; just energy transition; infrastructure resilience; distributed energy resources; grid flexibility; data-driven insights; scientific platforms; experimental facilities; research tools; analytic workflows; data catalogs; open-access repositories; big data analytics; scientific code; software tools; FAIR principles; data interoperability; scientific archives; data lifecycle management; Historic; Current; Present; 2019 - 2025</t>
+          <t>PNNL; Pacific Northwest National Laboratory; Scientific Discovery; Biology; Earth System Science; Human Health; Integrative Omics; Microbiome Science; National Security; Computational Research; Computing &amp; Analytics; Chemical &amp; Biological Signatures; Energy Resiliency; Materials Science; Chemistry; Data Analytics &amp; Machine Learning; Computational Math &amp; Statistics; Atmospheric Science; Renewable Energy; Visual Analytics; Coastal Science; Ecosystem Science; Energy Storage; Plant Science; Solar Energy; Bioenergy Technologies; Cybersecurity; Distribution; Electric Grid Modernization; Energy Efficiency; Grid Cybersecurity; Transportation; Subsurface Science; Terrestrial Aquatics; Wind Energy; Dataset; Publication; Project; Data Source; Person; Institution; Software; Resource; Guide; Method; Virology; Immune Response; Time-sampled Measurement; Differential Expression; Gene Expression; Mass Spectrometry; Multi-Omics; Virus; MERS-CoV; Mus musculus; West Nile virus; Influenza A; Ebola; High-throughput Sequencing; Metagenomics; Soil Microbiology; Proteomics; Genomics; Sequencing; Synthetic Data; HDF5; CSV; Globus; Remote Sensing; Large Eddy Simulation; Hydrologic Modeling; Transmissivity Fields; Land Surface Parameters; Tropical Cyclone Tracks; Hydraulic Pressure Fields; PFAS Spectra; Aerosol Modeling; LES; Climate Modeling; Hydrometeorology; Soil Moisture Products; Energy Vulnerability Index; Urban Energy Insecurity; Rooftop Solar; Weatherization; Friction Stir Welding; MCPC Characterization; Chitin Decomposition; Electric Vulnerability; Personal Chemical Exposure; Proteome Profiling; Metabolomics; Lipidomics; Hi-C Metagenomics; Hydraulic Transmissivity; Pressure Field Outputs; Q Exactive Plus; Illumina HiSeq X; Illumina MiSeq; Q Exactive GC Orbitrap; Synchrotron XPS; FTICR Mass Spectrometer; Orbitrap Mass Spec; Epifluorescence Microscopy; X-ray Diffraction; Electricity; Susceptability; Storms; Atmospheric Shift; Ecological changes; Weather pattern disruption; power; United States; policy; scientific data; research data; environmental data; climate data; energy data; experimental data; modeling data; simulation data; data repository; open data; data download; data analysis; geospatial data; atmospheric data; hydrological data; renewable energy data; greenhouse gas data; carbon emissions; water quality; soil data; weather data; sensor data; time series data; laboratory data; field data; data visualization; metadata; scientific research; computational modeling; data sharing; research collaboration; experimental results; project data; scientific computing; environmental monitoring; data standards; data quality; scientific datasets; research datasets; open science; big data; data curation; data management; scientific workflows; technology development; energy systems; PNNL research; grid resilience; electrical infrastructure; climate resilience; extreme weather impacts; energy reliability; electric grid modeling; transmission systems; storm vulnerability; infrastructure risk assessment; smart grid data; grid modernization; energy disruption; blackout analysis; grid hardening; weather-resilient energy systems; data science in energy; high-performance computing; environmental modeling; atmospheric simulations; integrated assessment models; hydrometeorological data; scientific data interoperability; FAIR data principles; scientific data infrastructure; observational data; multivariate data; climate projections; decarbonization data; clean energy transition; climate science; environmental risk assessment; renewable integration; simulation output data; scientific reproducibility; sensor networks; field campaign data; system dynamics modeling; data provenance; collaborative research platforms; cloud-based data systems; DOE data initiatives; research instrumentation; experimental protocols; model validation data; scientific metadata standards; sustainability data; knowledge discovery; interdisciplinary research; research metadata; scientific benchmarking; open access data; DOE National Labs; environmental resilience; climate adaptation; decarbonization strategies; bioinformatics; energy forecasting; grid optimization; power systems; molecular biology; energy transition; hydrogen economy; clean tech; carbon capture; carbon sequestration; electrification; precision agriculture; environmental genomics; environmental chemistry; advanced materials; battery innovation; smart sensors; AI in science; machine learning models; deep learning applications; real-time data; edge computing; high-resolution modeling; predictive modeling; climate impact modeling; earth observation; remote labs; sample metadata; environmental DNA; metatranscriptomics; host-pathogen interaction; zoonotic viruses; air quality; pollutant tracking; chemical forensics; forensic science; biodefense; cyberinfrastructure; quantum computing; supercomputing; exascale computing; digital twin; scientific visualization; temporal datasets; spatial datasets; climate justice; energy equity; environmental equity; equity mapping; urban analytics; green infrastructure; infrastructure monitoring; environmental sensors; sensor fusion; satellite data; UAV data; drone mapping; climate informatics; data pipelines; data integration; bioinformatics pipelines; multi-scale modeling; decision support systems; resilience planning; vulnerability mapping; water-energy nexus; carbon intensity; grid decarbonization; storm modeling; extreme heat modeling; natural hazards; wildfire risk; air-sea interactions; boundary layer dynamics; data governance; research reproducibility; cyber-physical systems; science policy interface; DOE Office of Science; science communication; national lab collaboration; translational research; multidisciplinary research; climate-smart innovation; life cycle assessment; circular economy; low-carbon technologies; just energy transition; infrastructure resilience; distributed energy resources; grid flexibility; data-driven insights; scientific platforms; experimental facilities; research tools; analytic workflows; data catalogs; open-access repositories; big data analytics; scientific code; software tools; FAIR principles; data interoperability; scientific archives; data lifecycle management; Historic; Current; Present; 2019 - 2025</t>
         </is>
       </c>
       <c r="M13" s="25" t="inlineStr">
         <is>
-          <t>The PNNL DataHub is an open-access, DOE‑supported platform hosting thousands of research datasets—spanning biology, Earth and atmospheric sciences, energy systems, materials science, and more—complete with associated publications, project information, metadata, and source code for reuse and citation.
+          <t>The PNNL DataHub is an open-access, DOE-supported platform hosting thousands of research datasets—spanning biology, Earth and atmospheric sciences, energy systems, materials science, and more—complete with associated publications, project information, metadata, and source code for reuse and citation.
 #### Host Organization
 - Pacific Northwest National Laboratory
 - U.S. Department of Energy: Wind Energy Technologies Office  Energy Efficiency and Renewable Energy
@@ -1923,7 +1923,7 @@
       </c>
       <c r="M15" s="25" t="inlineStr">
         <is>
-          <t>The World Animal Health Information System (WAHIS), provided by WOAH, is a publicly accessible global platform that publishes verified, real-time animal disease data—including immediate alerts, follow-up updates, six‑monthly and annual reports on WOAH-listed diseases (for both domestic and wild species), with detailed outbreak counts, species affected, geographic spread, control measures, and veterinary capacities to support surveillance, trade, decision‑making, and research.
+          <t>The World Animal Health Information System (WAHIS), provided by WOAH, is a publicly accessible global platform that publishes verified, real-time animal disease data—including immediate alerts, follow-up updates, six-monthly and annual reports on WOAH-listed diseases (for both domestic and wild species), with detailed outbreak counts, species affected, geographic spread, control measures, and veterinary capacities to support surveillance, trade, decision-making, and research.
 #### Host Organization
 - World Organization for Animal Health 
 #### Data Format
@@ -2449,7 +2449,7 @@
       </c>
       <c r="L21" s="24" t="inlineStr">
         <is>
-          <t>sea ice extent; sea ice concentration; sea ice thickness; sea ice age; sea ice freeboard; sea ice motion; sea ice draft; sea ice melt ponds; passive microwave; MASIE; climate data record CDR; near‑real‑time data; daily data; monthly data; hemispheric data; Arctic data; Antarctic data; Northern Hemisphere data; Southern Hemisphere data; 25 km grid; gridded data; polar stereographic projection; DMSP SSM/I; SMMR; SSMIS; Nimbus‑7; CryoSat‑2; ICESat‑2; satellite altimetry; helicopter lidar; field measurements; permafrost data; ground temperature; snow water equivalent SWE; snow depth; snow cover extent; glacier imagery; ice sheet elevation; glacier mass balance; ice shelf imagery; permafrost boreholes; EASE‑Grid; climate trends; interannual variability; historical sea ice; NOAA‑NSIDC datasets; NOAA funded; NSIDC DAAC; NASA‑NOAA missions; Arctic weather climate; Antarctic climate data; Arctic tutorial Python; data visualization; Jupyter notebooks; NetCDF format; data API; data tools; Historic; sea ice variability; ice edge position; ice floe tracking; ice thickness distribution; sea ice albedo; ice concentration anomalies; sea ice forecasting; ice deformation; ice dynamics; sea ice seasonal cycle; polar climate monitoring; cryosphere data; ocean-ice interaction; ice-ocean coupling; ice thermodynamics; satellite remote sensing; passive and active sensors; radar altimetry; microwave radiometry; SAR imagery; sea ice roughness; ice ridging; ice lead detection; freeze-up dates; melt season timing; ice volume estimates; polar vortex; climate model validation; ice thickness retrieval algorithms; sea ice observational data; ice-ocean modeling; polar night data; ice mass balance; ice draft measurements; ice thickness climatology; long-term ice trends; cryospheric processes; ice growth rates; polar climate variability; ice edge retreat; multiyear ice; first-year ice; ice export; sea ice concentration mapping; Arctic amplification; Antarctic sea ice variability; seasonal ice cycles; sea ice phenology; ice thickness validation; ice shelf monitoring; polar data archives; cryosphere research tools; ice buoy data; snow on ice measurements; climate change; soil; Historic; Current; Present; 1740 - 2025</t>
+          <t>sea ice extent; sea ice concentration; sea ice thickness; sea ice age; sea ice freeboard; sea ice motion; sea ice draft; sea ice melt ponds; passive microwave; MASIE; climate data record CDR; near-real-time data; daily data; monthly data; hemispheric data; Arctic data; Antarctic data; Northern Hemisphere data; Southern Hemisphere data; 25 km grid; gridded data; polar stereographic projection; DMSP SSM/I; SMMR; SSMIS; Nimbus-7; CryoSat-2; ICESat-2; satellite altimetry; helicopter lidar; field measurements; permafrost data; ground temperature; snow water equivalent SWE; snow depth; snow cover extent; glacier imagery; ice sheet elevation; glacier mass balance; ice shelf imagery; permafrost boreholes; EASE-Grid; climate trends; interannual variability; historical sea ice; NOAA-NSIDC datasets; NOAA funded; NSIDC DAAC; NASA-NOAA missions; Arctic weather climate; Antarctic climate data; Arctic tutorial Python; data visualization; Jupyter notebooks; NetCDF format; data API; data tools; Historic; sea ice variability; ice edge position; ice floe tracking; ice thickness distribution; sea ice albedo; ice concentration anomalies; sea ice forecasting; ice deformation; ice dynamics; sea ice seasonal cycle; polar climate monitoring; cryosphere data; ocean-ice interaction; ice-ocean coupling; ice thermodynamics; satellite remote sensing; passive and active sensors; radar altimetry; microwave radiometry; SAR imagery; sea ice roughness; ice ridging; ice lead detection; freeze-up dates; melt season timing; ice volume estimates; polar vortex; climate model validation; ice thickness retrieval algorithms; sea ice observational data; ice-ocean modeling; polar night data; ice mass balance; ice draft measurements; ice thickness climatology; long-term ice trends; cryospheric processes; ice growth rates; polar climate variability; ice edge retreat; multiyear ice; first-year ice; ice export; sea ice concentration mapping; Arctic amplification; Antarctic sea ice variability; seasonal ice cycles; sea ice phenology; ice thickness validation; ice shelf monitoring; polar data archives; cryosphere research tools; ice buoy data; snow on ice measurements; climate change; soil; Historic; Current; Present; 1740 - 2025</t>
         </is>
       </c>
       <c r="M21" s="25" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="L23" s="24" t="inlineStr">
         <is>
-          <t>meteorological data; soil sensor data; water sensor data; phenology data; organismal observations; airborne remote sensing; AOP lidar; AOP imaging spectrometer; AOP digital camera; flux tower; 2‑D sonic anemometer; soil temperature; soil moisture; soil CO₂ concentration; groundwater data; surface water chemistry; precipitation measurements; snow depth; plant phenology; breeding landbirds; small mammals; mosquitoes; ticks; ground beetles; soil microbes; aquatic macroinvertebrates; phytoplankton; periphyton; algae; fish; DNA sequence data; pathogen testing; Biological Variability data; carbon exchange flux; nutrient cycling; stream discharge; evapotranspiration; land cover mapping; vegetation height; biomass; topography; slope; aspect; plot-level vegetation; micrometeorological tower; phenocam imagery; terrestrial instrument system; aquatic instrument system; airborne; terrestrial observation system; aquatic observation system; data API; GraphQL; CSV download; HDF5 files; GeoTIFF imagery; shapefile; KML export; neonUtilities R package; data portal downloads; quality-controlled data; data availability charts; data latency; data completeness; data validity; sample archives; soil archives; automated instruments; observational sampling; protocols &amp; metadata; data tutorials; data visualization; code hub; learning hub; open access data; environmental monitoring; remote sensing platforms; spectral imagery; LiDAR point cloud; eddy covariance; carbon sequestration; soil respiration; water quality monitoring; hydrological sensors; stream gauge; aquatic biodiversity; ecological indicators; phenological events; wildlife surveys; insect monitoring; amphibian surveys; biodiversity metrics; ecosystem services; soil nutrient analysis; dissolved oxygen; turbidity; chlorophyll concentration; sediment transport; groundwater monitoring; weather stations; micrometeorological measurements; atmospheric chemistry; climate variables; plant community composition; vegetation indices; NDVI; habitat quality; ecological modeling data; species distribution modeling; ecological forecasting; environmental gradients; field sensor networks; sensor calibration protocols; sensor data fusion; real-time environmental data; data assimilation; environmental data portals; open environmental data; data interoperability; scientific data repositories; metadata standards; data provenance; data quality assurance; environmental data analytics; open source tools; R packages for ecology; GIS environmental layers; spatial data integration; ecosystem monitoring networks; experimental ecology data; long-term ecological research; data sharing platforms; environmental data visualization; machine learning in ecology; ecosystem resilience; data-driven ecological insights; interdisciplinary environmental research; Climate change; Historic; Current; Present; 2012 - 2025</t>
+          <t>meteorological data; soil sensor data; water sensor data; phenology data; organismal observations; airborne remote sensing; AOP lidar; AOP imaging spectrometer; AOP digital camera; flux tower; 2-D sonic anemometer; soil temperature; soil moisture; soil CO₂ concentration; groundwater data; surface water chemistry; precipitation measurements; snow depth; plant phenology; breeding landbirds; small mammals; mosquitoes; ticks; ground beetles; soil microbes; aquatic macroinvertebrates; phytoplankton; periphyton; algae; fish; DNA sequence data; pathogen testing; Biological Variability data; carbon exchange flux; nutrient cycling; stream discharge; evapotranspiration; land cover mapping; vegetation height; biomass; topography; slope; aspect; plot-level vegetation; micrometeorological tower; phenocam imagery; terrestrial instrument system; aquatic instrument system; airborne; terrestrial observation system; aquatic observation system; data API; GraphQL; CSV download; HDF5 files; GeoTIFF imagery; shapefile; KML export; neonUtilities R package; data portal downloads; quality-controlled data; data availability charts; data latency; data completeness; data validity; sample archives; soil archives; automated instruments; observational sampling; protocols &amp; metadata; data tutorials; data visualization; code hub; learning hub; open access data; environmental monitoring; remote sensing platforms; spectral imagery; LiDAR point cloud; eddy covariance; carbon sequestration; soil respiration; water quality monitoring; hydrological sensors; stream gauge; aquatic biodiversity; ecological indicators; phenological events; wildlife surveys; insect monitoring; amphibian surveys; biodiversity metrics; ecosystem services; soil nutrient analysis; dissolved oxygen; turbidity; chlorophyll concentration; sediment transport; groundwater monitoring; weather stations; micrometeorological measurements; atmospheric chemistry; climate variables; plant community composition; vegetation indices; NDVI; habitat quality; ecological modeling data; species distribution modeling; ecological forecasting; environmental gradients; field sensor networks; sensor calibration protocols; sensor data fusion; real-time environmental data; data assimilation; environmental data portals; open environmental data; data interoperability; scientific data repositories; metadata standards; data provenance; data quality assurance; environmental data analytics; open source tools; R packages for ecology; GIS environmental layers; spatial data integration; ecosystem monitoring networks; experimental ecology data; long-term ecological research; data sharing platforms; environmental data visualization; machine learning in ecology; ecosystem resilience; data-driven ecological insights; interdisciplinary environmental research; Climate change; Historic; Current; Present; 2012 - 2025</t>
         </is>
       </c>
       <c r="M23" s="25" t="inlineStr">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="L24" s="15" t="inlineStr">
         <is>
-          <t>Hazards; Waste; ecosystem; Contamination; USFS; EDW datasets; geospatial data; map services; downloadable data; national datasets; raster data; vector data; ESRI geodatabase; shapefile; GeoPackage; GeoJSON; CSV export; Character Separated Values; FGDB; KML export; GeoTIFF; ArcGIS REST service; OGC WMS; spatial data discovery; Geospatial Data Discovery Tool; FSTopo; visitor maps; interactive maps; motor vehicle user maps; administrative boundaries; forest boundaries; region boundaries; national forest lands; designated management areas; wilderness areas; wild &amp; scenic rivers; surface ownership; Land and Water Conservation Fund parcels; FASAB land classification; range vegetation improvement; silviculture; timber stand improvement; watershed condition classification; invasive plant occurrences; hazards/disasters; landscape change monitoring; forest biomass; tree canopy cover; Caribbean land cover; Chugach updates; rangelands; BigMap FIA; Puerto Rico Gap Analysis; special purpose FS data; State Private Tribal Forestry; research and development; map downloads; metadata XML; data discovery; attribute accuracy; FGDC metadata; spatial resolution; data refresh date; data quality; legal disclaimers; data standards; systems of record; resource planning; fire management; recreation; roads and trails; infrastructure data; hydrology; streamflow modeling; NHDPlus; climate projections; RCP8.5; VIC hydrologic model; business intelligence tools; Forest Service GIS; FSGeodata Clearinghouse; Data.gov; ArcGIS Online; open data portal; eco‑data integration; user licenses; map symbology; layer selection; map imagery; forest service maps; remote sensing; map tile services; web mapping; API services; XML metadata; geospatial standards; data discovery metadata manual; geospatial clearinghouse; data refresh schedule; download formats; forest service field centers; FSIC‑GO; environmental hazards; pollution data; hazardous waste sites; contaminated sites; soil contamination; water contamination; chemical spills; environmental risk assessment; disaster response mapping; emergency management GIS; spatial risk analysis; land use planning; natural resource data; forest health monitoring; wildfire risk; fire perimeter mapping; vegetation management; ecosystem restoration; soil erosion data; watershed management; hydrologic datasets; floodplain mapping; topographic data; digital elevation models; remote sensing imagery; multispectral data; LiDAR datasets; aerial photography; geospatial analytics; cartographic services; map visualization tools; spatial data infrastructure; data interoperability standards; geospatial metadata; geodatabase management; GIS web services; spatial data catalogs; data download portals; spatial data APIs; map service interoperability; cloud GIS platforms; spatial data governance; geographic information science; geospatial data portals; federal land management data; forest inventory analysis; landscape ecology; ecological footprint mapping; habitat suitability models; protected lands data; GIS data security; spatial decision support systems; environmental monitoring networks; forest carbon data; land cover classification; geospatial data visualization; user access controls; open GIS data; spatial data quality assurance; land tenure data; digital cartography; interactive geospatial dashboards; geospatial data standards compliance; geospatial workflows; GIS training resources; spatial data licensing; map layer metadata; spatial data cataloging; geospatial data refresh protocols; Historic; Current; Present; 1976 - 2025</t>
+          <t>Hazards; Waste; ecosystem; Contamination; USFS; EDW datasets; geospatial data; map services; downloadable data; national datasets; raster data; vector data; ESRI geodatabase; shapefile; GeoPackage; GeoJSON; CSV export; Character Separated Values; FGDB; KML export; GeoTIFF; ArcGIS REST service; OGC WMS; spatial data discovery; Geospatial Data Discovery Tool; FSTopo; visitor maps; interactive maps; motor vehicle user maps; administrative boundaries; forest boundaries; region boundaries; national forest lands; designated management areas; wilderness areas; wild &amp; scenic rivers; surface ownership; Land and Water Conservation Fund parcels; FASAB land classification; range vegetation improvement; silviculture; timber stand improvement; watershed condition classification; invasive plant occurrences; hazards/disasters; landscape change monitoring; forest biomass; tree canopy cover; Caribbean land cover; Chugach updates; rangelands; BigMap FIA; Puerto Rico Gap Analysis; special purpose FS data; State Private Tribal Forestry; research and development; map downloads; metadata XML; data discovery; attribute accuracy; FGDC metadata; spatial resolution; data refresh date; data quality; legal disclaimers; data standards; systems of record; resource planning; fire management; recreation; roads and trails; infrastructure data; hydrology; streamflow modeling; NHDPlus; climate projections; RCP8.5; VIC hydrologic model; business intelligence tools; Forest Service GIS; FSGeodata Clearinghouse; Data.gov; ArcGIS Online; open data portal; eco-data integration; user licenses; map symbology; layer selection; map imagery; forest service maps; remote sensing; map tile services; web mapping; API services; XML metadata; geospatial standards; data discovery metadata manual; geospatial clearinghouse; data refresh schedule; download formats; forest service field centers; FSIC-GO; environmental hazards; pollution data; hazardous waste sites; contaminated sites; soil contamination; water contamination; chemical spills; environmental risk assessment; disaster response mapping; emergency management GIS; spatial risk analysis; land use planning; natural resource data; forest health monitoring; wildfire risk; fire perimeter mapping; vegetation management; ecosystem restoration; soil erosion data; watershed management; hydrologic datasets; floodplain mapping; topographic data; digital elevation models; remote sensing imagery; multispectral data; LiDAR datasets; aerial photography; geospatial analytics; cartographic services; map visualization tools; spatial data infrastructure; data interoperability standards; geospatial metadata; geodatabase management; GIS web services; spatial data catalogs; data download portals; spatial data APIs; map service interoperability; cloud GIS platforms; spatial data governance; geographic information science; geospatial data portals; federal land management data; forest inventory analysis; landscape ecology; ecological footprint mapping; habitat suitability models; protected lands data; GIS data security; spatial decision support systems; environmental monitoring networks; forest carbon data; land cover classification; geospatial data visualization; user access controls; open GIS data; spatial data quality assurance; land tenure data; digital cartography; interactive geospatial dashboards; geospatial data standards compliance; geospatial workflows; GIS training resources; spatial data licensing; map layer metadata; spatial data cataloging; geospatial data refresh protocols; Historic; Current; Present; 1976 - 2025</t>
         </is>
       </c>
       <c r="M24" s="16" t="inlineStr">
@@ -3067,7 +3067,7 @@
 - Public
 #### Citation Information
 - Follow the instructions on the [NOAA by the Numbers - How to Cite Page](https://sciencecouncil.noaa.gov/noaa-by-the-numbers/how-to-cite/)
-- National Centers for Environmental Information. (n.d.). *World Ocean Database*. Retrieved July 22, 2025, from &lt;https://www.ncei.noaa.gov/products/world-ocean-database Wikipedia+13NCEI+13Data.gov+13&gt;
+- National Centers for Environmental Information. (n.d.). *World Ocean Database*. Retrieved July 22, 2025, from &lt;https://www.ncei.noaa.gov/products/world-ocean-database Wikipedia+13NCEI+13Data.gov+13&gt;
 - See specific source citation details on the database website.</t>
         </is>
       </c>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="M29" s="25" t="inlineStr">
         <is>
-          <t>BV‑BRC (Bacterial &amp; Viral Bioinformatics Resource Center) houses structured data linked to millions of assembled and annotated bacterial, archaeal, viral, phage and select eukaryotic genomes—sourced primarily from NCBI’s GenBank/RefSeq and SRA—and enriched with standardized metadata (e.g. antimicrobial resistance, clinical, taxonomy), curated features (genes, pathways, protein families, virulence factors) and integrated additional data types like protein‑protein interactions, protein structures, epitopes, domains, transcriptomics, and surveillance/serology datasets. It supports this data through a distributed SolrCloud database and offers users both a web interface and API/command‑line tools (e.g. annotation, BLAST, phylogenomics, metagenomics, primer design) to enable integrated infectious‑disease research and comparative analysis workflows.
+          <t>BV-BRC (Bacterial &amp; Viral Bioinformatics Resource Center) houses structured data linked to millions of assembled and annotated bacterial, archaeal, viral, phage and select eukaryotic genomes—sourced primarily from NCBI’s GenBank/RefSeq and SRA—and enriched with standardized metadata (e.g. antimicrobial resistance, clinical, taxonomy), curated features (genes, pathways, protein families, virulence factors) and integrated additional data types like protein-protein interactions, protein structures, epitopes, domains, transcriptomics, and surveillance/serology datasets. It supports this data through a distributed SolrCloud database and offers users both a web interface and API/command-line tools (e.g. annotation, BLAST, phylogenomics, metagenomics, primer design) to enable integrated infectious-disease research and comparative analysis workflows.
 #### Host Organization
 - National Institute of Allergy and Infectious Diseases 
 #### Data Format
@@ -3152,7 +3152,7 @@
 - Public
 #### Citation Information
 - Follow the instructions on the [Citing BV-BRC Resources Page](https://www.bv-brc.org/citation)
-- Olson RD, Assaf R, Brettin T, Conrad N, Cucinell C, Davis JJ, Dempsey DM, Dickerman A, Dietrich EM, Kenyon RW, Kuscuoglu M, Lefkowitz EJ, Lu J, Machi D, Macken C, Mao C, Niewiadomska A, Nguyen M, Olsen GJ, Overbeek JC, Parrello B, Parrello V, Porter JS, Pusch GD, Shukla M, Singh I, Stewart L, Tan G, Thomas C, VanOeffelen M, Vonstein V, Wallace ZS, Warren AS, Wattam AR, Xia F, Yoo H, Zhang Y, Zmasek CM, Scheuermann RH, Stevens RL. *Introducing the Bacterial and Viral Bioinformatics Resource Center (BV‑BRC): a resource combining PATRIC, IRD and ViPR*. Nucleic Acids Res. 2022 Nov 9 (online ahead of print): gkac1003. doi: 10.1093/nar/gkac1003. PMID: 36350631.
+- Olson RD, Assaf R, Brettin T, Conrad N, Cucinell C, Davis JJ, Dempsey DM, Dickerman A, Dietrich EM, Kenyon RW, Kuscuoglu M, Lefkowitz EJ, Lu J, Machi D, Macken C, Mao C, Niewiadomska A, Nguyen M, Olsen GJ, Overbeek JC, Parrello B, Parrello V, Porter JS, Pusch GD, Shukla M, Singh I, Stewart L, Tan G, Thomas C, VanOeffelen M, Vonstein V, Wallace ZS, Warren AS, Wattam AR, Xia F, Yoo H, Zhang Y, Zmasek CM, Scheuermann RH, Stevens RL. *Introducing the Bacterial and Viral Bioinformatics Resource Center (BV-BRC): a resource combining PATRIC, IRD and ViPR*. Nucleic Acids Res. 2022 Nov 9 (online ahead of print): gkac1003. doi: 10.1093/nar/gkac1003. PMID: 36350631.
 - See specific source citation details on the database website.</t>
         </is>
       </c>
